--- a/Модель_TCO_экскаваторов_аннуитет.xlsx
+++ b/Модель_TCO_экскаваторов_аннуитет.xlsx
@@ -3422,7 +3422,7 @@
     <row r="34">
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Капитальные ремонты (ППР) — из списка</t>
+          <t>Капитальные ремонты (запчасти) — авто</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -3431,50 +3431,50 @@
         </is>
       </c>
       <c r="E34" s="38">
-        <f>SUM(E69:E90)</f>
+        <f>SUM(E69:E90)-E35</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>SUM(F69:F90)</f>
+        <f>SUM(F69:F90)-F35</f>
         <v/>
       </c>
       <c r="G34" s="38">
-        <f>SUM(G69:G90)</f>
+        <f>SUM(G69:G90)-G35</f>
         <v/>
       </c>
       <c r="H34" s="38">
-        <f>SUM(H69:H90)</f>
+        <f>SUM(H69:H90)-H35</f>
         <v/>
       </c>
       <c r="I34" s="38">
-        <f>SUM(I69:I90)</f>
+        <f>SUM(I69:I90)-I35</f>
         <v/>
       </c>
       <c r="J34" s="38">
-        <f>SUM(J69:J90)</f>
+        <f>SUM(J69:J90)-J35</f>
         <v/>
       </c>
       <c r="K34" s="38">
-        <f>SUM(K69:K90)</f>
+        <f>SUM(K69:K90)-K35</f>
         <v/>
       </c>
       <c r="L34" s="38">
-        <f>SUM(L69:L90)</f>
+        <f>SUM(L69:L90)-L35</f>
         <v/>
       </c>
       <c r="M34" s="38">
-        <f>SUM(M69:M90)</f>
+        <f>SUM(M69:M90)-M35</f>
         <v/>
       </c>
       <c r="N34" s="38">
-        <f>SUM(N69:N90)</f>
+        <f>SUM(N69:N90)-N35</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Сервис ремонтов (трудозатраты)</t>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -3482,35 +3482,45 @@
           <t>тыс/год</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0</v>
+      <c r="E35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(E69:E90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(F69:F90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="G35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(G69:G90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(H69:H90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(I69:I90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="J35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(J69:J90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="K35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(K69:K90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="L35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(L69:L90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="M35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(M69:M90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="N35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(N69:N90&gt;0)*1)*$E$29/1000</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -4616,6 +4626,9 @@
           <t>Прочие/укрупнённо (капремонт)</t>
         </is>
       </c>
+      <c r="C90" s="47" t="n">
+        <v>250</v>
+      </c>
       <c r="E90" s="47" t="n">
         <v>0</v>
       </c>
@@ -4650,7 +4663,7 @@
     <row r="92">
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (стоимость по годам). КТГ, затраты ТО и капремонты пересчитаются снизу вверх; сводка «Данные по годам» и весь расчёт обновятся автоматически. Строка «Корректировка» и «Прочие/укрупнённо» — балансирующие, замените детализацией.</t>
+          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (нормо-час + стоимость по годам). Трудозатраты (сервис) считаются автоматически: нормо-часы ремонтируемых в году узлов × ставку (стр. «Ставка сервиса»); сервис ТО = ч·часы ТО × ставку. КТГ, затраты ТО и капремонты — снизу вверх; сводка «Данные по годам» и весь расчёт обновятся сами. Строки «Корректировка» и «Прочие/укрупнённо» — балансирующие.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18657,7 @@
     <row r="34">
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Капитальные ремонты (ППР) — из списка</t>
+          <t>Капитальные ремонты (запчасти) — авто</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -18653,50 +18666,50 @@
         </is>
       </c>
       <c r="E34" s="38">
-        <f>SUM(E69:E90)</f>
+        <f>SUM(E69:E90)-E35</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>SUM(F69:F90)</f>
+        <f>SUM(F69:F90)-F35</f>
         <v/>
       </c>
       <c r="G34" s="38">
-        <f>SUM(G69:G90)</f>
+        <f>SUM(G69:G90)-G35</f>
         <v/>
       </c>
       <c r="H34" s="38">
-        <f>SUM(H69:H90)</f>
+        <f>SUM(H69:H90)-H35</f>
         <v/>
       </c>
       <c r="I34" s="38">
-        <f>SUM(I69:I90)</f>
+        <f>SUM(I69:I90)-I35</f>
         <v/>
       </c>
       <c r="J34" s="38">
-        <f>SUM(J69:J90)</f>
+        <f>SUM(J69:J90)-J35</f>
         <v/>
       </c>
       <c r="K34" s="38">
-        <f>SUM(K69:K90)</f>
+        <f>SUM(K69:K90)-K35</f>
         <v/>
       </c>
       <c r="L34" s="38">
-        <f>SUM(L69:L90)</f>
+        <f>SUM(L69:L90)-L35</f>
         <v/>
       </c>
       <c r="M34" s="38">
-        <f>SUM(M69:M90)</f>
+        <f>SUM(M69:M90)-M35</f>
         <v/>
       </c>
       <c r="N34" s="38">
-        <f>SUM(N69:N90)</f>
+        <f>SUM(N69:N90)-N35</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Сервис ремонтов (трудозатраты)</t>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -18704,35 +18717,45 @@
           <t>тыс/год</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0</v>
+      <c r="E35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(E69:E90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(F69:F90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="G35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(G69:G90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(H69:H90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(I69:I90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="J35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(J69:J90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="K35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(K69:K90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="L35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(L69:L90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="M35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(M69:M90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="N35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(N69:N90&gt;0)*1)*$E$29/1000</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -19838,6 +19861,9 @@
           <t>Прочие/укрупнённо (капремонт)</t>
         </is>
       </c>
+      <c r="C90" s="47" t="n">
+        <v>250</v>
+      </c>
       <c r="E90" s="47" t="n">
         <v>0</v>
       </c>
@@ -19872,7 +19898,7 @@
     <row r="92">
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (стоимость по годам). КТГ, затраты ТО и капремонты пересчитаются снизу вверх; сводка «Данные по годам» и весь расчёт обновятся автоматически. Строка «Корректировка» и «Прочие/укрупнённо» — балансирующие, замените детализацией.</t>
+          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (нормо-час + стоимость по годам). Трудозатраты (сервис) считаются автоматически: нормо-часы ремонтируемых в году узлов × ставку (стр. «Ставка сервиса»); сервис ТО = ч·часы ТО × ставку. КТГ, затраты ТО и капремонты — снизу вверх; сводка «Данные по годам» и весь расчёт обновятся сами. Строки «Корректировка» и «Прочие/укрупнённо» — балансирующие.</t>
         </is>
       </c>
     </row>
@@ -20986,7 +21012,7 @@
     <row r="34">
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Капитальные ремонты (ППР) — из списка</t>
+          <t>Капитальные ремонты (запчасти) — авто</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -20995,50 +21021,50 @@
         </is>
       </c>
       <c r="E34" s="38">
-        <f>SUM(E69:E90)</f>
+        <f>SUM(E69:E90)-E35</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>SUM(F69:F90)</f>
+        <f>SUM(F69:F90)-F35</f>
         <v/>
       </c>
       <c r="G34" s="38">
-        <f>SUM(G69:G90)</f>
+        <f>SUM(G69:G90)-G35</f>
         <v/>
       </c>
       <c r="H34" s="38">
-        <f>SUM(H69:H90)</f>
+        <f>SUM(H69:H90)-H35</f>
         <v/>
       </c>
       <c r="I34" s="38">
-        <f>SUM(I69:I90)</f>
+        <f>SUM(I69:I90)-I35</f>
         <v/>
       </c>
       <c r="J34" s="38">
-        <f>SUM(J69:J90)</f>
+        <f>SUM(J69:J90)-J35</f>
         <v/>
       </c>
       <c r="K34" s="38">
-        <f>SUM(K69:K90)</f>
+        <f>SUM(K69:K90)-K35</f>
         <v/>
       </c>
       <c r="L34" s="38">
-        <f>SUM(L69:L90)</f>
+        <f>SUM(L69:L90)-L35</f>
         <v/>
       </c>
       <c r="M34" s="38">
-        <f>SUM(M69:M90)</f>
+        <f>SUM(M69:M90)-M35</f>
         <v/>
       </c>
       <c r="N34" s="38">
-        <f>SUM(N69:N90)</f>
+        <f>SUM(N69:N90)-N35</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Сервис ремонтов (трудозатраты)</t>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -21046,35 +21072,45 @@
           <t>тыс/год</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0</v>
+      <c r="E35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(E69:E90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(F69:F90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="G35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(G69:G90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(H69:H90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(I69:I90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="J35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(J69:J90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="K35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(K69:K90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="L35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(L69:L90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="M35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(M69:M90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="N35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(N69:N90&gt;0)*1)*$E$29/1000</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -22180,6 +22216,9 @@
           <t>Прочие/укрупнённо (капремонт)</t>
         </is>
       </c>
+      <c r="C90" s="47" t="n">
+        <v>250</v>
+      </c>
       <c r="E90" s="47" t="n">
         <v>0</v>
       </c>
@@ -22214,7 +22253,7 @@
     <row r="92">
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (стоимость по годам). КТГ, затраты ТО и капремонты пересчитаются снизу вверх; сводка «Данные по годам» и весь расчёт обновятся автоматически. Строка «Корректировка» и «Прочие/укрупнённо» — балансирующие, замените детализацией.</t>
+          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (нормо-час + стоимость по годам). Трудозатраты (сервис) считаются автоматически: нормо-часы ремонтируемых в году узлов × ставку (стр. «Ставка сервиса»); сервис ТО = ч·часы ТО × ставку. КТГ, затраты ТО и капремонты — снизу вверх; сводка «Данные по годам» и весь расчёт обновятся сами. Строки «Корректировка» и «Прочие/укрупнённо» — балансирующие.</t>
         </is>
       </c>
     </row>
@@ -23328,7 +23367,7 @@
     <row r="34">
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Капитальные ремонты (ППР) — из списка</t>
+          <t>Капитальные ремонты (запчасти) — авто</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -23337,50 +23376,50 @@
         </is>
       </c>
       <c r="E34" s="38">
-        <f>SUM(E69:E90)</f>
+        <f>SUM(E69:E90)-E35</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>SUM(F69:F90)</f>
+        <f>SUM(F69:F90)-F35</f>
         <v/>
       </c>
       <c r="G34" s="38">
-        <f>SUM(G69:G90)</f>
+        <f>SUM(G69:G90)-G35</f>
         <v/>
       </c>
       <c r="H34" s="38">
-        <f>SUM(H69:H90)</f>
+        <f>SUM(H69:H90)-H35</f>
         <v/>
       </c>
       <c r="I34" s="38">
-        <f>SUM(I69:I90)</f>
+        <f>SUM(I69:I90)-I35</f>
         <v/>
       </c>
       <c r="J34" s="38">
-        <f>SUM(J69:J90)</f>
+        <f>SUM(J69:J90)-J35</f>
         <v/>
       </c>
       <c r="K34" s="38">
-        <f>SUM(K69:K90)</f>
+        <f>SUM(K69:K90)-K35</f>
         <v/>
       </c>
       <c r="L34" s="38">
-        <f>SUM(L69:L90)</f>
+        <f>SUM(L69:L90)-L35</f>
         <v/>
       </c>
       <c r="M34" s="38">
-        <f>SUM(M69:M90)</f>
+        <f>SUM(M69:M90)-M35</f>
         <v/>
       </c>
       <c r="N34" s="38">
-        <f>SUM(N69:N90)</f>
+        <f>SUM(N69:N90)-N35</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Сервис ремонтов (трудозатраты)</t>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -23388,35 +23427,45 @@
           <t>тыс/год</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0</v>
+      <c r="E35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(E69:E90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(F69:F90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="G35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(G69:G90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(H69:H90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(I69:I90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="J35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(J69:J90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="K35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(K69:K90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="L35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(L69:L90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="M35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(M69:M90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="N35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(N69:N90&gt;0)*1)*$E$29/1000</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -24522,6 +24571,9 @@
           <t>Прочие/укрупнённо (капремонт)</t>
         </is>
       </c>
+      <c r="C90" s="47" t="n">
+        <v>250</v>
+      </c>
       <c r="E90" s="47" t="n">
         <v>0</v>
       </c>
@@ -24556,7 +24608,7 @@
     <row r="92">
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (стоимость по годам). КТГ, затраты ТО и капремонты пересчитаются снизу вверх; сводка «Данные по годам» и весь расчёт обновятся автоматически. Строка «Корректировка» и «Прочие/укрупнённо» — балансирующие, замените детализацией.</t>
+          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (нормо-час + стоимость по годам). Трудозатраты (сервис) считаются автоматически: нормо-часы ремонтируемых в году узлов × ставку (стр. «Ставка сервиса»); сервис ТО = ч·часы ТО × ставку. КТГ, затраты ТО и капремонты — снизу вверх; сводка «Данные по годам» и весь расчёт обновятся сами. Строки «Корректировка» и «Прочие/укрупнённо» — балансирующие.</t>
         </is>
       </c>
     </row>
@@ -25670,7 +25722,7 @@
     <row r="34">
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Капитальные ремонты (ППР) — из списка</t>
+          <t>Капитальные ремонты (запчасти) — авто</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -25679,50 +25731,50 @@
         </is>
       </c>
       <c r="E34" s="38">
-        <f>SUM(E69:E90)</f>
+        <f>SUM(E69:E90)-E35</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>SUM(F69:F90)</f>
+        <f>SUM(F69:F90)-F35</f>
         <v/>
       </c>
       <c r="G34" s="38">
-        <f>SUM(G69:G90)</f>
+        <f>SUM(G69:G90)-G35</f>
         <v/>
       </c>
       <c r="H34" s="38">
-        <f>SUM(H69:H90)</f>
+        <f>SUM(H69:H90)-H35</f>
         <v/>
       </c>
       <c r="I34" s="38">
-        <f>SUM(I69:I90)</f>
+        <f>SUM(I69:I90)-I35</f>
         <v/>
       </c>
       <c r="J34" s="38">
-        <f>SUM(J69:J90)</f>
+        <f>SUM(J69:J90)-J35</f>
         <v/>
       </c>
       <c r="K34" s="38">
-        <f>SUM(K69:K90)</f>
+        <f>SUM(K69:K90)-K35</f>
         <v/>
       </c>
       <c r="L34" s="38">
-        <f>SUM(L69:L90)</f>
+        <f>SUM(L69:L90)-L35</f>
         <v/>
       </c>
       <c r="M34" s="38">
-        <f>SUM(M69:M90)</f>
+        <f>SUM(M69:M90)-M35</f>
         <v/>
       </c>
       <c r="N34" s="38">
-        <f>SUM(N69:N90)</f>
+        <f>SUM(N69:N90)-N35</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Сервис ремонтов (трудозатраты)</t>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -25730,35 +25782,45 @@
           <t>тыс/год</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0</v>
+      <c r="E35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(E69:E90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(F69:F90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="G35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(G69:G90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(H69:H90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(I69:I90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="J35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(J69:J90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="K35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(K69:K90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="L35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(L69:L90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="M35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(M69:M90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="N35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(N69:N90&gt;0)*1)*$E$29/1000</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -26864,6 +26926,9 @@
           <t>Прочие/укрупнённо (капремонт)</t>
         </is>
       </c>
+      <c r="C90" s="47" t="n">
+        <v>250</v>
+      </c>
       <c r="E90" s="47" t="n">
         <v>0</v>
       </c>
@@ -26898,7 +26963,7 @@
     <row r="92">
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (стоимость по годам). КТГ, затраты ТО и капремонты пересчитаются снизу вверх; сводка «Данные по годам» и весь расчёт обновятся автоматически. Строка «Корректировка» и «Прочие/укрупнённо» — балансирующие, замените детализацией.</t>
+          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (нормо-час + стоимость по годам). Трудозатраты (сервис) считаются автоматически: нормо-часы ремонтируемых в году узлов × ставку (стр. «Ставка сервиса»); сервис ТО = ч·часы ТО × ставку. КТГ, затраты ТО и капремонты — снизу вверх; сводка «Данные по годам» и весь расчёт обновятся сами. Строки «Корректировка» и «Прочие/укрупнённо» — балансирующие.</t>
         </is>
       </c>
     </row>
@@ -28012,7 +28077,7 @@
     <row r="34">
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Капитальные ремонты (ППР) — из списка</t>
+          <t>Капитальные ремонты (запчасти) — авто</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -28021,50 +28086,50 @@
         </is>
       </c>
       <c r="E34" s="38">
-        <f>SUM(E69:E90)</f>
+        <f>SUM(E69:E90)-E35</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>SUM(F69:F90)</f>
+        <f>SUM(F69:F90)-F35</f>
         <v/>
       </c>
       <c r="G34" s="38">
-        <f>SUM(G69:G90)</f>
+        <f>SUM(G69:G90)-G35</f>
         <v/>
       </c>
       <c r="H34" s="38">
-        <f>SUM(H69:H90)</f>
+        <f>SUM(H69:H90)-H35</f>
         <v/>
       </c>
       <c r="I34" s="38">
-        <f>SUM(I69:I90)</f>
+        <f>SUM(I69:I90)-I35</f>
         <v/>
       </c>
       <c r="J34" s="38">
-        <f>SUM(J69:J90)</f>
+        <f>SUM(J69:J90)-J35</f>
         <v/>
       </c>
       <c r="K34" s="38">
-        <f>SUM(K69:K90)</f>
+        <f>SUM(K69:K90)-K35</f>
         <v/>
       </c>
       <c r="L34" s="38">
-        <f>SUM(L69:L90)</f>
+        <f>SUM(L69:L90)-L35</f>
         <v/>
       </c>
       <c r="M34" s="38">
-        <f>SUM(M69:M90)</f>
+        <f>SUM(M69:M90)-M35</f>
         <v/>
       </c>
       <c r="N34" s="38">
-        <f>SUM(N69:N90)</f>
+        <f>SUM(N69:N90)-N35</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Сервис ремонтов (трудозатраты)</t>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -28072,35 +28137,45 @@
           <t>тыс/год</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>0</v>
+      <c r="E35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(E69:E90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(F69:F90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="G35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(G69:G90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(H69:H90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(I69:I90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="J35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(J69:J90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="K35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(K69:K90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="L35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(L69:L90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="M35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(M69:M90&gt;0)*1)*$E$29/1000</f>
+        <v/>
+      </c>
+      <c r="N35" s="38">
+        <f>SUMPRODUCT($C$69:$C$90,(N69:N90&gt;0)*1)*$E$29/1000</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -29206,6 +29281,9 @@
           <t>Прочие/укрупнённо (капремонт)</t>
         </is>
       </c>
+      <c r="C90" s="47" t="n">
+        <v>250</v>
+      </c>
       <c r="E90" s="47" t="n">
         <v>0</v>
       </c>
@@ -29240,7 +29318,7 @@
     <row r="92">
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (стоимость по годам). КТГ, затраты ТО и капремонты пересчитаются снизу вверх; сводка «Данные по годам» и весь расчёт обновятся автоматически. Строка «Корректировка» и «Прочие/укрупнённо» — балансирующие, замените детализацией.</t>
+          <t>Заполняйте: каталог запчастей ТО (цена, кол-во, № ТО) и список узлов/капремонтов (нормо-час + стоимость по годам). Трудозатраты (сервис) считаются автоматически: нормо-часы ремонтируемых в году узлов × ставку (стр. «Ставка сервиса»); сервис ТО = ч·часы ТО × ставку. КТГ, затраты ТО и капремонты — снизу вверх; сводка «Данные по годам» и весь расчёт обновятся сами. Строки «Корректировка» и «Прочие/укрупнённо» — балансирующие.</t>
         </is>
       </c>
     </row>

--- a/Модель_TCO_экскаваторов_аннуитет.xlsx
+++ b/Модель_TCO_экскаваторов_аннуитет.xlsx
@@ -2606,9 +2606,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Ежесменный осмотр</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -2616,35 +2616,45 @@
           <t>ч/год</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3347,34 +3357,34 @@
         </is>
       </c>
       <c r="E32" s="31" t="n">
-        <v>1000.04</v>
+        <v>786.13</v>
       </c>
       <c r="F32" s="31" t="n">
-        <v>2106.65</v>
+        <v>1924.36</v>
       </c>
       <c r="G32" s="31" t="n">
-        <v>1871.91</v>
+        <v>1682.92</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>2402.67</v>
+        <v>2228.84</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>2412.57</v>
+        <v>2239.02</v>
       </c>
       <c r="J32" s="31" t="n">
-        <v>1980.41</v>
+        <v>1794.52</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>2204.54</v>
+        <v>2025.05</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>1713.31</v>
+        <v>1519.78</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>2635.37</v>
+        <v>2468.19</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>1852.89</v>
+        <v>1663.35</v>
       </c>
     </row>
     <row r="33">
@@ -17841,9 +17851,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Ежесменный осмотр</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -17851,35 +17861,45 @@
           <t>ч/год</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -18582,34 +18602,34 @@
         </is>
       </c>
       <c r="E32" s="31" t="n">
-        <v>392</v>
+        <v>160.72</v>
       </c>
       <c r="F32" s="31" t="n">
-        <v>602.79</v>
+        <v>377.53</v>
       </c>
       <c r="G32" s="31" t="n">
-        <v>953.1900000000001</v>
+        <v>737.9400000000001</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>1040.79</v>
+        <v>828.05</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>953.1900000000001</v>
+        <v>737.9400000000001</v>
       </c>
       <c r="J32" s="31" t="n">
-        <v>1372.37</v>
+        <v>1169.1</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>1596.5</v>
+        <v>1399.63</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>1105.27</v>
+        <v>894.37</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>2027.33</v>
+        <v>1842.78</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>1244.85</v>
+        <v>1037.94</v>
       </c>
     </row>
     <row r="33">
@@ -20196,9 +20216,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Ежесменный осмотр</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -20206,35 +20226,45 @@
           <t>ч/год</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -20937,34 +20967,34 @@
         </is>
       </c>
       <c r="E32" s="31" t="n">
-        <v>392</v>
+        <v>160.72</v>
       </c>
       <c r="F32" s="31" t="n">
-        <v>1498.61</v>
+        <v>1298.94</v>
       </c>
       <c r="G32" s="31" t="n">
-        <v>1263.87</v>
+        <v>1057.5</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>1794.64</v>
+        <v>1603.44</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>1804.53</v>
+        <v>1613.61</v>
       </c>
       <c r="J32" s="31" t="n">
-        <v>1372.37</v>
+        <v>1169.1</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>1596.5</v>
+        <v>1399.63</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>1105.27</v>
+        <v>894.37</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>2027.33</v>
+        <v>1842.78</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>1244.85</v>
+        <v>1037.94</v>
       </c>
     </row>
     <row r="33">
@@ -22551,9 +22581,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Ежесменный осмотр</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -22561,35 +22591,45 @@
           <t>ч/год</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -23292,34 +23332,34 @@
         </is>
       </c>
       <c r="E32" s="31" t="n">
-        <v>1000.04</v>
+        <v>786.13</v>
       </c>
       <c r="F32" s="31" t="n">
-        <v>2106.65</v>
+        <v>1924.36</v>
       </c>
       <c r="G32" s="31" t="n">
-        <v>1871.91</v>
+        <v>1682.92</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>2402.67</v>
+        <v>2228.84</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>2412.57</v>
+        <v>2239.02</v>
       </c>
       <c r="J32" s="31" t="n">
-        <v>1980.41</v>
+        <v>1794.52</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>2204.54</v>
+        <v>2025.05</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>1713.31</v>
+        <v>1519.78</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>2635.37</v>
+        <v>2468.19</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>1852.89</v>
+        <v>1663.35</v>
       </c>
     </row>
     <row r="33">
@@ -24906,9 +24946,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Ежесменный осмотр</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -24916,35 +24956,45 @@
           <t>ч/год</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -25647,34 +25697,34 @@
         </is>
       </c>
       <c r="E32" s="31" t="n">
-        <v>1000.04</v>
+        <v>786.13</v>
       </c>
       <c r="F32" s="31" t="n">
-        <v>2106.65</v>
+        <v>1924.36</v>
       </c>
       <c r="G32" s="31" t="n">
-        <v>1871.91</v>
+        <v>1682.92</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>2402.67</v>
+        <v>2228.84</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>2412.57</v>
+        <v>2239.02</v>
       </c>
       <c r="J32" s="31" t="n">
-        <v>1980.41</v>
+        <v>1794.52</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>2204.54</v>
+        <v>2025.05</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>1713.31</v>
+        <v>1519.78</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>2635.37</v>
+        <v>2468.19</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>1852.89</v>
+        <v>1663.35</v>
       </c>
     </row>
     <row r="33">
@@ -27261,9 +27311,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Ежесменный осмотр</t>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -27271,35 +27321,45 @@
           <t>ч/год</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -28002,34 +28062,34 @@
         </is>
       </c>
       <c r="E32" s="31" t="n">
-        <v>1000.04</v>
+        <v>786.13</v>
       </c>
       <c r="F32" s="31" t="n">
-        <v>2106.65</v>
+        <v>1924.36</v>
       </c>
       <c r="G32" s="31" t="n">
-        <v>1871.91</v>
+        <v>1682.92</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>2402.67</v>
+        <v>2228.84</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>2412.57</v>
+        <v>2239.02</v>
       </c>
       <c r="J32" s="31" t="n">
-        <v>1980.41</v>
+        <v>1794.52</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>2204.54</v>
+        <v>2025.05</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>1713.31</v>
+        <v>1519.78</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>2635.37</v>
+        <v>2468.19</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>1852.89</v>
+        <v>1663.35</v>
       </c>
     </row>
     <row r="33">

--- a/Модель_TCO_экскаваторов_аннуитет.xlsx
+++ b/Модель_TCO_экскаваторов_аннуитет.xlsx
@@ -17,14 +17,15 @@
     <sheet name="Поставщик 4" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Поставщик 5" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Поставщик 6" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Данные по годам" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Производительность" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Денежный поток" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Расчёт аннуитета" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Сравнение" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Аналитика" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Чувствительность" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Справочник" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Поставщик 7" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Данные по годам" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Производительность" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Денежный поток" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Расчёт аннуитета" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Сравнение" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Аналитика" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Чувствительность" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Справочник" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,12 +587,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$4:$I$4</f>
+              <f>'Сравнение'!$D$4:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$12:$I$12</f>
+              <f>'Сравнение'!$D$12:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -860,6 +861,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Ввод данных'!J$7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Денежный поток'!$E$4:$N$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Денежный поток'!$E$139:$N$139</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -962,12 +995,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$21:$I$21</f>
+              <f>'Сравнение'!$D$21:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$22:$I$22</f>
+              <f>'Сравнение'!$D$22:$J$22</f>
             </numRef>
           </val>
         </ser>
@@ -986,12 +1019,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$21:$I$21</f>
+              <f>'Сравнение'!$D$21:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$23:$I$23</f>
+              <f>'Сравнение'!$D$23:$J$23</f>
             </numRef>
           </val>
         </ser>
@@ -1010,12 +1043,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$21:$I$21</f>
+              <f>'Сравнение'!$D$21:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$24:$I$24</f>
+              <f>'Сравнение'!$D$24:$J$24</f>
             </numRef>
           </val>
         </ser>
@@ -1034,12 +1067,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$21:$I$21</f>
+              <f>'Сравнение'!$D$21:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$25:$I$25</f>
+              <f>'Сравнение'!$D$25:$J$25</f>
             </numRef>
           </val>
         </ser>
@@ -1058,12 +1091,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$21:$I$21</f>
+              <f>'Сравнение'!$D$21:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$26:$I$26</f>
+              <f>'Сравнение'!$D$26:$J$26</f>
             </numRef>
           </val>
         </ser>
@@ -1082,12 +1115,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$21:$I$21</f>
+              <f>'Сравнение'!$D$21:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$27:$I$27</f>
+              <f>'Сравнение'!$D$27:$J$27</f>
             </numRef>
           </val>
         </ser>
@@ -1175,12 +1208,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$4:$I$4</f>
+              <f>'Сравнение'!$D$4:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$12:$I$12</f>
+              <f>'Сравнение'!$D$12:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -1268,12 +1301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Сравнение'!$D$4:$I$4</f>
+              <f>'Сравнение'!$D$4:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Сравнение'!$D$5:$I$5</f>
+              <f>'Сравнение'!$D$5:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1353,12 +1386,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Аналитика'!$D$7:$I$7</f>
+              <f>'Аналитика'!$D$7:$J$7</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Аналитика'!$D$9:$I$9</f>
+              <f>'Аналитика'!$D$9:$J$9</f>
             </numRef>
           </yVal>
         </ser>
@@ -1461,12 +1494,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Аналитика'!$D$4:$I$4</f>
+              <f>'Аналитика'!$D$4:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Аналитика'!$D$24:$I$24</f>
+              <f>'Аналитика'!$D$24:$J$24</f>
             </numRef>
           </val>
         </ser>
@@ -1483,12 +1516,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Аналитика'!$D$4:$I$4</f>
+              <f>'Аналитика'!$D$4:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Аналитика'!$D$25:$I$25</f>
+              <f>'Аналитика'!$D$25:$J$25</f>
             </numRef>
           </val>
         </ser>
@@ -1505,12 +1538,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Аналитика'!$D$4:$I$4</f>
+              <f>'Аналитика'!$D$4:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Аналитика'!$D$26:$I$26</f>
+              <f>'Аналитика'!$D$26:$J$26</f>
             </numRef>
           </val>
         </ser>
@@ -3505,43 +3538,43 @@
         </is>
       </c>
       <c r="E35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(E75:E82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(E75:E82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="F35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(F75:F82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(F75:F82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="G35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(G75:G82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(G75:G82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="H35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(H75:H82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(H75:H82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="I35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(I75:I82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(I75:I82&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
       <c r="J35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(J75:J82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(J75:J82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="K35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(K75:K82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(K75:K82&gt;0)*1),0))*$E$29/1000</f>
         <v>6.0</v>
       </c>
       <c r="L35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(L75:L82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(L75:L82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="M35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(M75:M82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(M75:M82&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="N35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1)+SUMPRODUCT($P$75:$P$82,(N75:N82&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(N75:N82&gt;0)*1),0))*$E$29/1000</f>
         <v>8.4</v>
       </c>
     </row>
@@ -4933,7 +4966,2601 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:N35"/>
+  <dimension ref="B1:P84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ШАБЛОН ДАННЫХ ПОСТАВЩИКА — ВАРИАНТ 7</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Модели ТО и Ремонтов с полными списками. Зелёное — авто; сводка тянется в «Данные по годам».</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Экскаватор:</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="str">
+        <f>'Ввод данных'!J7</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Валюта затрат ТОиР:</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>год 1</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>год 2</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>год 3</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>год 4</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>год 5</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>год 6</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>год 7</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>год 8</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>год 9</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>год 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>СВОДКА ПО ГОДАМ (зелёное — авто из моделей ниже; тянется в расчёт)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Простои на ТО</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>ч/год</t>
+        </is>
+      </c>
+      <c r="E8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="F8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="G8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="H8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="I8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="J8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="K8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="L8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="M8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+      <c r="N8" s="38">
+        <f>$G$27</f>
+        <v>273.21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>Простои в ремонтах</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>ч/год</t>
+        </is>
+      </c>
+      <c r="E9" s="38">
+        <f>E32</f>
+        <v>242.79</v>
+      </c>
+      <c r="F9" s="38">
+        <f>F32</f>
+        <v>283.79</v>
+      </c>
+      <c r="G9" s="38">
+        <f>G32</f>
+        <v>1065.79</v>
+      </c>
+      <c r="H9" s="38">
+        <f>H32</f>
+        <v>291.29</v>
+      </c>
+      <c r="I9" s="38">
+        <f>I32</f>
+        <v>337.79</v>
+      </c>
+      <c r="J9" s="38">
+        <f>J32</f>
+        <v>1211.79</v>
+      </c>
+      <c r="K9" s="38">
+        <f>K32</f>
+        <v>437.79</v>
+      </c>
+      <c r="L9" s="38">
+        <f>L32</f>
+        <v>1151.29</v>
+      </c>
+      <c r="M9" s="38">
+        <f>M32</f>
+        <v>1005.79</v>
+      </c>
+      <c r="N9" s="38">
+        <f>N32</f>
+        <v>1187.79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Ежесменное ТО (20 мин/смену)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>ч/год</t>
+        </is>
+      </c>
+      <c r="E10" s="38">
+        <f>('Параметры'!C26-E8-E9)/'Параметры'!C33*20/60</f>
+        <v>229.0</v>
+      </c>
+      <c r="F10" s="38">
+        <f>('Параметры'!C26-F8-F9)/'Параметры'!C33*20/60</f>
+        <v>227.86111111111114</v>
+      </c>
+      <c r="G10" s="38">
+        <f>('Параметры'!C26-G8-G9)/'Параметры'!C33*20/60</f>
+        <v>206.13888888888894</v>
+      </c>
+      <c r="H10" s="38">
+        <f>('Параметры'!C26-H8-H9)/'Параметры'!C33*20/60</f>
+        <v>227.6527777777778</v>
+      </c>
+      <c r="I10" s="38">
+        <f>('Параметры'!C26-I8-I9)/'Параметры'!C33*20/60</f>
+        <v>226.36111111111114</v>
+      </c>
+      <c r="J10" s="38">
+        <f>('Параметры'!C26-J8-J9)/'Параметры'!C33*20/60</f>
+        <v>202.08333333333337</v>
+      </c>
+      <c r="K10" s="38">
+        <f>('Параметры'!C26-K8-K9)/'Параметры'!C33*20/60</f>
+        <v>223.58333333333337</v>
+      </c>
+      <c r="L10" s="38">
+        <f>('Параметры'!C26-L8-L9)/'Параметры'!C33*20/60</f>
+        <v>203.76388888888894</v>
+      </c>
+      <c r="M10" s="38">
+        <f>('Параметры'!C26-M8-M9)/'Параметры'!C33*20/60</f>
+        <v>207.8055555555556</v>
+      </c>
+      <c r="N10" s="38">
+        <f>('Параметры'!C26-N8-N9)/'Параметры'!C33*20/60</f>
+        <v>202.75000000000003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (авто) = (8760 − простои)/8760</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E11" s="39">
+        <f>('Параметры'!C26-E8-E9-E10)/'Параметры'!C26</f>
+        <v>0.9149543378995434</v>
+      </c>
+      <c r="F11" s="39">
+        <f>('Параметры'!C26-F8-F9-F10)/'Параметры'!C26</f>
+        <v>0.9104039827498731</v>
+      </c>
+      <c r="G11" s="39">
+        <f>('Параметры'!C26-G8-G9-G10)/'Параметры'!C26</f>
+        <v>0.8236142820903096</v>
+      </c>
+      <c r="H11" s="39">
+        <f>('Параметры'!C26-H8-H9-H10)/'Параметры'!C26</f>
+        <v>0.9095716007102994</v>
+      </c>
+      <c r="I11" s="39">
+        <f>('Параметры'!C26-I8-I9-I10)/'Параметры'!C26</f>
+        <v>0.9044108320649418</v>
+      </c>
+      <c r="J11" s="39">
+        <f>('Параметры'!C26-J8-J9-J10)/'Параметры'!C26</f>
+        <v>0.8074105783866059</v>
+      </c>
+      <c r="K11" s="39">
+        <f>('Параметры'!C26-K8-K9-K10)/'Параметры'!C26</f>
+        <v>0.8933124048706241</v>
+      </c>
+      <c r="L11" s="39">
+        <f>('Параметры'!C26-L8-L9-L10)/'Параметры'!C26</f>
+        <v>0.814125126839168</v>
+      </c>
+      <c r="M11" s="39">
+        <f>('Параметры'!C26-M8-M9-M10)/'Параметры'!C26</f>
+        <v>0.8302733384069001</v>
+      </c>
+      <c r="N11" s="39">
+        <f>('Параметры'!C26-N8-N9-N10)/'Параметры'!C26</f>
+        <v>0.8100742009132421</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>ТО (запчасти + смазочные)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="F12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="G12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="H12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="I12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="J12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="K12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="L12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="M12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+      <c r="N12" s="38">
+        <f>$E$28</f>
+        <v>107.51971999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>Текущие ремонты</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E13" s="38">
+        <f>E33</f>
+        <v>140.13</v>
+      </c>
+      <c r="F13" s="38">
+        <f>F33</f>
+        <v>140.13</v>
+      </c>
+      <c r="G13" s="38">
+        <f>G33</f>
+        <v>140.13</v>
+      </c>
+      <c r="H13" s="38">
+        <f>H33</f>
+        <v>140.13</v>
+      </c>
+      <c r="I13" s="38">
+        <f>I33</f>
+        <v>140.13</v>
+      </c>
+      <c r="J13" s="38">
+        <f>J33</f>
+        <v>140.13</v>
+      </c>
+      <c r="K13" s="38">
+        <f>K33</f>
+        <v>140.13</v>
+      </c>
+      <c r="L13" s="38">
+        <f>L33</f>
+        <v>140.13</v>
+      </c>
+      <c r="M13" s="38">
+        <f>M33</f>
+        <v>140.13</v>
+      </c>
+      <c r="N13" s="38">
+        <f>N33</f>
+        <v>140.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>Капитальные ремонты (ППР)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E14" s="38">
+        <f>E34</f>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="38">
+        <f>F34</f>
+        <v>417.99</v>
+      </c>
+      <c r="G14" s="38">
+        <f>G34</f>
+        <v>1274.6</v>
+      </c>
+      <c r="H14" s="38">
+        <f>H34</f>
+        <v>420.98</v>
+      </c>
+      <c r="I14" s="38">
+        <f>I34</f>
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="38">
+        <f>J34</f>
+        <v>1692.59</v>
+      </c>
+      <c r="K14" s="38">
+        <f>K34</f>
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="38">
+        <f>L34</f>
+        <v>420.98</v>
+      </c>
+      <c r="M14" s="38">
+        <f>M34</f>
+        <v>1274.6</v>
+      </c>
+      <c r="N14" s="38">
+        <f>N34</f>
+        <v>417.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Сервис (ТО + ремонты)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E15" s="38">
+        <f>$E$30+E35</f>
+        <v>29.720999999999997</v>
+      </c>
+      <c r="F15" s="38">
+        <f>$E$30+F35</f>
+        <v>32.120999999999995</v>
+      </c>
+      <c r="G15" s="38">
+        <f>$E$30+G35</f>
+        <v>35.721</v>
+      </c>
+      <c r="H15" s="38">
+        <f>$E$30+H35</f>
+        <v>33.321</v>
+      </c>
+      <c r="I15" s="38">
+        <f>$E$30+I35</f>
+        <v>29.720999999999997</v>
+      </c>
+      <c r="J15" s="38">
+        <f>$E$30+J35</f>
+        <v>38.120999999999995</v>
+      </c>
+      <c r="K15" s="38">
+        <f>$E$30+K35</f>
+        <v>29.720999999999997</v>
+      </c>
+      <c r="L15" s="38">
+        <f>$E$30+L35</f>
+        <v>33.321</v>
+      </c>
+      <c r="M15" s="38">
+        <f>$E$30+M35</f>
+        <v>35.721</v>
+      </c>
+      <c r="N15" s="38">
+        <f>$E$30+N35</f>
+        <v>32.120999999999995</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>ИТОГО ТОиР (авто) → «Данные по годам»</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E16" s="38">
+        <f>E12+E13+E14+E15</f>
+        <v>277.37072</v>
+      </c>
+      <c r="F16" s="38">
+        <f>F12+F13+F14+F15</f>
+        <v>697.76072</v>
+      </c>
+      <c r="G16" s="38">
+        <f>G12+G13+G14+G15</f>
+        <v>1557.9707199999998</v>
+      </c>
+      <c r="H16" s="38">
+        <f>H12+H13+H14+H15</f>
+        <v>701.95072</v>
+      </c>
+      <c r="I16" s="38">
+        <f>I12+I13+I14+I15</f>
+        <v>277.37072</v>
+      </c>
+      <c r="J16" s="38">
+        <f>J12+J13+J14+J15</f>
+        <v>1978.3607200000001</v>
+      </c>
+      <c r="K16" s="38">
+        <f>K12+K13+K14+K15</f>
+        <v>277.37072</v>
+      </c>
+      <c r="L16" s="38">
+        <f>L12+L13+L14+L15</f>
+        <v>701.95072</v>
+      </c>
+      <c r="M16" s="38">
+        <f>M12+M13+M14+M15</f>
+        <v>1557.9707199999998</v>
+      </c>
+      <c r="N16" s="38">
+        <f>N12+N13+N14+N15</f>
+        <v>697.76072</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Удельный расход ДТ</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>кг/час</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="H17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="I17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="J17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="K17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="L17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="M17" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="N17" s="33" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Расходники на ковш</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>руб/м³</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N18" s="40" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>РАСЧЁТ ТО (по интервалам обслуживания)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Годовая наработка</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>м/час</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Вид ТО</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>интервал</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>длит.простоя</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>персонал</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>ТО/год</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>простой,ч</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>ч·час</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>ТО-1</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="n">
+        <v>500</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E22" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="42">
+        <f>$E$20/C22</f>
+        <v>14.0</v>
+      </c>
+      <c r="G22" s="42">
+        <f>F22*D22</f>
+        <v>142.79999999999998</v>
+      </c>
+      <c r="H22" s="42">
+        <f>G22*E22</f>
+        <v>285.59999999999997</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>ТО-2</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" s="41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E23" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="42">
+        <f>$E$20/C23</f>
+        <v>7.0</v>
+      </c>
+      <c r="G23" s="42">
+        <f>F23*D23</f>
+        <v>65.8</v>
+      </c>
+      <c r="H23" s="42">
+        <f>G23*E23</f>
+        <v>131.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>ТО-3</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D24" s="41" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="42">
+        <f>$E$20/C24</f>
+        <v>3.5</v>
+      </c>
+      <c r="G24" s="42">
+        <f>F24*D24</f>
+        <v>43.4</v>
+      </c>
+      <c r="H24" s="42">
+        <f>G24*E24</f>
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>ТО-4</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="42">
+        <f>$E$20/C25</f>
+        <v>1.75</v>
+      </c>
+      <c r="G25" s="42">
+        <f>F25*D25</f>
+        <v>13.65</v>
+      </c>
+      <c r="H25" s="42">
+        <f>G25*E25</f>
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>ТО-5</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="42">
+        <f>$E$20/C26</f>
+        <v>1.4</v>
+      </c>
+      <c r="G26" s="42">
+        <f>F26*D26</f>
+        <v>7.56</v>
+      </c>
+      <c r="H26" s="42">
+        <f>G26*E26</f>
+        <v>15.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Итого простои / ч·часы ТО</t>
+        </is>
+      </c>
+      <c r="G27" s="44">
+        <f>SUM(G22:G26)</f>
+        <v>273.21</v>
+      </c>
+      <c r="H27" s="44">
+        <f>SUM(H22:H26)</f>
+        <v>546.42</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>Затраты на запчасти ТО (из каталога)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E28" s="38">
+        <f>SUM(F39:F66)</f>
+        <v>107.51971999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Ставка сервиса</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>вал/ч·час</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ТО (авто) = ч·часы × ставка</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E30" s="38">
+        <f>$H$27*$E$29/1000</f>
+        <v>27.320999999999998</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>РАСЧЁТ РЕМОНТОВ (из списков по периодичности замены узлов)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Простои в ремонтах</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>ч/год</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>242.79</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>283.79</v>
+      </c>
+      <c r="G32" s="31" t="n">
+        <v>1065.79</v>
+      </c>
+      <c r="H32" s="31" t="n">
+        <v>291.29</v>
+      </c>
+      <c r="I32" s="31" t="n">
+        <v>337.79</v>
+      </c>
+      <c r="J32" s="31" t="n">
+        <v>1211.79</v>
+      </c>
+      <c r="K32" s="31" t="n">
+        <v>437.79</v>
+      </c>
+      <c r="L32" s="31" t="n">
+        <v>1151.29</v>
+      </c>
+      <c r="M32" s="31" t="n">
+        <v>1005.79</v>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>1187.79</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>Текущие ремонты (из списка)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E33" s="38">
+        <f>SUM(E70:E71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="F33" s="38">
+        <f>SUM(F70:F71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="G33" s="38">
+        <f>SUM(G70:G71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="H33" s="38">
+        <f>SUM(H70:H71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="I33" s="38">
+        <f>SUM(I70:I71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="J33" s="38">
+        <f>SUM(J70:J71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="K33" s="38">
+        <f>SUM(K70:K71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="L33" s="38">
+        <f>SUM(L70:L71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="M33" s="38">
+        <f>SUM(M70:M71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+      <c r="N33" s="38">
+        <f>SUM(N70:N71)*$E$36</f>
+        <v>140.13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>Капитальные ремонты ППР (из списка)</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E34" s="38">
+        <f>SUM(E75:E82)*$E$36</f>
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="38">
+        <f>SUM(F75:F82)*$E$36</f>
+        <v>417.99</v>
+      </c>
+      <c r="G34" s="38">
+        <f>SUM(G75:G82)*$E$36</f>
+        <v>1274.6</v>
+      </c>
+      <c r="H34" s="38">
+        <f>SUM(H75:H82)*$E$36</f>
+        <v>420.98</v>
+      </c>
+      <c r="I34" s="38">
+        <f>SUM(I75:I82)*$E$36</f>
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="38">
+        <f>SUM(J75:J82)*$E$36</f>
+        <v>1692.59</v>
+      </c>
+      <c r="K34" s="38">
+        <f>SUM(K75:K82)*$E$36</f>
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="38">
+        <f>SUM(L75:L82)*$E$36</f>
+        <v>420.98</v>
+      </c>
+      <c r="M34" s="38">
+        <f>SUM(M75:M82)*$E$36</f>
+        <v>1274.6</v>
+      </c>
+      <c r="N34" s="38">
+        <f>SUM(N75:N82)*$E$36</f>
+        <v>417.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Сервис ремонтов (трудозатраты, авто)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>тыс/год</t>
+        </is>
+      </c>
+      <c r="E35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(E75:E82&gt;0)*1),0))*$E$29/1000</f>
+        <v>2.4</v>
+      </c>
+      <c r="F35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(F75:F82&gt;0)*1),0))*$E$29/1000</f>
+        <v>4.8</v>
+      </c>
+      <c r="G35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(G75:G82&gt;0)*1),0))*$E$29/1000</f>
+        <v>8.4</v>
+      </c>
+      <c r="H35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(H75:H82&gt;0)*1),0))*$E$29/1000</f>
+        <v>6.0</v>
+      </c>
+      <c r="I35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(I75:I82&gt;0)*1),0))*$E$29/1000</f>
+        <v>2.4</v>
+      </c>
+      <c r="J35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(J75:J82&gt;0)*1),0))*$E$29/1000</f>
+        <v>10.8</v>
+      </c>
+      <c r="K35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(K75:K82&gt;0)*1),0))*$E$29/1000</f>
+        <v>2.4</v>
+      </c>
+      <c r="L35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(L75:L82&gt;0)*1),0))*$E$29/1000</f>
+        <v>6.0</v>
+      </c>
+      <c r="M35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(M75:M82&gt;0)*1),0))*$E$29/1000</f>
+        <v>8.4</v>
+      </c>
+      <c r="N35" s="38">
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$82,(N75:N82&gt;0)*1),0))*$E$29/1000</f>
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Коэффициент поглощения (0–1; 1=как у поставщика)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>КАТАЛОГ ЗАПЧАСТЕЙ ТО (заполняет подрядчик)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>цена за ед</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>кол-во/ТО</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>№ ТО</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>стоимость,тыс/год</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Масляный фильтр</t>
+        </is>
+      </c>
+      <c r="C39" s="45" t="n">
+        <v>114.83</v>
+      </c>
+      <c r="D39" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E39))*D39*C39/1000</f>
+        <v>6.430479999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Топливный фильтр</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="n">
+        <v>141.33</v>
+      </c>
+      <c r="D40" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E40))*D40*C40/1000</f>
+        <v>3.95724</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Масло ДВС</t>
+        </is>
+      </c>
+      <c r="C41" s="45" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="D41" s="45" t="n">
+        <v>130</v>
+      </c>
+      <c r="E41" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E41))*D41*C41/1000</f>
+        <v>12.5034</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр управляющего контура</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="n">
+        <v>126</v>
+      </c>
+      <c r="D42" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E42))*D42*C42/1000</f>
+        <v>1.764</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Сливной фильтр</t>
+        </is>
+      </c>
+      <c r="C43" s="45" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="D43" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E43))*D43*C43/1000</f>
+        <v>0.85876</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Сливной фильтр насоса</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="n">
+        <v>201</v>
+      </c>
+      <c r="D44" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E44))*D44*C44/1000</f>
+        <v>8.442</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Смазка</t>
+        </is>
+      </c>
+      <c r="C45" s="45" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="D45" s="45" t="n">
+        <v>200</v>
+      </c>
+      <c r="E45" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E45))*D45*C45/1000</f>
+        <v>34.272</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Топливный фильтр (ТО-2)</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="D46" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E46))*D46*C46/1000</f>
+        <v>1.1223800000000002</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр сапуна топл.бака</t>
+        </is>
+      </c>
+      <c r="C47" s="45" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="D47" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E47))*D47*C47/1000</f>
+        <v>0.13419</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр сапуна гидробака</t>
+        </is>
+      </c>
+      <c r="C48" s="45" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="D48" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E48))*D48*C48/1000</f>
+        <v>0.26838</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>Гидравлический фильтр</t>
+        </is>
+      </c>
+      <c r="C49" s="45" t="n">
+        <v>344.33</v>
+      </c>
+      <c r="D49" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E49))*D49*C49/1000</f>
+        <v>7.230929999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>О-кольцо</t>
+        </is>
+      </c>
+      <c r="C50" s="45" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D50" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E50))*D50*C50/1000</f>
+        <v>0.5145</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Воздушный фильтр</t>
+        </is>
+      </c>
+      <c r="C51" s="45" t="n">
+        <v>401.33</v>
+      </c>
+      <c r="D51" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E51))*D51*C51/1000</f>
+        <v>5.61862</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>О-кольцо (2)</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="D52" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E52))*D52*C52/1000</f>
+        <v>0.13762</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>Масло редуктора поворота</t>
+        </is>
+      </c>
+      <c r="C53" s="45" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D53" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="E53" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E53))*D53*C53/1000</f>
+        <v>2.8937999999999997</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Масло механизма отбора мощн.</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D54" s="45" t="n">
+        <v>36</v>
+      </c>
+      <c r="E54" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E54))*D54*C54/1000</f>
+        <v>1.73628</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр гидромотора поворота</t>
+        </is>
+      </c>
+      <c r="C55" s="45" t="n">
+        <v>102</v>
+      </c>
+      <c r="D55" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E55))*D55*C55/1000</f>
+        <v>1.428</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>Прокладка клапанной крышки</t>
+        </is>
+      </c>
+      <c r="C56" s="45" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="D56" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="E56" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E56))*D56*C56/1000</f>
+        <v>0.17514</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр салонный кондиц.</t>
+        </is>
+      </c>
+      <c r="C57" s="45" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="D57" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E57))*D57*C57/1000</f>
+        <v>0.07581</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр наружный кондиц.</t>
+        </is>
+      </c>
+      <c r="C58" s="45" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="D58" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E58))*D58*C58/1000</f>
+        <v>0.35931</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>Масло конечной передачи</t>
+        </is>
+      </c>
+      <c r="C59" s="45" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D59" s="45" t="n">
+        <v>170</v>
+      </c>
+      <c r="E59" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E59))*D59*C59/1000</f>
+        <v>4.09955</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Фильтр охлажд. жидкости</t>
+        </is>
+      </c>
+      <c r="C60" s="45" t="n">
+        <v>134.83</v>
+      </c>
+      <c r="D60" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E60))*D60*C60/1000</f>
+        <v>0.471905</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>Ремень генератора</t>
+        </is>
+      </c>
+      <c r="C61" s="45" t="n">
+        <v>28</v>
+      </c>
+      <c r="D61" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E61))*D61*C61/1000</f>
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Ремень генератора (2)</t>
+        </is>
+      </c>
+      <c r="C62" s="45" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="D62" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E62))*D62*C62/1000</f>
+        <v>0.275625</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Ремень кондиционера</t>
+        </is>
+      </c>
+      <c r="C63" s="45" t="n">
+        <v>61</v>
+      </c>
+      <c r="D63" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E63))*D63*C63/1000</f>
+        <v>0.2135</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Охлаждающая жидкость</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D64" s="45" t="n">
+        <v>190</v>
+      </c>
+      <c r="E64" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E64))*D64*C64/1000</f>
+        <v>0.7847</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Гидравлическое масло</t>
+        </is>
+      </c>
+      <c r="C65" s="45" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="D65" s="45" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E65" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="46">
+        <f>($E$20/INDEX($C$22:$C$26,E65))*D65*C65/1000</f>
+        <v>11.702599999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Корректировка (поглощения/прочее)</t>
+        </is>
+      </c>
+      <c r="F66" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>ТЕКУЩИЕ РЕМОНТЫ — по ресурсу замены (затрата в годы кратные ресурсу)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Узел / вид ремонта</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>стоим.замены,тыс</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>ресурс, м/ч</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>год 1</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>год 2</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr">
+        <is>
+          <t>год 3</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>год 4</t>
+        </is>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>год 5</t>
+        </is>
+      </c>
+      <c r="J69" s="15" t="inlineStr">
+        <is>
+          <t>год 6</t>
+        </is>
+      </c>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>год 7</t>
+        </is>
+      </c>
+      <c r="L69" s="15" t="inlineStr">
+        <is>
+          <t>год 8</t>
+        </is>
+      </c>
+      <c r="M69" s="15" t="inlineStr">
+        <is>
+          <t>год 9</t>
+        </is>
+      </c>
+      <c r="N69" s="15" t="inlineStr">
+        <is>
+          <t>год 10</t>
+        </is>
+      </c>
+      <c r="P69" s="15" t="inlineStr">
+        <is>
+          <t>нормо-час</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>Гидроцилиндры (ремкомплекты)</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="D70" s="47" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E70" s="46">
+        <f>(INT($E$20*1/$D70)-INT($E$20*(1-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="F70" s="46">
+        <f>(INT($E$20*2/$D70)-INT($E$20*(2-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="G70" s="46">
+        <f>(INT($E$20*3/$D70)-INT($E$20*(3-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="H70" s="46">
+        <f>(INT($E$20*4/$D70)-INT($E$20*(4-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="I70" s="46">
+        <f>(INT($E$20*5/$D70)-INT($E$20*(5-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="J70" s="46">
+        <f>(INT($E$20*6/$D70)-INT($E$20*(6-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="K70" s="46">
+        <f>(INT($E$20*7/$D70)-INT($E$20*(7-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="L70" s="46">
+        <f>(INT($E$20*8/$D70)-INT($E$20*(8-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="M70" s="46">
+        <f>(INT($E$20*9/$D70)-INT($E$20*(9-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="N70" s="46">
+        <f>(INT($E$20*10/$D70)-INT($E$20*(10-1)/$D70))*$C70</f>
+        <v>21.06</v>
+      </c>
+      <c r="P70" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Ковш (коронки, адаптеры, защиты)</t>
+        </is>
+      </c>
+      <c r="C71" s="45" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="D71" s="47" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E71" s="46">
+        <f>(INT($E$20*1/$D71)-INT($E$20*(1-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="F71" s="46">
+        <f>(INT($E$20*2/$D71)-INT($E$20*(2-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="G71" s="46">
+        <f>(INT($E$20*3/$D71)-INT($E$20*(3-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="H71" s="46">
+        <f>(INT($E$20*4/$D71)-INT($E$20*(4-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="I71" s="46">
+        <f>(INT($E$20*5/$D71)-INT($E$20*(5-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="J71" s="46">
+        <f>(INT($E$20*6/$D71)-INT($E$20*(6-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="K71" s="46">
+        <f>(INT($E$20*7/$D71)-INT($E$20*(7-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="L71" s="46">
+        <f>(INT($E$20*8/$D71)-INT($E$20*(8-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="M71" s="46">
+        <f>(INT($E$20*9/$D71)-INT($E$20*(9-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="N71" s="46">
+        <f>(INT($E$20*10/$D71)-INT($E$20*(10-1)/$D71))*$C71</f>
+        <v>119.07</v>
+      </c>
+      <c r="P71" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>КАПИТАЛЬНЫЕ РЕМОНТЫ (ППР) — по ресурсу до замены узла (данные поставщика)</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Узел / вид ремонта</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>стоим.замены,тыс</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>ресурс, м/ч</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>год 1</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>год 2</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>год 3</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>год 4</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>год 5</t>
+        </is>
+      </c>
+      <c r="J74" s="15" t="inlineStr">
+        <is>
+          <t>год 6</t>
+        </is>
+      </c>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>год 7</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>год 8</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>год 9</t>
+        </is>
+      </c>
+      <c r="N74" s="15" t="inlineStr">
+        <is>
+          <t>год 10</t>
+        </is>
+      </c>
+      <c r="P74" s="15" t="inlineStr">
+        <is>
+          <t>нормо-час</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Рабочее оборудование (пальцы/втулки)</t>
+        </is>
+      </c>
+      <c r="C75" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" s="47" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E75" s="46">
+        <f>(INT($E$20*1/$D75)-INT($E$20*(1-1)/$D75))*$C75</f>
+        <v>0.0</v>
+      </c>
+      <c r="F75" s="46">
+        <f>(INT($E$20*2/$D75)-INT($E$20*(2-1)/$D75))*$C75</f>
+        <v>12.0</v>
+      </c>
+      <c r="G75" s="46">
+        <f>(INT($E$20*3/$D75)-INT($E$20*(3-1)/$D75))*$C75</f>
+        <v>0.0</v>
+      </c>
+      <c r="H75" s="46">
+        <f>(INT($E$20*4/$D75)-INT($E$20*(4-1)/$D75))*$C75</f>
+        <v>12.0</v>
+      </c>
+      <c r="I75" s="46">
+        <f>(INT($E$20*5/$D75)-INT($E$20*(5-1)/$D75))*$C75</f>
+        <v>0.0</v>
+      </c>
+      <c r="J75" s="46">
+        <f>(INT($E$20*6/$D75)-INT($E$20*(6-1)/$D75))*$C75</f>
+        <v>12.0</v>
+      </c>
+      <c r="K75" s="46">
+        <f>(INT($E$20*7/$D75)-INT($E$20*(7-1)/$D75))*$C75</f>
+        <v>0.0</v>
+      </c>
+      <c r="L75" s="46">
+        <f>(INT($E$20*8/$D75)-INT($E$20*(8-1)/$D75))*$C75</f>
+        <v>12.0</v>
+      </c>
+      <c r="M75" s="46">
+        <f>(INT($E$20*9/$D75)-INT($E$20*(9-1)/$D75))*$C75</f>
+        <v>0.0</v>
+      </c>
+      <c r="N75" s="46">
+        <f>(INT($E$20*10/$D75)-INT($E$20*(10-1)/$D75))*$C75</f>
+        <v>12.0</v>
+      </c>
+      <c r="P75" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>Ходовая часть</t>
+        </is>
+      </c>
+      <c r="C76" s="45" t="n">
+        <v>405.99</v>
+      </c>
+      <c r="D76" s="47" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E76" s="46">
+        <f>(INT($E$20*1/$D76)-INT($E$20*(1-1)/$D76))*$C76</f>
+        <v>0.0</v>
+      </c>
+      <c r="F76" s="46">
+        <f>(INT($E$20*2/$D76)-INT($E$20*(2-1)/$D76))*$C76</f>
+        <v>405.99</v>
+      </c>
+      <c r="G76" s="46">
+        <f>(INT($E$20*3/$D76)-INT($E$20*(3-1)/$D76))*$C76</f>
+        <v>0.0</v>
+      </c>
+      <c r="H76" s="46">
+        <f>(INT($E$20*4/$D76)-INT($E$20*(4-1)/$D76))*$C76</f>
+        <v>405.99</v>
+      </c>
+      <c r="I76" s="46">
+        <f>(INT($E$20*5/$D76)-INT($E$20*(5-1)/$D76))*$C76</f>
+        <v>0.0</v>
+      </c>
+      <c r="J76" s="46">
+        <f>(INT($E$20*6/$D76)-INT($E$20*(6-1)/$D76))*$C76</f>
+        <v>405.99</v>
+      </c>
+      <c r="K76" s="46">
+        <f>(INT($E$20*7/$D76)-INT($E$20*(7-1)/$D76))*$C76</f>
+        <v>0.0</v>
+      </c>
+      <c r="L76" s="46">
+        <f>(INT($E$20*8/$D76)-INT($E$20*(8-1)/$D76))*$C76</f>
+        <v>405.99</v>
+      </c>
+      <c r="M76" s="46">
+        <f>(INT($E$20*9/$D76)-INT($E$20*(9-1)/$D76))*$C76</f>
+        <v>0.0</v>
+      </c>
+      <c r="N76" s="46">
+        <f>(INT($E$20*10/$D76)-INT($E$20*(10-1)/$D76))*$C76</f>
+        <v>405.99</v>
+      </c>
+      <c r="P76" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>Гидросистема (капремонт)</t>
+        </is>
+      </c>
+      <c r="C77" s="45" t="n">
+        <v>834.88</v>
+      </c>
+      <c r="D77" s="47" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E77" s="46">
+        <f>(INT($E$20*1/$D77)-INT($E$20*(1-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="F77" s="46">
+        <f>(INT($E$20*2/$D77)-INT($E$20*(2-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="G77" s="46">
+        <f>(INT($E$20*3/$D77)-INT($E$20*(3-1)/$D77))*$C77</f>
+        <v>834.88</v>
+      </c>
+      <c r="H77" s="46">
+        <f>(INT($E$20*4/$D77)-INT($E$20*(4-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="I77" s="46">
+        <f>(INT($E$20*5/$D77)-INT($E$20*(5-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="J77" s="46">
+        <f>(INT($E$20*6/$D77)-INT($E$20*(6-1)/$D77))*$C77</f>
+        <v>834.88</v>
+      </c>
+      <c r="K77" s="46">
+        <f>(INT($E$20*7/$D77)-INT($E$20*(7-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="L77" s="46">
+        <f>(INT($E$20*8/$D77)-INT($E$20*(8-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="M77" s="46">
+        <f>(INT($E$20*9/$D77)-INT($E$20*(9-1)/$D77))*$C77</f>
+        <v>834.88</v>
+      </c>
+      <c r="N77" s="46">
+        <f>(INT($E$20*10/$D77)-INT($E$20*(10-1)/$D77))*$C77</f>
+        <v>0.0</v>
+      </c>
+      <c r="P77" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Капремонт ДВС</t>
+        </is>
+      </c>
+      <c r="C78" s="45" t="n">
+        <v>246.94</v>
+      </c>
+      <c r="D78" s="47" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E78" s="46">
+        <f>(INT($E$20*1/$D78)-INT($E$20*(1-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="F78" s="46">
+        <f>(INT($E$20*2/$D78)-INT($E$20*(2-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="G78" s="46">
+        <f>(INT($E$20*3/$D78)-INT($E$20*(3-1)/$D78))*$C78</f>
+        <v>246.94</v>
+      </c>
+      <c r="H78" s="46">
+        <f>(INT($E$20*4/$D78)-INT($E$20*(4-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="I78" s="46">
+        <f>(INT($E$20*5/$D78)-INT($E$20*(5-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="J78" s="46">
+        <f>(INT($E$20*6/$D78)-INT($E$20*(6-1)/$D78))*$C78</f>
+        <v>246.94</v>
+      </c>
+      <c r="K78" s="46">
+        <f>(INT($E$20*7/$D78)-INT($E$20*(7-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="L78" s="46">
+        <f>(INT($E$20*8/$D78)-INT($E$20*(8-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="M78" s="46">
+        <f>(INT($E$20*9/$D78)-INT($E$20*(9-1)/$D78))*$C78</f>
+        <v>246.94</v>
+      </c>
+      <c r="N78" s="46">
+        <f>(INT($E$20*10/$D78)-INT($E$20*(10-1)/$D78))*$C78</f>
+        <v>0.0</v>
+      </c>
+      <c r="P78" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>Рабочее оборудование (капремонт)</t>
+        </is>
+      </c>
+      <c r="C79" s="45" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="D79" s="47" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E79" s="46">
+        <f>(INT($E$20*1/$D79)-INT($E$20*(1-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="F79" s="46">
+        <f>(INT($E$20*2/$D79)-INT($E$20*(2-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="G79" s="46">
+        <f>(INT($E$20*3/$D79)-INT($E$20*(3-1)/$D79))*$C79</f>
+        <v>92.68</v>
+      </c>
+      <c r="H79" s="46">
+        <f>(INT($E$20*4/$D79)-INT($E$20*(4-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="I79" s="46">
+        <f>(INT($E$20*5/$D79)-INT($E$20*(5-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="J79" s="46">
+        <f>(INT($E$20*6/$D79)-INT($E$20*(6-1)/$D79))*$C79</f>
+        <v>92.68</v>
+      </c>
+      <c r="K79" s="46">
+        <f>(INT($E$20*7/$D79)-INT($E$20*(7-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="L79" s="46">
+        <f>(INT($E$20*8/$D79)-INT($E$20*(8-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="M79" s="46">
+        <f>(INT($E$20*9/$D79)-INT($E$20*(9-1)/$D79))*$C79</f>
+        <v>92.68</v>
+      </c>
+      <c r="N79" s="46">
+        <f>(INT($E$20*10/$D79)-INT($E$20*(10-1)/$D79))*$C79</f>
+        <v>0.0</v>
+      </c>
+      <c r="P79" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Централизованная смазка</t>
+        </is>
+      </c>
+      <c r="C80" s="45" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="D80" s="47" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E80" s="46">
+        <f>(INT($E$20*1/$D80)-INT($E$20*(1-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="F80" s="46">
+        <f>(INT($E$20*2/$D80)-INT($E$20*(2-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="G80" s="46">
+        <f>(INT($E$20*3/$D80)-INT($E$20*(3-1)/$D80))*$C80</f>
+        <v>98.23</v>
+      </c>
+      <c r="H80" s="46">
+        <f>(INT($E$20*4/$D80)-INT($E$20*(4-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="I80" s="46">
+        <f>(INT($E$20*5/$D80)-INT($E$20*(5-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="J80" s="46">
+        <f>(INT($E$20*6/$D80)-INT($E$20*(6-1)/$D80))*$C80</f>
+        <v>98.23</v>
+      </c>
+      <c r="K80" s="46">
+        <f>(INT($E$20*7/$D80)-INT($E$20*(7-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="L80" s="46">
+        <f>(INT($E$20*8/$D80)-INT($E$20*(8-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="M80" s="46">
+        <f>(INT($E$20*9/$D80)-INT($E$20*(9-1)/$D80))*$C80</f>
+        <v>98.23</v>
+      </c>
+      <c r="N80" s="46">
+        <f>(INT($E$20*10/$D80)-INT($E$20*(10-1)/$D80))*$C80</f>
+        <v>0.0</v>
+      </c>
+      <c r="P80" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Датчики электрика</t>
+        </is>
+      </c>
+      <c r="C81" s="45" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D81" s="47" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E81" s="46">
+        <f>(INT($E$20*1/$D81)-INT($E$20*(1-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="F81" s="46">
+        <f>(INT($E$20*2/$D81)-INT($E$20*(2-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="G81" s="46">
+        <f>(INT($E$20*3/$D81)-INT($E$20*(3-1)/$D81))*$C81</f>
+        <v>1.87</v>
+      </c>
+      <c r="H81" s="46">
+        <f>(INT($E$20*4/$D81)-INT($E$20*(4-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="I81" s="46">
+        <f>(INT($E$20*5/$D81)-INT($E$20*(5-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="J81" s="46">
+        <f>(INT($E$20*6/$D81)-INT($E$20*(6-1)/$D81))*$C81</f>
+        <v>1.87</v>
+      </c>
+      <c r="K81" s="46">
+        <f>(INT($E$20*7/$D81)-INT($E$20*(7-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="L81" s="46">
+        <f>(INT($E$20*8/$D81)-INT($E$20*(8-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="M81" s="46">
+        <f>(INT($E$20*9/$D81)-INT($E$20*(9-1)/$D81))*$C81</f>
+        <v>1.87</v>
+      </c>
+      <c r="N81" s="46">
+        <f>(INT($E$20*10/$D81)-INT($E$20*(10-1)/$D81))*$C81</f>
+        <v>0.0</v>
+      </c>
+      <c r="P81" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>Электронный блок</t>
+        </is>
+      </c>
+      <c r="C82" s="45" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D82" s="47" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E82" s="46">
+        <f>(INT($E$20*1/$D82)-INT($E$20*(1-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="F82" s="46">
+        <f>(INT($E$20*2/$D82)-INT($E$20*(2-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="G82" s="46">
+        <f>(INT($E$20*3/$D82)-INT($E$20*(3-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="H82" s="46">
+        <f>(INT($E$20*4/$D82)-INT($E$20*(4-1)/$D82))*$C82</f>
+        <v>2.99</v>
+      </c>
+      <c r="I82" s="46">
+        <f>(INT($E$20*5/$D82)-INT($E$20*(5-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="J82" s="46">
+        <f>(INT($E$20*6/$D82)-INT($E$20*(6-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="K82" s="46">
+        <f>(INT($E$20*7/$D82)-INT($E$20*(7-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="L82" s="46">
+        <f>(INT($E$20*8/$D82)-INT($E$20*(8-1)/$D82))*$C82</f>
+        <v>2.99</v>
+      </c>
+      <c r="M82" s="46">
+        <f>(INT($E$20*9/$D82)-INT($E$20*(9-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="N82" s="46">
+        <f>(INT($E$20*10/$D82)-INT($E$20*(10-1)/$D82))*$C82</f>
+        <v>0.0</v>
+      </c>
+      <c r="P82" s="47" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="48" t="inlineStr">
+        <is>
+          <t>Капремонты считаются ПО ПЕРИОДИЧНОСТИ, как у поставщиков: для каждого узла заданы стоимость замены и ресурс (м/ч); затрата возникает в те годы, когда наработка пересекает кратное ресурсу значение (число замен = ЦЕЛОЕ(наработка×год/ресурс) − ЦЕЛОЕ(наработка×(год−1)/ресурс)). Трудозатраты — нормо-часы × ставку. «Коэффициент поглощения» &lt; 1 учитывает восстановление/поглощение узлов (у поставщика = 1).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B37:N37"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="E4:N4"/>
+    <mergeCell ref="B73:N73"/>
+    <mergeCell ref="B19:N19"/>
+    <mergeCell ref="B68:N68"/>
+    <mergeCell ref="B84:P84"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="B2:N2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"CNY,USD,EUR,RUB"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6449,9 +9076,241 @@
         <v>0.87</v>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" s="5" t="str">
+        <f>"Вариант 7:  "&amp;'Ввод данных'!J7</f>
+        <v>Вариант 7:  XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>КТГ (техготовность)</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E37" s="50">
+        <f>'Поставщик 7'!E11</f>
+        <v>0.9149543378995434</v>
+      </c>
+      <c r="F37" s="50">
+        <f>'Поставщик 7'!F11</f>
+        <v>0.9104039827498731</v>
+      </c>
+      <c r="G37" s="50">
+        <f>'Поставщик 7'!G11</f>
+        <v>0.8236142820903096</v>
+      </c>
+      <c r="H37" s="50">
+        <f>'Поставщик 7'!H11</f>
+        <v>0.9095716007102994</v>
+      </c>
+      <c r="I37" s="50">
+        <f>'Поставщик 7'!I11</f>
+        <v>0.9044108320649418</v>
+      </c>
+      <c r="J37" s="50">
+        <f>'Поставщик 7'!J11</f>
+        <v>0.8074105783866059</v>
+      </c>
+      <c r="K37" s="50">
+        <f>'Поставщик 7'!K11</f>
+        <v>0.8933124048706241</v>
+      </c>
+      <c r="L37" s="50">
+        <f>'Поставщик 7'!L11</f>
+        <v>0.814125126839168</v>
+      </c>
+      <c r="M37" s="50">
+        <f>'Поставщик 7'!M11</f>
+        <v>0.8302733384069001</v>
+      </c>
+      <c r="N37" s="50">
+        <f>'Поставщик 7'!N11</f>
+        <v>0.8100742009132421</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Затраты на ТОиР и сервис</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>тыс.вал/г</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="str">
+        <f>'Поставщик 7'!$D$5</f>
+        <v>USD</v>
+      </c>
+      <c r="E38" s="52">
+        <f>'Поставщик 7'!E16</f>
+        <v>277.37072</v>
+      </c>
+      <c r="F38" s="52">
+        <f>'Поставщик 7'!F16</f>
+        <v>697.76072</v>
+      </c>
+      <c r="G38" s="52">
+        <f>'Поставщик 7'!G16</f>
+        <v>1557.9707199999998</v>
+      </c>
+      <c r="H38" s="52">
+        <f>'Поставщик 7'!H16</f>
+        <v>701.95072</v>
+      </c>
+      <c r="I38" s="52">
+        <f>'Поставщик 7'!I16</f>
+        <v>277.37072</v>
+      </c>
+      <c r="J38" s="52">
+        <f>'Поставщик 7'!J16</f>
+        <v>1978.3607200000001</v>
+      </c>
+      <c r="K38" s="52">
+        <f>'Поставщик 7'!K16</f>
+        <v>277.37072</v>
+      </c>
+      <c r="L38" s="52">
+        <f>'Поставщик 7'!L16</f>
+        <v>701.95072</v>
+      </c>
+      <c r="M38" s="52">
+        <f>'Поставщик 7'!M16</f>
+        <v>1557.9707199999998</v>
+      </c>
+      <c r="N38" s="52">
+        <f>'Поставщик 7'!N16</f>
+        <v>697.76072</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Удельный расход ДТ</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>кг/час</t>
+        </is>
+      </c>
+      <c r="E39" s="53">
+        <f>'Поставщик 7'!E17</f>
+        <v>105.0</v>
+      </c>
+      <c r="F39" s="53">
+        <f>'Поставщик 7'!F17</f>
+        <v>105.0</v>
+      </c>
+      <c r="G39" s="53">
+        <f>'Поставщик 7'!G17</f>
+        <v>105.0</v>
+      </c>
+      <c r="H39" s="53">
+        <f>'Поставщик 7'!H17</f>
+        <v>105.0</v>
+      </c>
+      <c r="I39" s="53">
+        <f>'Поставщик 7'!I17</f>
+        <v>105.0</v>
+      </c>
+      <c r="J39" s="53">
+        <f>'Поставщик 7'!J17</f>
+        <v>105.0</v>
+      </c>
+      <c r="K39" s="53">
+        <f>'Поставщик 7'!K17</f>
+        <v>105.0</v>
+      </c>
+      <c r="L39" s="53">
+        <f>'Поставщик 7'!L17</f>
+        <v>105.0</v>
+      </c>
+      <c r="M39" s="53">
+        <f>'Поставщик 7'!M17</f>
+        <v>105.0</v>
+      </c>
+      <c r="N39" s="53">
+        <f>'Поставщик 7'!N17</f>
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Расходники на ковш</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>руб/м³</t>
+        </is>
+      </c>
+      <c r="E40" s="54">
+        <f>'Поставщик 7'!E18</f>
+        <v>0.87</v>
+      </c>
+      <c r="F40" s="54">
+        <f>'Поставщик 7'!F18</f>
+        <v>0.87</v>
+      </c>
+      <c r="G40" s="54">
+        <f>'Поставщик 7'!G18</f>
+        <v>0.87</v>
+      </c>
+      <c r="H40" s="54">
+        <f>'Поставщик 7'!H18</f>
+        <v>0.87</v>
+      </c>
+      <c r="I40" s="54">
+        <f>'Поставщик 7'!I18</f>
+        <v>0.87</v>
+      </c>
+      <c r="J40" s="54">
+        <f>'Поставщик 7'!J18</f>
+        <v>0.87</v>
+      </c>
+      <c r="K40" s="54">
+        <f>'Поставщик 7'!K18</f>
+        <v>0.87</v>
+      </c>
+      <c r="L40" s="54">
+        <f>'Поставщик 7'!L18</f>
+        <v>0.87</v>
+      </c>
+      <c r="M40" s="54">
+        <f>'Поставщик 7'!M18</f>
+        <v>0.87</v>
+      </c>
+      <c r="N40" s="54">
+        <f>'Поставщик 7'!N18</f>
+        <v>0.87</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B16:N16"/>
+    <mergeCell ref="B36:N36"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B1:N1"/>
     <mergeCell ref="B4:N4"/>
@@ -6465,13 +9324,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K14"/>
+  <dimension ref="B1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6483,12 +9342,17 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>РАСЧЁТ ПРОИЗВОДИТЕЛЬНОСТИ (1-й год)</t>
+          <t>РАСЧЁТ ПРОИЗВОДИТЕЛЬНОСТИ</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -6500,11 +9364,14 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Часовая и годовая производительность. По годам — на листе «Денежный поток».</t>
+          <t>Часовая производительность (геометрия ковша/цикла — неизменна по годам) и полная погодовая таблица по каждой машине (КТГ по годам из «Данные по годам»).</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -6516,6 +9383,9 @@
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="15" t="inlineStr">
@@ -6557,6 +9427,11 @@
         <v>TZCO TZ2000
 Дзикай</v>
       </c>
+      <c r="J4" s="15" t="str">
+        <f>'Ввод данных'!J7</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="55" t="inlineStr">
@@ -6593,6 +9468,10 @@
         <f>'Ввод данных'!I11*IF('Ввод данных'!I12="CNY",'Параметры'!C20,IF('Ввод данных'!I12="USD",'Параметры'!C21,IF('Ввод данных'!I12="EUR",'Параметры'!C22,1)))+'Ввод данных'!I13</f>
         <v>172584.72</v>
       </c>
+      <c r="J5" s="56">
+        <f>'Ввод данных'!J11*IF('Ввод данных'!J12="CNY",'Параметры'!C20,IF('Ввод данных'!J12="USD",'Параметры'!C21,IF('Ввод данных'!J12="EUR",'Параметры'!C22,1)))+'Ввод данных'!J13</f>
+        <v>201722.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="22" t="inlineStr">
@@ -6629,6 +9508,10 @@
         <f>'Ввод данных'!I16*'Параметры'!C27*('Параметры'!C29/'Параметры'!C28)*'Параметры'!C30</f>
         <v>18.05976</v>
       </c>
+      <c r="J6" s="57">
+        <f>'Ввод данных'!J16*'Параметры'!C27*('Параметры'!C29/'Параметры'!C28)*'Параметры'!C30</f>
+        <v>18.05976</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
@@ -6665,6 +9548,10 @@
         <f>ROUNDUP('Параметры'!C31/I6,0)</f>
         <v>8.0</v>
       </c>
+      <c r="J7" s="56">
+        <f>ROUNDUP('Параметры'!C31/J6,0)</f>
+        <v>8.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
@@ -6701,6 +9588,10 @@
         <f>3600/(I7*'Ввод данных'!I17+'Параметры'!C32)</f>
         <v>10.89588377723971</v>
       </c>
+      <c r="J8" s="57">
+        <f>3600/(J7*'Ввод данных'!J17+'Параметры'!C32)</f>
+        <v>15.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
@@ -6737,6 +9628,10 @@
         <f>'Параметры'!C31*I8</f>
         <v>1481.8401937046006</v>
       </c>
+      <c r="J9" s="56">
+        <f>'Параметры'!C31*J8</f>
+        <v>2040.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
@@ -6773,6 +9668,10 @@
         <f>I9/'Параметры'!C27</f>
         <v>531.6972349137426</v>
       </c>
+      <c r="J10" s="58">
+        <f>J9/'Параметры'!C27</f>
+        <v>731.9698600645856</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
@@ -6809,6 +9708,10 @@
         <f>'Параметры'!C26*'Данные по годам'!E32</f>
         <v>7486.752777777779</v>
       </c>
+      <c r="J11" s="56">
+        <f>'Параметры'!C26*'Данные по годам'!E37</f>
+        <v>8015.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
@@ -6845,6 +9748,10 @@
         <f>I11*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
         <v>4719.773730324075</v>
       </c>
+      <c r="J12" s="56">
+        <f>J11*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5052.789583333333</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
@@ -6881,6 +9788,10 @@
         <f>I12/'Параметры'!C26</f>
         <v>0.5387869555164468</v>
       </c>
+      <c r="J13" s="59">
+        <f>J12/'Параметры'!C26</f>
+        <v>0.5768024638508371</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="37" t="inlineStr">
@@ -6917,23 +9828,2068 @@
         <f>I10*I12/1000</f>
         <v>2509.4906418318305</v>
       </c>
+      <c r="J14" s="60">
+        <f>J10*J12/1000</f>
+        <v>3698.4896842482963</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ПОГОДОВАЯ ПРОИЗВОДИТЕЛЬНОСТЬ (КТГ по годам из «Данные по годам»; часовая производительность — из геометрии выше)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>год 1</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>год 2</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>год 3</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>год 4</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>год 5</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>год 6</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>год 7</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>год 8</t>
+        </is>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>год 9</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>год 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="str">
+        <f>"Вариант 1:  "&amp;'Ввод данных'!D7</f>
+        <v>Вариант 1:  Komatsu PC2000-8
+Mining Solutions</v>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E19" s="39">
+        <f>'Данные по годам'!E7</f>
+        <v>0.9240628170979199</v>
+      </c>
+      <c r="F19" s="39">
+        <f>'Данные по годам'!F7</f>
+        <v>0.9000003170979199</v>
+      </c>
+      <c r="G19" s="39">
+        <f>'Данные по годам'!G7</f>
+        <v>0.8600004756468798</v>
+      </c>
+      <c r="H19" s="39">
+        <f>'Данные по годам'!H7</f>
+        <v>0.8499996829020803</v>
+      </c>
+      <c r="I19" s="39">
+        <f>'Данные по годам'!I7</f>
+        <v>0.8600004756468798</v>
+      </c>
+      <c r="J19" s="39">
+        <f>'Данные по годам'!J7</f>
+        <v>0.81214849695586</v>
+      </c>
+      <c r="K19" s="39">
+        <f>'Данные по годам'!K7</f>
+        <v>0.7865632927447997</v>
+      </c>
+      <c r="L19" s="39">
+        <f>'Данные по годам'!L7</f>
+        <v>0.8426392059868087</v>
+      </c>
+      <c r="M19" s="39">
+        <f>'Данные по годам'!M7</f>
+        <v>0.7373806126331812</v>
+      </c>
+      <c r="N19" s="39">
+        <f>'Данные по годам'!N7</f>
+        <v>0.826705194063927</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E20" s="38">
+        <f>'Параметры'!C26*E19</f>
+        <v>8094.790277777779</v>
+      </c>
+      <c r="F20" s="38">
+        <f>'Параметры'!C26*F19</f>
+        <v>7884.002777777779</v>
+      </c>
+      <c r="G20" s="38">
+        <f>'Параметры'!C26*G19</f>
+        <v>7533.604166666667</v>
+      </c>
+      <c r="H20" s="38">
+        <f>'Параметры'!C26*H19</f>
+        <v>7445.997222222223</v>
+      </c>
+      <c r="I20" s="38">
+        <f>'Параметры'!C26*I19</f>
+        <v>7533.604166666667</v>
+      </c>
+      <c r="J20" s="38">
+        <f>'Параметры'!C26*J19</f>
+        <v>7114.420833333334</v>
+      </c>
+      <c r="K20" s="38">
+        <f>'Параметры'!C26*K19</f>
+        <v>6890.294444444446</v>
+      </c>
+      <c r="L20" s="38">
+        <f>'Параметры'!C26*L19</f>
+        <v>7381.519444444445</v>
+      </c>
+      <c r="M20" s="38">
+        <f>'Параметры'!C26*M19</f>
+        <v>6459.454166666667</v>
+      </c>
+      <c r="N20" s="38">
+        <f>'Параметры'!C26*N19</f>
+        <v>7241.9375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E21" s="38">
+        <f>E20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>5103.090704282408</v>
+      </c>
+      <c r="F21" s="38">
+        <f>F20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4970.206751157408</v>
+      </c>
+      <c r="G21" s="38">
+        <f>G20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4749.309626736111</v>
+      </c>
+      <c r="H21" s="38">
+        <f>H20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4694.080748842593</v>
+      </c>
+      <c r="I21" s="38">
+        <f>I20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4749.309626736111</v>
+      </c>
+      <c r="J21" s="38">
+        <f>J20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4485.049467013889</v>
+      </c>
+      <c r="K21" s="38">
+        <f>K20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4343.756456018519</v>
+      </c>
+      <c r="L21" s="38">
+        <f>L20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4653.432883101852</v>
+      </c>
+      <c r="M21" s="38">
+        <f>M20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4072.147564236111</v>
+      </c>
+      <c r="N21" s="38">
+        <f>N20*(1-'Ввод данных'!D18/(60*'Параметры'!C33))</f>
+        <v>4565.438098958333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E22" s="39">
+        <f>E21/'Параметры'!C26</f>
+        <v>0.5825446009454804</v>
+      </c>
+      <c r="F22" s="39">
+        <f>F21/'Параметры'!C26</f>
+        <v>0.5673751999038137</v>
+      </c>
+      <c r="G22" s="39">
+        <f>G21/'Параметры'!C26</f>
+        <v>0.5421586331890538</v>
+      </c>
+      <c r="H22" s="39">
+        <f>H21/'Параметры'!C26</f>
+        <v>0.535853966762853</v>
+      </c>
+      <c r="I22" s="39">
+        <f>I21/'Параметры'!C26</f>
+        <v>0.5421586331890538</v>
+      </c>
+      <c r="J22" s="39">
+        <f>J21/'Параметры'!C26</f>
+        <v>0.5119919482892566</v>
+      </c>
+      <c r="K22" s="39">
+        <f>K21/'Параметры'!C26</f>
+        <v>0.49586260913453417</v>
+      </c>
+      <c r="L22" s="39">
+        <f>L21/'Параметры'!C26</f>
+        <v>0.5312137994408507</v>
+      </c>
+      <c r="M22" s="39">
+        <f>M21/'Параметры'!C26</f>
+        <v>0.4648570278808346</v>
+      </c>
+      <c r="N22" s="39">
+        <f>N21/'Параметры'!C26</f>
+        <v>0.5211687327578006</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E23" s="38">
+        <f>'Производительность'!D10*E21/1000</f>
+        <v>2213.5162007173226</v>
+      </c>
+      <c r="F23" s="38">
+        <f>'Производительность'!D10*F21/1000</f>
+        <v>2155.876468229183</v>
+      </c>
+      <c r="G23" s="38">
+        <f>'Производительность'!D10*G21/1000</f>
+        <v>2060.0601498580268</v>
+      </c>
+      <c r="H23" s="38">
+        <f>'Производительность'!D10*H21/1000</f>
+        <v>2036.1040763627718</v>
+      </c>
+      <c r="I23" s="38">
+        <f>'Производительность'!D10*I21/1000</f>
+        <v>2060.0601498580268</v>
+      </c>
+      <c r="J23" s="38">
+        <f>'Производительность'!D10*J21/1000</f>
+        <v>1945.4346848906075</v>
+      </c>
+      <c r="K23" s="38">
+        <f>'Производительность'!D10*K21/1000</f>
+        <v>1884.1474401579353</v>
+      </c>
+      <c r="L23" s="38">
+        <f>'Производительность'!D10*L21/1000</f>
+        <v>2018.47266148978</v>
+      </c>
+      <c r="M23" s="38">
+        <f>'Производительность'!D10*M21/1000</f>
+        <v>1766.3343897814811</v>
+      </c>
+      <c r="N23" s="38">
+        <f>'Производительность'!D10*N21/1000</f>
+        <v>1980.3040512166274</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="str">
+        <f>"Вариант 2:  "&amp;'Ввод данных'!E7</f>
+        <v>Вариант 2:  Komatsu PC2000-11R
+ИСТК</v>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E26" s="39">
+        <f>'Данные по годам'!E12</f>
+        <v>0.9240628170979199</v>
+      </c>
+      <c r="F26" s="39">
+        <f>'Данные по годам'!F12</f>
+        <v>0.797738299086758</v>
+      </c>
+      <c r="G26" s="39">
+        <f>'Данные по годам'!G12</f>
+        <v>0.8245343417047185</v>
+      </c>
+      <c r="H26" s="39">
+        <f>'Данные по годам'!H12</f>
+        <v>0.7639435882800609</v>
+      </c>
+      <c r="I26" s="39">
+        <f>'Данные по годам'!I12</f>
+        <v>0.7628148782343989</v>
+      </c>
+      <c r="J26" s="39">
+        <f>'Данные по годам'!J12</f>
+        <v>0.81214849695586</v>
+      </c>
+      <c r="K26" s="39">
+        <f>'Данные по годам'!K12</f>
+        <v>0.7865632927447997</v>
+      </c>
+      <c r="L26" s="39">
+        <f>'Данные по годам'!L12</f>
+        <v>0.8426392059868087</v>
+      </c>
+      <c r="M26" s="39">
+        <f>'Данные по годам'!M12</f>
+        <v>0.7373806126331812</v>
+      </c>
+      <c r="N26" s="39">
+        <f>'Данные по годам'!N12</f>
+        <v>0.826705194063927</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E27" s="38">
+        <f>'Параметры'!C26*E26</f>
+        <v>8094.790277777779</v>
+      </c>
+      <c r="F27" s="38">
+        <f>'Параметры'!C26*F26</f>
+        <v>6988.1875</v>
+      </c>
+      <c r="G27" s="38">
+        <f>'Параметры'!C26*G26</f>
+        <v>7222.9208333333345</v>
+      </c>
+      <c r="H27" s="38">
+        <f>'Параметры'!C26*H26</f>
+        <v>6692.145833333334</v>
+      </c>
+      <c r="I27" s="38">
+        <f>'Параметры'!C26*I26</f>
+        <v>6682.258333333334</v>
+      </c>
+      <c r="J27" s="38">
+        <f>'Параметры'!C26*J26</f>
+        <v>7114.420833333334</v>
+      </c>
+      <c r="K27" s="38">
+        <f>'Параметры'!C26*K26</f>
+        <v>6890.294444444446</v>
+      </c>
+      <c r="L27" s="38">
+        <f>'Параметры'!C26*L26</f>
+        <v>7381.519444444445</v>
+      </c>
+      <c r="M27" s="38">
+        <f>'Параметры'!C26*M26</f>
+        <v>6459.454166666667</v>
+      </c>
+      <c r="N27" s="38">
+        <f>'Параметры'!C26*N26</f>
+        <v>7241.9375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E28" s="38">
+        <f>E27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>5103.090704282408</v>
+      </c>
+      <c r="F28" s="38">
+        <f>F27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4405.4698697916665</v>
+      </c>
+      <c r="G28" s="38">
+        <f>G27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4553.449675347223</v>
+      </c>
+      <c r="H28" s="38">
+        <f>H27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4218.8402690972225</v>
+      </c>
+      <c r="I28" s="38">
+        <f>I27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4212.607024305556</v>
+      </c>
+      <c r="J28" s="38">
+        <f>J27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4485.049467013889</v>
+      </c>
+      <c r="K28" s="38">
+        <f>K27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4343.756456018519</v>
+      </c>
+      <c r="L28" s="38">
+        <f>L27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4653.432883101852</v>
+      </c>
+      <c r="M28" s="38">
+        <f>M27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4072.147564236111</v>
+      </c>
+      <c r="N28" s="38">
+        <f>N27*(1-'Ввод данных'!E18/(60*'Параметры'!C33))</f>
+        <v>4565.438098958333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E29" s="39">
+        <f>E28/'Параметры'!C26</f>
+        <v>0.5825446009454804</v>
+      </c>
+      <c r="F29" s="39">
+        <f>F28/'Параметры'!C26</f>
+        <v>0.5029075193826104</v>
+      </c>
+      <c r="G29" s="39">
+        <f>G28/'Параметры'!C26</f>
+        <v>0.519800191249683</v>
+      </c>
+      <c r="H29" s="39">
+        <f>H28/'Параметры'!C26</f>
+        <v>0.4816027704448884</v>
+      </c>
+      <c r="I29" s="39">
+        <f>I28/'Параметры'!C26</f>
+        <v>0.4808912128202689</v>
+      </c>
+      <c r="J29" s="39">
+        <f>J28/'Параметры'!C26</f>
+        <v>0.5119919482892566</v>
+      </c>
+      <c r="K29" s="39">
+        <f>K28/'Параметры'!C26</f>
+        <v>0.49586260913453417</v>
+      </c>
+      <c r="L29" s="39">
+        <f>L28/'Параметры'!C26</f>
+        <v>0.5312137994408507</v>
+      </c>
+      <c r="M29" s="39">
+        <f>M28/'Параметры'!C26</f>
+        <v>0.4648570278808346</v>
+      </c>
+      <c r="N29" s="39">
+        <f>N28/'Параметры'!C26</f>
+        <v>0.5211687327578006</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E30" s="38">
+        <f>'Производительность'!E10*E28/1000</f>
+        <v>2213.5162007173226</v>
+      </c>
+      <c r="F30" s="38">
+        <f>'Производительность'!E10*F28/1000</f>
+        <v>1910.9162453986098</v>
+      </c>
+      <c r="G30" s="38">
+        <f>'Производительность'!E10*G28/1000</f>
+        <v>1975.1039535852087</v>
+      </c>
+      <c r="H30" s="38">
+        <f>'Производительность'!E10*H28/1000</f>
+        <v>1829.9638052775897</v>
+      </c>
+      <c r="I30" s="38">
+        <f>'Производительность'!E10*I28/1000</f>
+        <v>1827.2600735336464</v>
+      </c>
+      <c r="J30" s="38">
+        <f>'Производительность'!E10*J28/1000</f>
+        <v>1945.4346848906075</v>
+      </c>
+      <c r="K30" s="38">
+        <f>'Производительность'!E10*K28/1000</f>
+        <v>1884.1474401579353</v>
+      </c>
+      <c r="L30" s="38">
+        <f>'Производительность'!E10*L28/1000</f>
+        <v>2018.47266148978</v>
+      </c>
+      <c r="M30" s="38">
+        <f>'Производительность'!E10*M28/1000</f>
+        <v>1766.3343897814811</v>
+      </c>
+      <c r="N30" s="38">
+        <f>'Производительность'!E10*N28/1000</f>
+        <v>1980.3040512166274</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="str">
+        <f>"Вариант 3:  "&amp;'Ввод данных'!F7</f>
+        <v>Вариант 3:  Zoomlion ZE2000G
+Орикс</v>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E33" s="39">
+        <f>'Данные по годам'!E17</f>
+        <v>0.8546521435819382</v>
+      </c>
+      <c r="F33" s="39">
+        <f>'Данные по годам'!F17</f>
+        <v>0.728326515728057</v>
+      </c>
+      <c r="G33" s="39">
+        <f>'Данные по годам'!G17</f>
+        <v>0.7551225583460174</v>
+      </c>
+      <c r="H33" s="39">
+        <f>'Данные по годам'!H17</f>
+        <v>0.6945340246067987</v>
+      </c>
+      <c r="I33" s="39">
+        <f>'Данные по годам'!I17</f>
+        <v>0.6934042047184171</v>
+      </c>
+      <c r="J33" s="39">
+        <f>'Данные по годам'!J17</f>
+        <v>0.7427367135971588</v>
+      </c>
+      <c r="K33" s="39">
+        <f>'Данные по годам'!K17</f>
+        <v>0.7171515093860985</v>
+      </c>
+      <c r="L33" s="39">
+        <f>'Данные по годам'!L17</f>
+        <v>0.7732285324708271</v>
+      </c>
+      <c r="M33" s="39">
+        <f>'Данные по годам'!M17</f>
+        <v>0.6679699391171994</v>
+      </c>
+      <c r="N33" s="39">
+        <f>'Данные по годам'!N17</f>
+        <v>0.7572945205479452</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E34" s="38">
+        <f>'Параметры'!C26*E33</f>
+        <v>7486.752777777779</v>
+      </c>
+      <c r="F34" s="38">
+        <f>'Параметры'!C26*F33</f>
+        <v>6380.140277777779</v>
+      </c>
+      <c r="G34" s="38">
+        <f>'Параметры'!C26*G33</f>
+        <v>6614.873611111112</v>
+      </c>
+      <c r="H34" s="38">
+        <f>'Параметры'!C26*H33</f>
+        <v>6084.118055555557</v>
+      </c>
+      <c r="I34" s="38">
+        <f>'Параметры'!C26*I33</f>
+        <v>6074.220833333334</v>
+      </c>
+      <c r="J34" s="38">
+        <f>'Параметры'!C26*J33</f>
+        <v>6506.373611111111</v>
+      </c>
+      <c r="K34" s="38">
+        <f>'Параметры'!C26*K33</f>
+        <v>6282.247222222223</v>
+      </c>
+      <c r="L34" s="38">
+        <f>'Параметры'!C26*L33</f>
+        <v>6773.481944444446</v>
+      </c>
+      <c r="M34" s="38">
+        <f>'Параметры'!C26*M33</f>
+        <v>5851.416666666666</v>
+      </c>
+      <c r="N34" s="38">
+        <f>'Параметры'!C26*N33</f>
+        <v>6633.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E35" s="38">
+        <f>E34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>4719.773730324075</v>
+      </c>
+      <c r="F35" s="38">
+        <f>F34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>4022.146766782408</v>
+      </c>
+      <c r="G35" s="38">
+        <f>G34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>4170.126572337963</v>
+      </c>
+      <c r="H35" s="38">
+        <f>H34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>3835.529424189815</v>
+      </c>
+      <c r="I35" s="38">
+        <f>I34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>3829.2900503472224</v>
+      </c>
+      <c r="J35" s="38">
+        <f>J34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>4101.726364004629</v>
+      </c>
+      <c r="K35" s="38">
+        <f>K34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>3960.4333530092595</v>
+      </c>
+      <c r="L35" s="38">
+        <f>L34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>4270.115909143519</v>
+      </c>
+      <c r="M35" s="38">
+        <f>M34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>3688.830590277777</v>
+      </c>
+      <c r="N35" s="38">
+        <f>N34*(1-'Ввод данных'!F18/(60*'Параметры'!C33))</f>
+        <v>4182.121125</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E36" s="39">
+        <f>E35/'Параметры'!C26</f>
+        <v>0.5387869555164468</v>
+      </c>
+      <c r="F36" s="39">
+        <f>F35/'Параметры'!C26</f>
+        <v>0.4591491742902292</v>
+      </c>
+      <c r="G36" s="39">
+        <f>G35/'Параметры'!C26</f>
+        <v>0.4760418461573017</v>
+      </c>
+      <c r="H36" s="39">
+        <f>H35/'Параметры'!C26</f>
+        <v>0.43784582467920263</v>
+      </c>
+      <c r="I36" s="39">
+        <f>I35/'Параметры'!C26</f>
+        <v>0.43713356739123543</v>
+      </c>
+      <c r="J36" s="39">
+        <f>J35/'Параметры'!C26</f>
+        <v>0.4682336031968755</v>
+      </c>
+      <c r="K36" s="39">
+        <f>K35/'Параметры'!C26</f>
+        <v>0.4521042640421529</v>
+      </c>
+      <c r="L36" s="39">
+        <f>L35/'Параметры'!C26</f>
+        <v>0.48745615401181724</v>
+      </c>
+      <c r="M36" s="39">
+        <f>M35/'Параметры'!C26</f>
+        <v>0.421099382451801</v>
+      </c>
+      <c r="N36" s="39">
+        <f>N35/'Параметры'!C26</f>
+        <v>0.4774110873287671</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E37" s="38">
+        <f>'Производительность'!F10*E35/1000</f>
+        <v>2047.2486618795972</v>
+      </c>
+      <c r="F37" s="38">
+        <f>'Производительность'!F10*F35/1000</f>
+        <v>1744.6460480242636</v>
+      </c>
+      <c r="G37" s="38">
+        <f>'Производительность'!F10*G35/1000</f>
+        <v>1808.8337562108616</v>
+      </c>
+      <c r="H37" s="38">
+        <f>'Производительность'!F10*H35/1000</f>
+        <v>1663.6989249764858</v>
+      </c>
+      <c r="I37" s="38">
+        <f>'Производительность'!F10*I35/1000</f>
+        <v>1660.9925346959208</v>
+      </c>
+      <c r="J37" s="38">
+        <f>'Производительность'!F10*J35/1000</f>
+        <v>1779.164487516261</v>
+      </c>
+      <c r="K37" s="38">
+        <f>'Производительность'!F10*K35/1000</f>
+        <v>1717.8772427835884</v>
+      </c>
+      <c r="L37" s="38">
+        <f>'Производительность'!F10*L35/1000</f>
+        <v>1852.205122652055</v>
+      </c>
+      <c r="M37" s="38">
+        <f>'Производительность'!F10*M35/1000</f>
+        <v>1600.0668509437553</v>
+      </c>
+      <c r="N37" s="38">
+        <f>'Производительность'!F10*N35/1000</f>
+        <v>1814.036512378902</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="str">
+        <f>"Вариант 4:  "&amp;'Ввод данных'!G7</f>
+        <v>Вариант 4:  Sany SY2000
+АСТ</v>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E40" s="39">
+        <f>'Данные по годам'!E22</f>
+        <v>0.8546521435819382</v>
+      </c>
+      <c r="F40" s="39">
+        <f>'Данные по годам'!F22</f>
+        <v>0.728326515728057</v>
+      </c>
+      <c r="G40" s="39">
+        <f>'Данные по годам'!G22</f>
+        <v>0.7551225583460174</v>
+      </c>
+      <c r="H40" s="39">
+        <f>'Данные по годам'!H22</f>
+        <v>0.6945340246067987</v>
+      </c>
+      <c r="I40" s="39">
+        <f>'Данные по годам'!I22</f>
+        <v>0.6934042047184171</v>
+      </c>
+      <c r="J40" s="39">
+        <f>'Данные по годам'!J22</f>
+        <v>0.7427367135971588</v>
+      </c>
+      <c r="K40" s="39">
+        <f>'Данные по годам'!K22</f>
+        <v>0.7171515093860985</v>
+      </c>
+      <c r="L40" s="39">
+        <f>'Данные по годам'!L22</f>
+        <v>0.7732285324708271</v>
+      </c>
+      <c r="M40" s="39">
+        <f>'Данные по годам'!M22</f>
+        <v>0.6679699391171994</v>
+      </c>
+      <c r="N40" s="39">
+        <f>'Данные по годам'!N22</f>
+        <v>0.7572945205479452</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E41" s="38">
+        <f>'Параметры'!C26*E40</f>
+        <v>7486.752777777779</v>
+      </c>
+      <c r="F41" s="38">
+        <f>'Параметры'!C26*F40</f>
+        <v>6380.140277777779</v>
+      </c>
+      <c r="G41" s="38">
+        <f>'Параметры'!C26*G40</f>
+        <v>6614.873611111112</v>
+      </c>
+      <c r="H41" s="38">
+        <f>'Параметры'!C26*H40</f>
+        <v>6084.118055555557</v>
+      </c>
+      <c r="I41" s="38">
+        <f>'Параметры'!C26*I40</f>
+        <v>6074.220833333334</v>
+      </c>
+      <c r="J41" s="38">
+        <f>'Параметры'!C26*J40</f>
+        <v>6506.373611111111</v>
+      </c>
+      <c r="K41" s="38">
+        <f>'Параметры'!C26*K40</f>
+        <v>6282.247222222223</v>
+      </c>
+      <c r="L41" s="38">
+        <f>'Параметры'!C26*L40</f>
+        <v>6773.481944444446</v>
+      </c>
+      <c r="M41" s="38">
+        <f>'Параметры'!C26*M40</f>
+        <v>5851.416666666666</v>
+      </c>
+      <c r="N41" s="38">
+        <f>'Параметры'!C26*N40</f>
+        <v>6633.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E42" s="38">
+        <f>E41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>4719.773730324075</v>
+      </c>
+      <c r="F42" s="38">
+        <f>F41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>4022.146766782408</v>
+      </c>
+      <c r="G42" s="38">
+        <f>G41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>4170.126572337963</v>
+      </c>
+      <c r="H42" s="38">
+        <f>H41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>3835.529424189815</v>
+      </c>
+      <c r="I42" s="38">
+        <f>I41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>3829.2900503472224</v>
+      </c>
+      <c r="J42" s="38">
+        <f>J41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>4101.726364004629</v>
+      </c>
+      <c r="K42" s="38">
+        <f>K41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>3960.4333530092595</v>
+      </c>
+      <c r="L42" s="38">
+        <f>L41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>4270.115909143519</v>
+      </c>
+      <c r="M42" s="38">
+        <f>M41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>3688.830590277777</v>
+      </c>
+      <c r="N42" s="38">
+        <f>N41*(1-'Ввод данных'!G18/(60*'Параметры'!C33))</f>
+        <v>4182.121125</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E43" s="39">
+        <f>E42/'Параметры'!C26</f>
+        <v>0.5387869555164468</v>
+      </c>
+      <c r="F43" s="39">
+        <f>F42/'Параметры'!C26</f>
+        <v>0.4591491742902292</v>
+      </c>
+      <c r="G43" s="39">
+        <f>G42/'Параметры'!C26</f>
+        <v>0.4760418461573017</v>
+      </c>
+      <c r="H43" s="39">
+        <f>H42/'Параметры'!C26</f>
+        <v>0.43784582467920263</v>
+      </c>
+      <c r="I43" s="39">
+        <f>I42/'Параметры'!C26</f>
+        <v>0.43713356739123543</v>
+      </c>
+      <c r="J43" s="39">
+        <f>J42/'Параметры'!C26</f>
+        <v>0.4682336031968755</v>
+      </c>
+      <c r="K43" s="39">
+        <f>K42/'Параметры'!C26</f>
+        <v>0.4521042640421529</v>
+      </c>
+      <c r="L43" s="39">
+        <f>L42/'Параметры'!C26</f>
+        <v>0.48745615401181724</v>
+      </c>
+      <c r="M43" s="39">
+        <f>M42/'Параметры'!C26</f>
+        <v>0.421099382451801</v>
+      </c>
+      <c r="N43" s="39">
+        <f>N42/'Параметры'!C26</f>
+        <v>0.4774110873287671</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E44" s="38">
+        <f>'Производительность'!G10*E42/1000</f>
+        <v>2047.2486618795972</v>
+      </c>
+      <c r="F44" s="38">
+        <f>'Производительность'!G10*F42/1000</f>
+        <v>1744.6460480242636</v>
+      </c>
+      <c r="G44" s="38">
+        <f>'Производительность'!G10*G42/1000</f>
+        <v>1808.8337562108616</v>
+      </c>
+      <c r="H44" s="38">
+        <f>'Производительность'!G10*H42/1000</f>
+        <v>1663.6989249764858</v>
+      </c>
+      <c r="I44" s="38">
+        <f>'Производительность'!G10*I42/1000</f>
+        <v>1660.9925346959208</v>
+      </c>
+      <c r="J44" s="38">
+        <f>'Производительность'!G10*J42/1000</f>
+        <v>1779.164487516261</v>
+      </c>
+      <c r="K44" s="38">
+        <f>'Производительность'!G10*K42/1000</f>
+        <v>1717.8772427835884</v>
+      </c>
+      <c r="L44" s="38">
+        <f>'Производительность'!G10*L42/1000</f>
+        <v>1852.205122652055</v>
+      </c>
+      <c r="M44" s="38">
+        <f>'Производительность'!G10*M42/1000</f>
+        <v>1600.0668509437553</v>
+      </c>
+      <c r="N44" s="38">
+        <f>'Производительность'!G10*N42/1000</f>
+        <v>1814.036512378902</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="5" t="str">
+        <f>"Вариант 5:  "&amp;'Ввод данных'!H7</f>
+        <v>Вариант 5:  Shantui SE2000LCW</v>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E47" s="39">
+        <f>'Данные по годам'!E27</f>
+        <v>0.8546521435819382</v>
+      </c>
+      <c r="F47" s="39">
+        <f>'Данные по годам'!F27</f>
+        <v>0.728326515728057</v>
+      </c>
+      <c r="G47" s="39">
+        <f>'Данные по годам'!G27</f>
+        <v>0.7551225583460174</v>
+      </c>
+      <c r="H47" s="39">
+        <f>'Данные по годам'!H27</f>
+        <v>0.6945340246067987</v>
+      </c>
+      <c r="I47" s="39">
+        <f>'Данные по годам'!I27</f>
+        <v>0.6934042047184171</v>
+      </c>
+      <c r="J47" s="39">
+        <f>'Данные по годам'!J27</f>
+        <v>0.7427367135971588</v>
+      </c>
+      <c r="K47" s="39">
+        <f>'Данные по годам'!K27</f>
+        <v>0.7171515093860985</v>
+      </c>
+      <c r="L47" s="39">
+        <f>'Данные по годам'!L27</f>
+        <v>0.7732285324708271</v>
+      </c>
+      <c r="M47" s="39">
+        <f>'Данные по годам'!M27</f>
+        <v>0.6679699391171994</v>
+      </c>
+      <c r="N47" s="39">
+        <f>'Данные по годам'!N27</f>
+        <v>0.7572945205479452</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E48" s="38">
+        <f>'Параметры'!C26*E47</f>
+        <v>7486.752777777779</v>
+      </c>
+      <c r="F48" s="38">
+        <f>'Параметры'!C26*F47</f>
+        <v>6380.140277777779</v>
+      </c>
+      <c r="G48" s="38">
+        <f>'Параметры'!C26*G47</f>
+        <v>6614.873611111112</v>
+      </c>
+      <c r="H48" s="38">
+        <f>'Параметры'!C26*H47</f>
+        <v>6084.118055555557</v>
+      </c>
+      <c r="I48" s="38">
+        <f>'Параметры'!C26*I47</f>
+        <v>6074.220833333334</v>
+      </c>
+      <c r="J48" s="38">
+        <f>'Параметры'!C26*J47</f>
+        <v>6506.373611111111</v>
+      </c>
+      <c r="K48" s="38">
+        <f>'Параметры'!C26*K47</f>
+        <v>6282.247222222223</v>
+      </c>
+      <c r="L48" s="38">
+        <f>'Параметры'!C26*L47</f>
+        <v>6773.481944444446</v>
+      </c>
+      <c r="M48" s="38">
+        <f>'Параметры'!C26*M47</f>
+        <v>5851.416666666666</v>
+      </c>
+      <c r="N48" s="38">
+        <f>'Параметры'!C26*N47</f>
+        <v>6633.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E49" s="38">
+        <f>E48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>4719.773730324075</v>
+      </c>
+      <c r="F49" s="38">
+        <f>F48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>4022.146766782408</v>
+      </c>
+      <c r="G49" s="38">
+        <f>G48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>4170.126572337963</v>
+      </c>
+      <c r="H49" s="38">
+        <f>H48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>3835.529424189815</v>
+      </c>
+      <c r="I49" s="38">
+        <f>I48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>3829.2900503472224</v>
+      </c>
+      <c r="J49" s="38">
+        <f>J48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>4101.726364004629</v>
+      </c>
+      <c r="K49" s="38">
+        <f>K48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>3960.4333530092595</v>
+      </c>
+      <c r="L49" s="38">
+        <f>L48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>4270.115909143519</v>
+      </c>
+      <c r="M49" s="38">
+        <f>M48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>3688.830590277777</v>
+      </c>
+      <c r="N49" s="38">
+        <f>N48*(1-'Ввод данных'!H18/(60*'Параметры'!C33))</f>
+        <v>4182.121125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E50" s="39">
+        <f>E49/'Параметры'!C26</f>
+        <v>0.5387869555164468</v>
+      </c>
+      <c r="F50" s="39">
+        <f>F49/'Параметры'!C26</f>
+        <v>0.4591491742902292</v>
+      </c>
+      <c r="G50" s="39">
+        <f>G49/'Параметры'!C26</f>
+        <v>0.4760418461573017</v>
+      </c>
+      <c r="H50" s="39">
+        <f>H49/'Параметры'!C26</f>
+        <v>0.43784582467920263</v>
+      </c>
+      <c r="I50" s="39">
+        <f>I49/'Параметры'!C26</f>
+        <v>0.43713356739123543</v>
+      </c>
+      <c r="J50" s="39">
+        <f>J49/'Параметры'!C26</f>
+        <v>0.4682336031968755</v>
+      </c>
+      <c r="K50" s="39">
+        <f>K49/'Параметры'!C26</f>
+        <v>0.4521042640421529</v>
+      </c>
+      <c r="L50" s="39">
+        <f>L49/'Параметры'!C26</f>
+        <v>0.48745615401181724</v>
+      </c>
+      <c r="M50" s="39">
+        <f>M49/'Параметры'!C26</f>
+        <v>0.421099382451801</v>
+      </c>
+      <c r="N50" s="39">
+        <f>N49/'Параметры'!C26</f>
+        <v>0.4774110873287671</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E51" s="38">
+        <f>'Производительность'!H10*E49/1000</f>
+        <v>2047.2486618795972</v>
+      </c>
+      <c r="F51" s="38">
+        <f>'Производительность'!H10*F49/1000</f>
+        <v>1744.6460480242636</v>
+      </c>
+      <c r="G51" s="38">
+        <f>'Производительность'!H10*G49/1000</f>
+        <v>1808.8337562108616</v>
+      </c>
+      <c r="H51" s="38">
+        <f>'Производительность'!H10*H49/1000</f>
+        <v>1663.6989249764858</v>
+      </c>
+      <c r="I51" s="38">
+        <f>'Производительность'!H10*I49/1000</f>
+        <v>1660.9925346959208</v>
+      </c>
+      <c r="J51" s="38">
+        <f>'Производительность'!H10*J49/1000</f>
+        <v>1779.164487516261</v>
+      </c>
+      <c r="K51" s="38">
+        <f>'Производительность'!H10*K49/1000</f>
+        <v>1717.8772427835884</v>
+      </c>
+      <c r="L51" s="38">
+        <f>'Производительность'!H10*L49/1000</f>
+        <v>1852.205122652055</v>
+      </c>
+      <c r="M51" s="38">
+        <f>'Производительность'!H10*M49/1000</f>
+        <v>1600.0668509437553</v>
+      </c>
+      <c r="N51" s="38">
+        <f>'Производительность'!H10*N49/1000</f>
+        <v>1814.036512378902</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="str">
+        <f>"Вариант 6:  "&amp;'Ввод данных'!I7</f>
+        <v>Вариант 6:  TZCO TZ2000
+Дзикай</v>
+      </c>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E54" s="39">
+        <f>'Данные по годам'!E32</f>
+        <v>0.8546521435819382</v>
+      </c>
+      <c r="F54" s="39">
+        <f>'Данные по годам'!F32</f>
+        <v>0.728326515728057</v>
+      </c>
+      <c r="G54" s="39">
+        <f>'Данные по годам'!G32</f>
+        <v>0.7551225583460174</v>
+      </c>
+      <c r="H54" s="39">
+        <f>'Данные по годам'!H32</f>
+        <v>0.6945340246067987</v>
+      </c>
+      <c r="I54" s="39">
+        <f>'Данные по годам'!I32</f>
+        <v>0.6934042047184171</v>
+      </c>
+      <c r="J54" s="39">
+        <f>'Данные по годам'!J32</f>
+        <v>0.7427367135971588</v>
+      </c>
+      <c r="K54" s="39">
+        <f>'Данные по годам'!K32</f>
+        <v>0.7171515093860985</v>
+      </c>
+      <c r="L54" s="39">
+        <f>'Данные по годам'!L32</f>
+        <v>0.7732285324708271</v>
+      </c>
+      <c r="M54" s="39">
+        <f>'Данные по годам'!M32</f>
+        <v>0.6679699391171994</v>
+      </c>
+      <c r="N54" s="39">
+        <f>'Данные по годам'!N32</f>
+        <v>0.7572945205479452</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E55" s="38">
+        <f>'Параметры'!C26*E54</f>
+        <v>7486.752777777779</v>
+      </c>
+      <c r="F55" s="38">
+        <f>'Параметры'!C26*F54</f>
+        <v>6380.140277777779</v>
+      </c>
+      <c r="G55" s="38">
+        <f>'Параметры'!C26*G54</f>
+        <v>6614.873611111112</v>
+      </c>
+      <c r="H55" s="38">
+        <f>'Параметры'!C26*H54</f>
+        <v>6084.118055555557</v>
+      </c>
+      <c r="I55" s="38">
+        <f>'Параметры'!C26*I54</f>
+        <v>6074.220833333334</v>
+      </c>
+      <c r="J55" s="38">
+        <f>'Параметры'!C26*J54</f>
+        <v>6506.373611111111</v>
+      </c>
+      <c r="K55" s="38">
+        <f>'Параметры'!C26*K54</f>
+        <v>6282.247222222223</v>
+      </c>
+      <c r="L55" s="38">
+        <f>'Параметры'!C26*L54</f>
+        <v>6773.481944444446</v>
+      </c>
+      <c r="M55" s="38">
+        <f>'Параметры'!C26*M54</f>
+        <v>5851.416666666666</v>
+      </c>
+      <c r="N55" s="38">
+        <f>'Параметры'!C26*N54</f>
+        <v>6633.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E56" s="38">
+        <f>E55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>4719.773730324075</v>
+      </c>
+      <c r="F56" s="38">
+        <f>F55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>4022.146766782408</v>
+      </c>
+      <c r="G56" s="38">
+        <f>G55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>4170.126572337963</v>
+      </c>
+      <c r="H56" s="38">
+        <f>H55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>3835.529424189815</v>
+      </c>
+      <c r="I56" s="38">
+        <f>I55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>3829.2900503472224</v>
+      </c>
+      <c r="J56" s="38">
+        <f>J55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>4101.726364004629</v>
+      </c>
+      <c r="K56" s="38">
+        <f>K55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>3960.4333530092595</v>
+      </c>
+      <c r="L56" s="38">
+        <f>L55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>4270.115909143519</v>
+      </c>
+      <c r="M56" s="38">
+        <f>M55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>3688.830590277777</v>
+      </c>
+      <c r="N56" s="38">
+        <f>N55*(1-'Ввод данных'!I18/(60*'Параметры'!C33))</f>
+        <v>4182.121125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E57" s="39">
+        <f>E56/'Параметры'!C26</f>
+        <v>0.5387869555164468</v>
+      </c>
+      <c r="F57" s="39">
+        <f>F56/'Параметры'!C26</f>
+        <v>0.4591491742902292</v>
+      </c>
+      <c r="G57" s="39">
+        <f>G56/'Параметры'!C26</f>
+        <v>0.4760418461573017</v>
+      </c>
+      <c r="H57" s="39">
+        <f>H56/'Параметры'!C26</f>
+        <v>0.43784582467920263</v>
+      </c>
+      <c r="I57" s="39">
+        <f>I56/'Параметры'!C26</f>
+        <v>0.43713356739123543</v>
+      </c>
+      <c r="J57" s="39">
+        <f>J56/'Параметры'!C26</f>
+        <v>0.4682336031968755</v>
+      </c>
+      <c r="K57" s="39">
+        <f>K56/'Параметры'!C26</f>
+        <v>0.4521042640421529</v>
+      </c>
+      <c r="L57" s="39">
+        <f>L56/'Параметры'!C26</f>
+        <v>0.48745615401181724</v>
+      </c>
+      <c r="M57" s="39">
+        <f>M56/'Параметры'!C26</f>
+        <v>0.421099382451801</v>
+      </c>
+      <c r="N57" s="39">
+        <f>N56/'Параметры'!C26</f>
+        <v>0.4774110873287671</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E58" s="38">
+        <f>'Производительность'!I10*E56/1000</f>
+        <v>2509.4906418318305</v>
+      </c>
+      <c r="F58" s="38">
+        <f>'Производительность'!I10*F56/1000</f>
+        <v>2138.5643143154566</v>
+      </c>
+      <c r="G58" s="38">
+        <f>'Производительность'!I10*G56/1000</f>
+        <v>2217.244767752418</v>
+      </c>
+      <c r="H58" s="38">
+        <f>'Производительность'!I10*H56/1000</f>
+        <v>2039.340389272024</v>
+      </c>
+      <c r="I58" s="38">
+        <f>'Производительность'!I10*I56/1000</f>
+        <v>2036.0229314523244</v>
+      </c>
+      <c r="J58" s="38">
+        <f>'Производительность'!I10*J56/1000</f>
+        <v>2180.8765661140606</v>
+      </c>
+      <c r="K58" s="38">
+        <f>'Производительность'!I10*K56/1000</f>
+        <v>2105.7514628551853</v>
+      </c>
+      <c r="L58" s="38">
+        <f>'Производительность'!I10*L56/1000</f>
+        <v>2270.4088216527916</v>
+      </c>
+      <c r="M58" s="38">
+        <f>'Производительность'!I10*M56/1000</f>
+        <v>1961.3410249159228</v>
+      </c>
+      <c r="N58" s="38">
+        <f>'Производительность'!I10*N56/1000</f>
+        <v>2223.62223823685</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="str">
+        <f>"Вариант 7:  "&amp;'Ввод данных'!J7</f>
+        <v>Вариант 7:  XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="37" t="inlineStr">
+        <is>
+          <t>КТГ (по годам)</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E61" s="39">
+        <f>'Данные по годам'!E37</f>
+        <v>0.9149543378995434</v>
+      </c>
+      <c r="F61" s="39">
+        <f>'Данные по годам'!F37</f>
+        <v>0.9104039827498731</v>
+      </c>
+      <c r="G61" s="39">
+        <f>'Данные по годам'!G37</f>
+        <v>0.8236142820903096</v>
+      </c>
+      <c r="H61" s="39">
+        <f>'Данные по годам'!H37</f>
+        <v>0.9095716007102994</v>
+      </c>
+      <c r="I61" s="39">
+        <f>'Данные по годам'!I37</f>
+        <v>0.9044108320649418</v>
+      </c>
+      <c r="J61" s="39">
+        <f>'Данные по годам'!J37</f>
+        <v>0.8074105783866059</v>
+      </c>
+      <c r="K61" s="39">
+        <f>'Данные по годам'!K37</f>
+        <v>0.8933124048706241</v>
+      </c>
+      <c r="L61" s="39">
+        <f>'Данные по годам'!L37</f>
+        <v>0.814125126839168</v>
+      </c>
+      <c r="M61" s="39">
+        <f>'Данные по годам'!M37</f>
+        <v>0.8302733384069001</v>
+      </c>
+      <c r="N61" s="39">
+        <f>'Данные по годам'!N37</f>
+        <v>0.8100742009132421</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="37" t="inlineStr">
+        <is>
+          <t>Время техготовности</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E62" s="38">
+        <f>'Параметры'!C26*E61</f>
+        <v>8015.0</v>
+      </c>
+      <c r="F62" s="38">
+        <f>'Параметры'!C26*F61</f>
+        <v>7975.138888888889</v>
+      </c>
+      <c r="G62" s="38">
+        <f>'Параметры'!C26*G61</f>
+        <v>7214.861111111112</v>
+      </c>
+      <c r="H62" s="38">
+        <f>'Параметры'!C26*H61</f>
+        <v>7967.847222222223</v>
+      </c>
+      <c r="I62" s="38">
+        <f>'Параметры'!C26*I61</f>
+        <v>7922.63888888889</v>
+      </c>
+      <c r="J62" s="38">
+        <f>'Параметры'!C26*J61</f>
+        <v>7072.916666666668</v>
+      </c>
+      <c r="K62" s="38">
+        <f>'Параметры'!C26*K61</f>
+        <v>7825.416666666667</v>
+      </c>
+      <c r="L62" s="38">
+        <f>'Параметры'!C26*L61</f>
+        <v>7131.736111111112</v>
+      </c>
+      <c r="M62" s="38">
+        <f>'Параметры'!C26*M61</f>
+        <v>7273.194444444445</v>
+      </c>
+      <c r="N62" s="38">
+        <f>'Параметры'!C26*N61</f>
+        <v>7096.250000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="37" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="E63" s="38">
+        <f>E62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5052.789583333333</v>
+      </c>
+      <c r="F63" s="38">
+        <f>F62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5027.660474537037</v>
+      </c>
+      <c r="G63" s="38">
+        <f>G62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4548.36869212963</v>
+      </c>
+      <c r="H63" s="38">
+        <f>H62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5023.0636863425925</v>
+      </c>
+      <c r="I63" s="38">
+        <f>I62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4994.563599537038</v>
+      </c>
+      <c r="J63" s="38">
+        <f>J62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4458.884548611111</v>
+      </c>
+      <c r="K63" s="38">
+        <f>K62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4933.273090277778</v>
+      </c>
+      <c r="L63" s="38">
+        <f>L62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4495.965306712963</v>
+      </c>
+      <c r="M63" s="38">
+        <f>M62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4585.142997685185</v>
+      </c>
+      <c r="N63" s="38">
+        <f>N62*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4473.594270833333</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="37" t="inlineStr">
+        <is>
+          <t>КИО</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="E64" s="39">
+        <f>E63/'Параметры'!C26</f>
+        <v>0.5768024638508371</v>
+      </c>
+      <c r="F64" s="39">
+        <f>F63/'Параметры'!C26</f>
+        <v>0.5739338441252325</v>
+      </c>
+      <c r="G64" s="39">
+        <f>G63/'Параметры'!C26</f>
+        <v>0.5192201703344327</v>
+      </c>
+      <c r="H64" s="39">
+        <f>H63/'Параметры'!C26</f>
+        <v>0.5734090966144512</v>
+      </c>
+      <c r="I64" s="39">
+        <f>I63/'Параметры'!C26</f>
+        <v>0.570155662047607</v>
+      </c>
+      <c r="J64" s="39">
+        <f>J63/'Параметры'!C26</f>
+        <v>0.5090050854578895</v>
+      </c>
+      <c r="K64" s="39">
+        <f>K63/'Параметры'!C26</f>
+        <v>0.5631590285705226</v>
+      </c>
+      <c r="L64" s="39">
+        <f>L63/'Параметры'!C26</f>
+        <v>0.5132380487115255</v>
+      </c>
+      <c r="M64" s="39">
+        <f>M63/'Параметры'!C26</f>
+        <v>0.5234181504206832</v>
+      </c>
+      <c r="N64" s="39">
+        <f>N63/'Параметры'!C26</f>
+        <v>0.5106842774923896</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="37" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="E65" s="38">
+        <f>'Производительность'!J10*E63/1000</f>
+        <v>3698.4896842482963</v>
+      </c>
+      <c r="F65" s="38">
+        <f>'Производительность'!J10*F63/1000</f>
+        <v>3680.095933999123</v>
+      </c>
+      <c r="G65" s="38">
+        <f>'Производительность'!J10*G63/1000</f>
+        <v>3329.268795100268</v>
+      </c>
+      <c r="H65" s="38">
+        <f>'Производительность'!J10*H63/1000</f>
+        <v>3676.731223587689</v>
+      </c>
+      <c r="I65" s="38">
+        <f>'Производительность'!J10*I63/1000</f>
+        <v>3655.8700190367986</v>
+      </c>
+      <c r="J65" s="38">
+        <f>'Производительность'!J10*J63/1000</f>
+        <v>3263.7690990910182</v>
+      </c>
+      <c r="K65" s="38">
+        <f>'Производительность'!J10*K63/1000</f>
+        <v>3611.007213551011</v>
+      </c>
+      <c r="L65" s="38">
+        <f>'Производительность'!J10*L63/1000</f>
+        <v>3290.911096409919</v>
+      </c>
+      <c r="M65" s="38">
+        <f>'Производительность'!J10*M63/1000</f>
+        <v>3356.1864783917395</v>
+      </c>
+      <c r="N65" s="38">
+        <f>'Производительность'!J10*N63/1000</f>
+        <v>3274.536172407607</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:K2"/>
+  <mergeCells count="10">
+    <mergeCell ref="B46:N46"/>
+    <mergeCell ref="B16:N16"/>
+    <mergeCell ref="B60:N60"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="B32:N32"/>
+    <mergeCell ref="B18:N18"/>
+    <mergeCell ref="B53:N53"/>
+    <mergeCell ref="B39:N39"/>
+    <mergeCell ref="B25:N25"/>
+    <mergeCell ref="B2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:N120"/>
+  <dimension ref="B1:N139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -12712,10 +17668,943 @@
         <v>32.43018221027532</v>
       </c>
     </row>
+    <row r="122">
+      <c r="B122" s="5" t="str">
+        <f>"Вариант 7:  "&amp;'Ввод данных'!J7</f>
+        <v>Вариант 7:  XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="22" t="inlineStr">
+        <is>
+          <t>КТГ</t>
+        </is>
+      </c>
+      <c r="C123" s="24" t="inlineStr">
+        <is>
+          <t>коэф.</t>
+        </is>
+      </c>
+      <c r="D123" s="59" t="n"/>
+      <c r="E123" s="59">
+        <f>'Данные по годам'!E37</f>
+        <v>0.9149543378995434</v>
+      </c>
+      <c r="F123" s="59">
+        <f>'Данные по годам'!F37</f>
+        <v>0.9104039827498731</v>
+      </c>
+      <c r="G123" s="59">
+        <f>'Данные по годам'!G37</f>
+        <v>0.8236142820903096</v>
+      </c>
+      <c r="H123" s="59">
+        <f>'Данные по годам'!H37</f>
+        <v>0.9095716007102994</v>
+      </c>
+      <c r="I123" s="59">
+        <f>'Данные по годам'!I37</f>
+        <v>0.9044108320649418</v>
+      </c>
+      <c r="J123" s="59">
+        <f>'Данные по годам'!J37</f>
+        <v>0.8074105783866059</v>
+      </c>
+      <c r="K123" s="59">
+        <f>'Данные по годам'!K37</f>
+        <v>0.8933124048706241</v>
+      </c>
+      <c r="L123" s="59">
+        <f>'Данные по годам'!L37</f>
+        <v>0.814125126839168</v>
+      </c>
+      <c r="M123" s="59">
+        <f>'Данные по годам'!M37</f>
+        <v>0.8302733384069001</v>
+      </c>
+      <c r="N123" s="59">
+        <f>'Данные по годам'!N37</f>
+        <v>0.8100742009132421</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="22" t="inlineStr">
+        <is>
+          <t>Эффективное время</t>
+        </is>
+      </c>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>час/год</t>
+        </is>
+      </c>
+      <c r="D124" s="56" t="n"/>
+      <c r="E124" s="56">
+        <f>'Параметры'!C26*E123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5052.789583333333</v>
+      </c>
+      <c r="F124" s="56">
+        <f>'Параметры'!C26*F123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5027.660474537037</v>
+      </c>
+      <c r="G124" s="56">
+        <f>'Параметры'!C26*G123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4548.36869212963</v>
+      </c>
+      <c r="H124" s="56">
+        <f>'Параметры'!C26*H123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>5023.0636863425925</v>
+      </c>
+      <c r="I124" s="56">
+        <f>'Параметры'!C26*I123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4994.563599537038</v>
+      </c>
+      <c r="J124" s="56">
+        <f>'Параметры'!C26*J123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4458.884548611111</v>
+      </c>
+      <c r="K124" s="56">
+        <f>'Параметры'!C26*K123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4933.273090277778</v>
+      </c>
+      <c r="L124" s="56">
+        <f>'Параметры'!C26*L123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4495.965306712963</v>
+      </c>
+      <c r="M124" s="56">
+        <f>'Параметры'!C26*M123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4585.142997685185</v>
+      </c>
+      <c r="N124" s="56">
+        <f>'Параметры'!C26*N123*(1-'Ввод данных'!J18/(60*'Параметры'!C33))</f>
+        <v>4473.594270833333</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="22" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="C125" s="24" t="inlineStr">
+        <is>
+          <t>тыс.м³</t>
+        </is>
+      </c>
+      <c r="D125" s="56" t="n"/>
+      <c r="E125" s="56">
+        <f>'Производительность'!J10*E124/1000</f>
+        <v>3698.4896842482963</v>
+      </c>
+      <c r="F125" s="56">
+        <f>'Производительность'!J10*F124/1000</f>
+        <v>3680.095933999123</v>
+      </c>
+      <c r="G125" s="56">
+        <f>'Производительность'!J10*G124/1000</f>
+        <v>3329.268795100268</v>
+      </c>
+      <c r="H125" s="56">
+        <f>'Производительность'!J10*H124/1000</f>
+        <v>3676.731223587689</v>
+      </c>
+      <c r="I125" s="56">
+        <f>'Производительность'!J10*I124/1000</f>
+        <v>3655.8700190367986</v>
+      </c>
+      <c r="J125" s="56">
+        <f>'Производительность'!J10*J124/1000</f>
+        <v>3263.7690990910182</v>
+      </c>
+      <c r="K125" s="56">
+        <f>'Производительность'!J10*K124/1000</f>
+        <v>3611.007213551011</v>
+      </c>
+      <c r="L125" s="56">
+        <f>'Производительность'!J10*L124/1000</f>
+        <v>3290.911096409919</v>
+      </c>
+      <c r="M125" s="56">
+        <f>'Производительность'!J10*M124/1000</f>
+        <v>3356.1864783917395</v>
+      </c>
+      <c r="N125" s="56">
+        <f>'Производительность'!J10*N124/1000</f>
+        <v>3274.536172407607</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>Дизтопливо</t>
+        </is>
+      </c>
+      <c r="C126" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D126" s="56" t="n"/>
+      <c r="E126" s="56">
+        <f>E124*'Данные по годам'!E39*'Параметры'!C10*(1+'Параметры'!C14)^(E$4-1)/1000</f>
+        <v>29089.667549687496</v>
+      </c>
+      <c r="F126" s="56">
+        <f>F124*'Данные по годам'!F39*'Параметры'!C10*(1+'Параметры'!C14)^(F$4-1)/1000</f>
+        <v>28944.995500980902</v>
+      </c>
+      <c r="G126" s="56">
+        <f>G124*'Данные по годам'!G39*'Параметры'!C10*(1+'Параметры'!C14)^(G$4-1)/1000</f>
+        <v>26185.6408158941</v>
+      </c>
+      <c r="H126" s="56">
+        <f>H124*'Данные по годам'!H39*'Параметры'!C10*(1+'Параметры'!C14)^(H$4-1)/1000</f>
+        <v>28918.531101827255</v>
+      </c>
+      <c r="I126" s="56">
+        <f>I124*'Данные по годам'!I39*'Параметры'!C10*(1+'Параметры'!C14)^(I$4-1)/1000</f>
+        <v>28754.45182707466</v>
+      </c>
+      <c r="J126" s="56">
+        <f>J124*'Данные по годам'!J39*'Параметры'!C10*(1+'Параметры'!C14)^(J$4-1)/1000</f>
+        <v>25670.467179036455</v>
+      </c>
+      <c r="K126" s="56">
+        <f>K124*'Данные по годам'!K39*'Параметры'!C10*(1+'Параметры'!C14)^(K$4-1)/1000</f>
+        <v>28401.593171692708</v>
+      </c>
+      <c r="L126" s="56">
+        <f>L124*'Данные по годам'!L39*'Параметры'!C10*(1+'Параметры'!C14)^(L$4-1)/1000</f>
+        <v>25883.946665542535</v>
+      </c>
+      <c r="M126" s="56">
+        <f>M124*'Данные по годам'!M39*'Параметры'!C10*(1+'Параметры'!C14)^(M$4-1)/1000</f>
+        <v>26397.35600912326</v>
+      </c>
+      <c r="N126" s="56">
+        <f>N124*'Данные по годам'!N39*'Параметры'!C10*(1+'Параметры'!C14)^(N$4-1)/1000</f>
+        <v>25755.153256328125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t>ТОиР и сервис (по годам)</t>
+        </is>
+      </c>
+      <c r="C127" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D127" s="56" t="n"/>
+      <c r="E127" s="56">
+        <f>'Данные по годам'!E38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>21115.067956576</v>
+      </c>
+      <c r="F127" s="56">
+        <f>'Данные по годам'!F38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>53117.593018576</v>
+      </c>
+      <c r="G127" s="56">
+        <f>'Данные по годам'!G38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>118601.76743657599</v>
+      </c>
+      <c r="H127" s="56">
+        <f>'Данные по годам'!H38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>53436.560120576</v>
+      </c>
+      <c r="I127" s="56">
+        <f>'Данные по годам'!I38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>21115.067956576</v>
+      </c>
+      <c r="J127" s="56">
+        <f>'Данные по годам'!J38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>150604.29249857602</v>
+      </c>
+      <c r="K127" s="56">
+        <f>'Данные по годам'!K38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>21115.067956576</v>
+      </c>
+      <c r="L127" s="56">
+        <f>'Данные по годам'!L38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>53436.560120576</v>
+      </c>
+      <c r="M127" s="56">
+        <f>'Данные по годам'!M38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>118601.76743657599</v>
+      </c>
+      <c r="N127" s="56">
+        <f>'Данные по годам'!N38*IF('Данные по годам'!$D$38="CNY",'Параметры'!C20,IF('Данные по годам'!$D$38="USD",'Параметры'!C21,IF('Данные по годам'!$D$38="EUR",'Параметры'!C22,1)))</f>
+        <v>53117.593018576</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>Расходники на ковш</t>
+        </is>
+      </c>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D128" s="56" t="n"/>
+      <c r="E128" s="56">
+        <f>'Данные по годам'!E40*E125*(1+'Параметры'!C15)^(E$4-1)</f>
+        <v>3217.6860252960178</v>
+      </c>
+      <c r="F128" s="56">
+        <f>'Данные по годам'!F40*F125*(1+'Параметры'!C15)^(F$4-1)</f>
+        <v>3201.683462579237</v>
+      </c>
+      <c r="G128" s="56">
+        <f>'Данные по годам'!G40*G125*(1+'Параметры'!C15)^(G$4-1)</f>
+        <v>2896.463851737233</v>
+      </c>
+      <c r="H128" s="56">
+        <f>'Данные по годам'!H40*H125*(1+'Параметры'!C15)^(H$4-1)</f>
+        <v>3198.7561645212895</v>
+      </c>
+      <c r="I128" s="56">
+        <f>'Данные по годам'!I40*I125*(1+'Параметры'!C15)^(I$4-1)</f>
+        <v>3180.6069165620147</v>
+      </c>
+      <c r="J128" s="56">
+        <f>'Данные по годам'!J40*J125*(1+'Параметры'!C15)^(J$4-1)</f>
+        <v>2839.479116209186</v>
+      </c>
+      <c r="K128" s="56">
+        <f>'Данные по годам'!K40*K125*(1+'Параметры'!C15)^(K$4-1)</f>
+        <v>3141.5762757893795</v>
+      </c>
+      <c r="L128" s="56">
+        <f>'Данные по годам'!L40*L125*(1+'Параметры'!C15)^(L$4-1)</f>
+        <v>2863.09265387663</v>
+      </c>
+      <c r="M128" s="56">
+        <f>'Данные по годам'!M40*M125*(1+'Параметры'!C15)^(M$4-1)</f>
+        <v>2919.882236200813</v>
+      </c>
+      <c r="N128" s="56">
+        <f>'Данные по годам'!N40*N125*(1+'Параметры'!C15)^(N$4-1)</f>
+        <v>2848.846469994618</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="22" t="inlineStr">
+        <is>
+          <t>Персонал</t>
+        </is>
+      </c>
+      <c r="C129" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D129" s="56" t="n"/>
+      <c r="E129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(E$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="F129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(F$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="G129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(G$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="H129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(H$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="I129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(I$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="J129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(J$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="K129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(K$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="L129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(L$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="M129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(M$4-1)</f>
+        <v>10015.0</v>
+      </c>
+      <c r="N129" s="56">
+        <f>'Ввод данных'!J20*(1+'Параметры'!C16)^(N$4-1)</f>
+        <v>10015.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>Итого денежные затраты</t>
+        </is>
+      </c>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D130" s="56" t="n"/>
+      <c r="E130" s="65">
+        <f>E126+E127+E128+E129</f>
+        <v>63437.421531559514</v>
+      </c>
+      <c r="F130" s="65">
+        <f>F126+F127+F128+F129</f>
+        <v>95279.27198213614</v>
+      </c>
+      <c r="G130" s="65">
+        <f>G126+G127+G128+G129</f>
+        <v>157698.87210420732</v>
+      </c>
+      <c r="H130" s="65">
+        <f>H126+H127+H128+H129</f>
+        <v>95568.84738692454</v>
+      </c>
+      <c r="I130" s="65">
+        <f>I126+I127+I128+I129</f>
+        <v>63065.12670021267</v>
+      </c>
+      <c r="J130" s="65">
+        <f>J126+J127+J128+J129</f>
+        <v>189129.23879382166</v>
+      </c>
+      <c r="K130" s="65">
+        <f>K126+K127+K128+K129</f>
+        <v>62673.23740405809</v>
+      </c>
+      <c r="L130" s="65">
+        <f>L126+L127+L128+L129</f>
+        <v>92198.59943999517</v>
+      </c>
+      <c r="M130" s="65">
+        <f>M126+M127+M128+M129</f>
+        <v>157934.00568190007</v>
+      </c>
+      <c r="N130" s="65">
+        <f>N126+N127+N128+N129</f>
+        <v>91736.59274489875</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="22" t="inlineStr">
+        <is>
+          <t>Амортизация (НУ)</t>
+        </is>
+      </c>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D131" s="56" t="n"/>
+      <c r="E131" s="56">
+        <f>IF(E$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(E$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>39017.87234042553</v>
+      </c>
+      <c r="F131" s="56">
+        <f>IF(F$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(F$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>39017.87234042553</v>
+      </c>
+      <c r="G131" s="56">
+        <f>IF(G$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(G$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>39017.87234042553</v>
+      </c>
+      <c r="H131" s="56">
+        <f>IF(H$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(H$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>39017.87234042553</v>
+      </c>
+      <c r="I131" s="56">
+        <f>IF(I$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(I$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>39017.87234042553</v>
+      </c>
+      <c r="J131" s="56">
+        <f>IF(J$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(J$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>6633.038297872337</v>
+      </c>
+      <c r="K131" s="56">
+        <f>IF(K$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(K$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="L131" s="56">
+        <f>IF(L$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(L$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="M131" s="56">
+        <f>IF(M$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(M$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="N131" s="56">
+        <f>IF(N$4&lt;=INT('Параметры'!C9),'Производительность'!J5/'Параметры'!C9,IF(N$4=INT('Параметры'!C9)+1,'Производительность'!J5*('Параметры'!C9-INT('Параметры'!C9))/'Параметры'!C9,0))</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="22" t="inlineStr">
+        <is>
+          <t>Налогооблагаемая база</t>
+        </is>
+      </c>
+      <c r="C132" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D132" s="56" t="n"/>
+      <c r="E132" s="56">
+        <f>E130+E131</f>
+        <v>102455.29387198505</v>
+      </c>
+      <c r="F132" s="56">
+        <f>F130+F131</f>
+        <v>134297.14432256168</v>
+      </c>
+      <c r="G132" s="56">
+        <f>G130+G131</f>
+        <v>196716.74444463284</v>
+      </c>
+      <c r="H132" s="56">
+        <f>H130+H131</f>
+        <v>134586.71972735005</v>
+      </c>
+      <c r="I132" s="56">
+        <f>I130+I131</f>
+        <v>102082.9990406382</v>
+      </c>
+      <c r="J132" s="56">
+        <f>J130+J131</f>
+        <v>195762.277091694</v>
+      </c>
+      <c r="K132" s="56">
+        <f>K130+K131</f>
+        <v>62673.23740405809</v>
+      </c>
+      <c r="L132" s="56">
+        <f>L130+L131</f>
+        <v>92198.59943999517</v>
+      </c>
+      <c r="M132" s="56">
+        <f>M130+M131</f>
+        <v>157934.00568190007</v>
+      </c>
+      <c r="N132" s="56">
+        <f>N130+N131</f>
+        <v>91736.59274489875</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="22" t="inlineStr">
+        <is>
+          <t>Налог на прибыль (щит)</t>
+        </is>
+      </c>
+      <c r="C133" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D133" s="56" t="n"/>
+      <c r="E133" s="56">
+        <f>-E132*'Параметры'!C7</f>
+        <v>-25613.823467996262</v>
+      </c>
+      <c r="F133" s="56">
+        <f>-F132*'Параметры'!C7</f>
+        <v>-33574.28608064042</v>
+      </c>
+      <c r="G133" s="56">
+        <f>-G132*'Параметры'!C7</f>
+        <v>-49179.18611115821</v>
+      </c>
+      <c r="H133" s="56">
+        <f>-H132*'Параметры'!C7</f>
+        <v>-33646.67993183751</v>
+      </c>
+      <c r="I133" s="56">
+        <f>-I132*'Параметры'!C7</f>
+        <v>-25520.74976015955</v>
+      </c>
+      <c r="J133" s="56">
+        <f>-J132*'Параметры'!C7</f>
+        <v>-48940.5692729235</v>
+      </c>
+      <c r="K133" s="56">
+        <f>-K132*'Параметры'!C7</f>
+        <v>-15668.309351014523</v>
+      </c>
+      <c r="L133" s="56">
+        <f>-L132*'Параметры'!C7</f>
+        <v>-23049.649859998794</v>
+      </c>
+      <c r="M133" s="56">
+        <f>-M132*'Параметры'!C7</f>
+        <v>-39483.50142047502</v>
+      </c>
+      <c r="N133" s="56">
+        <f>-N132*'Параметры'!C7</f>
+        <v>-22934.148186224687</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="22" t="inlineStr">
+        <is>
+          <t>Операц. денежный поток</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D134" s="56" t="n"/>
+      <c r="E134" s="65">
+        <f>E132+E133-E131</f>
+        <v>37823.59806356326</v>
+      </c>
+      <c r="F134" s="65">
+        <f>F132+F133-F131</f>
+        <v>61704.98590149573</v>
+      </c>
+      <c r="G134" s="65">
+        <f>G132+G133-G131</f>
+        <v>108519.68599304909</v>
+      </c>
+      <c r="H134" s="65">
+        <f>H132+H133-H131</f>
+        <v>61922.16745508701</v>
+      </c>
+      <c r="I134" s="65">
+        <f>I132+I133-I131</f>
+        <v>37544.37694005312</v>
+      </c>
+      <c r="J134" s="65">
+        <f>J132+J133-J131</f>
+        <v>140188.66952089814</v>
+      </c>
+      <c r="K134" s="65">
+        <f>K132+K133-K131</f>
+        <v>47004.928053043564</v>
+      </c>
+      <c r="L134" s="65">
+        <f>L132+L133-L131</f>
+        <v>69148.94957999638</v>
+      </c>
+      <c r="M134" s="65">
+        <f>M132+M133-M131</f>
+        <v>118450.50426142506</v>
+      </c>
+      <c r="N134" s="65">
+        <f>N132+N133-N131</f>
+        <v>68802.44455867406</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="22" t="inlineStr">
+        <is>
+          <t>Инвестиции / остаточная ст-ть</t>
+        </is>
+      </c>
+      <c r="C135" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D135" s="56">
+        <f>IF(D$4=0,'Производительность'!J5,IF(D$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>201722.4</v>
+      </c>
+      <c r="E135" s="56">
+        <f>IF(E$4=0,'Производительность'!J5,IF(E$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="F135" s="56">
+        <f>IF(F$4=0,'Производительность'!J5,IF(F$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G135" s="56">
+        <f>IF(G$4=0,'Производительность'!J5,IF(G$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="H135" s="56">
+        <f>IF(H$4=0,'Производительность'!J5,IF(H$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="I135" s="56">
+        <f>IF(I$4=0,'Производительность'!J5,IF(I$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="J135" s="56">
+        <f>IF(J$4=0,'Производительность'!J5,IF(J$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="K135" s="56">
+        <f>IF(K$4=0,'Производительность'!J5,IF(K$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="L135" s="56">
+        <f>IF(L$4=0,'Производительность'!J5,IF(L$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="M135" s="56">
+        <f>IF(M$4=0,'Производительность'!J5,IF(M$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>0.0</v>
+      </c>
+      <c r="N135" s="56">
+        <f>IF(N$4=0,'Производительность'!J5,IF(N$4='Параметры'!C8,-'Ввод данных'!J14*'Производительность'!J5,0))</f>
+        <v>-0.0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>Чистый денежный поток</t>
+        </is>
+      </c>
+      <c r="C136" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D136" s="65">
+        <f>0+D135</f>
+        <v>201722.4</v>
+      </c>
+      <c r="E136" s="65">
+        <f>E134+E135</f>
+        <v>37823.59806356326</v>
+      </c>
+      <c r="F136" s="65">
+        <f>F134+F135</f>
+        <v>61704.98590149573</v>
+      </c>
+      <c r="G136" s="65">
+        <f>G134+G135</f>
+        <v>108519.68599304909</v>
+      </c>
+      <c r="H136" s="65">
+        <f>H134+H135</f>
+        <v>61922.16745508701</v>
+      </c>
+      <c r="I136" s="65">
+        <f>I134+I135</f>
+        <v>37544.37694005312</v>
+      </c>
+      <c r="J136" s="65">
+        <f>J134+J135</f>
+        <v>140188.66952089814</v>
+      </c>
+      <c r="K136" s="65">
+        <f>K134+K135</f>
+        <v>47004.928053043564</v>
+      </c>
+      <c r="L136" s="65">
+        <f>L134+L135</f>
+        <v>69148.94957999638</v>
+      </c>
+      <c r="M136" s="65">
+        <f>M134+M135</f>
+        <v>118450.50426142506</v>
+      </c>
+      <c r="N136" s="65">
+        <f>N134+N135</f>
+        <v>68802.44455867406</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="22" t="inlineStr">
+        <is>
+          <t>Дисконтированный поток</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D137" s="56">
+        <f>D136*D$6</f>
+        <v>201722.4</v>
+      </c>
+      <c r="E137" s="56">
+        <f>E136*E$6</f>
+        <v>33771.06969961005</v>
+      </c>
+      <c r="F137" s="56">
+        <f>F136*F$6</f>
+        <v>49190.836975044425</v>
+      </c>
+      <c r="G137" s="56">
+        <f>G136*G$6</f>
+        <v>77242.16898876602</v>
+      </c>
+      <c r="H137" s="56">
+        <f>H136*H$6</f>
+        <v>39352.65687171907</v>
+      </c>
+      <c r="I137" s="56">
+        <f>I136*I$6</f>
+        <v>21303.68775700822</v>
+      </c>
+      <c r="J137" s="56">
+        <f>J136*J$6</f>
+        <v>71023.94281572949</v>
+      </c>
+      <c r="K137" s="56">
+        <f>K136*K$6</f>
+        <v>21262.642321761385</v>
+      </c>
+      <c r="L137" s="56">
+        <f>L136*L$6</f>
+        <v>27928.100967751572</v>
+      </c>
+      <c r="M137" s="56">
+        <f>M136*M$6</f>
+        <v>42714.43930079317</v>
+      </c>
+      <c r="N137" s="56">
+        <f>N136*N$6</f>
+        <v>22152.545759908204</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>Кумул. дисконт. поток</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>тыс.руб</t>
+        </is>
+      </c>
+      <c r="D138" s="56">
+        <f>SUM($D137:D137)</f>
+        <v>201722.4</v>
+      </c>
+      <c r="E138" s="56">
+        <f>SUM($D137:E137)</f>
+        <v>235493.46969961005</v>
+      </c>
+      <c r="F138" s="56">
+        <f>SUM($D137:F137)</f>
+        <v>284684.3066746545</v>
+      </c>
+      <c r="G138" s="56">
+        <f>SUM($D137:G137)</f>
+        <v>361926.4756634205</v>
+      </c>
+      <c r="H138" s="56">
+        <f>SUM($D137:H137)</f>
+        <v>401279.13253513956</v>
+      </c>
+      <c r="I138" s="56">
+        <f>SUM($D137:I137)</f>
+        <v>422582.8202921478</v>
+      </c>
+      <c r="J138" s="56">
+        <f>SUM($D137:J137)</f>
+        <v>493606.7631078773</v>
+      </c>
+      <c r="K138" s="56">
+        <f>SUM($D137:K137)</f>
+        <v>514869.4054296387</v>
+      </c>
+      <c r="L138" s="56">
+        <f>SUM($D137:L137)</f>
+        <v>542797.5063973903</v>
+      </c>
+      <c r="M138" s="56">
+        <f>SUM($D137:M137)</f>
+        <v>585511.9456981835</v>
+      </c>
+      <c r="N138" s="56">
+        <f>SUM($D137:N137)</f>
+        <v>607664.4914580917</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="37" t="inlineStr">
+        <is>
+          <t>Аннуитет по году</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>руб/м³</t>
+        </is>
+      </c>
+      <c r="D139" s="66" t="n"/>
+      <c r="E139" s="66">
+        <f>SUM($D137:E137)/SUM($E$6:E$6)/(SUM($E125:E125)/E$4)</f>
+        <v>71.31361949902802</v>
+      </c>
+      <c r="F139" s="66">
+        <f>SUM($D137:F137)/SUM($E$6:F$6)/(SUM($E125:F125)/F$4)</f>
+        <v>45.65838924539084</v>
+      </c>
+      <c r="G139" s="66">
+        <f>SUM($D137:G137)/SUM($E$6:G$6)/(SUM($E125:G125)/G$4)</f>
+        <v>42.217902867298015</v>
+      </c>
+      <c r="H139" s="66">
+        <f>SUM($D137:H137)/SUM($E$6:H$6)/(SUM($E125:H125)/H$4)</f>
+        <v>36.73791163291093</v>
+      </c>
+      <c r="I139" s="66">
+        <f>SUM($D137:I137)/SUM($E$6:I$6)/(SUM($E125:I125)/I$4)</f>
+        <v>32.49047283939567</v>
+      </c>
+      <c r="J139" s="66">
+        <f>SUM($D137:J137)/SUM($E$6:J$6)/(SUM($E125:J125)/J$4)</f>
+        <v>33.81240884091861</v>
+      </c>
+      <c r="K139" s="66">
+        <f>SUM($D137:K137)/SUM($E$6:K$6)/(SUM($E125:K125)/K$4)</f>
+        <v>31.696238261529164</v>
+      </c>
+      <c r="L139" s="66">
+        <f>SUM($D137:L137)/SUM($E$6:L$6)/(SUM($E125:L125)/L$4)</f>
+        <v>30.99088877994659</v>
+      </c>
+      <c r="M139" s="66">
+        <f>SUM($D137:M137)/SUM($E$6:M$6)/(SUM($E125:M125)/M$4)</f>
+        <v>31.334635188880583</v>
+      </c>
+      <c r="N139" s="66">
+        <f>SUM($D137:N137)/SUM($E$6:N$6)/(SUM($E125:N125)/N$4)</f>
+        <v>30.87160394612582</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B46:N46"/>
     <mergeCell ref="B84:N84"/>
+    <mergeCell ref="B122:N122"/>
     <mergeCell ref="B27:N27"/>
     <mergeCell ref="B1:N1"/>
     <mergeCell ref="B8:N8"/>
@@ -12727,7 +18616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12745,6 +18634,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12819,6 +18709,11 @@
         <v>TZCO TZ2000
 Дзикай</v>
       </c>
+      <c r="J4" s="15" t="str">
+        <f>'Ввод данных'!J7</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="inlineStr">
@@ -12869,6 +18764,10 @@
         <f>SUMPRODUCT('Денежный поток'!E107:N107,'Денежный поток'!$E$6:$N$6)</f>
         <v>153107.74073754784</v>
       </c>
+      <c r="J6" s="56">
+        <f>SUMPRODUCT('Денежный поток'!E126:N126,'Денежный поток'!$E$6:$N$6)</f>
+        <v>156499.01921601032</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
@@ -12905,6 +18804,10 @@
         <f>SUMPRODUCT('Денежный поток'!E108:N108,'Денежный поток'!$E$6:$N$6)</f>
         <v>120242.34500982112</v>
       </c>
+      <c r="J7" s="56">
+        <f>SUMPRODUCT('Денежный поток'!E127:N127,'Денежный поток'!$E$6:$N$6)</f>
+        <v>358863.0772724765</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
@@ -12941,6 +18844,10 @@
         <f>SUMPRODUCT('Денежный поток'!E109:N109,'Денежный поток'!$E$6:$N$6)</f>
         <v>10764.188899449604</v>
       </c>
+      <c r="J8" s="56">
+        <f>SUMPRODUCT('Денежный поток'!E128:N128,'Денежный поток'!$E$6:$N$6)</f>
+        <v>17310.775595622057</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
@@ -12977,6 +18884,10 @@
         <f>SUMPRODUCT('Денежный поток'!E110:N110,'Денежный поток'!$E$6:$N$6)</f>
         <v>56586.983629534785</v>
       </c>
+      <c r="J9" s="56">
+        <f>SUMPRODUCT('Денежный поток'!E129:N129,'Денежный поток'!$E$6:$N$6)</f>
+        <v>56586.983629534785</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
@@ -13013,6 +18924,10 @@
         <f>SUMPRODUCT('Денежный поток'!E114:N114,'Денежный поток'!$E$6:$N$6)</f>
         <v>-115977.7104045313</v>
       </c>
+      <c r="J10" s="56">
+        <f>SUMPRODUCT('Денежный поток'!E133:N133,'Денежный поток'!$E$6:$N$6)</f>
+        <v>-183317.76425555206</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
@@ -13049,6 +18964,10 @@
         <f>'Производительность'!I5*(1-'Ввод данных'!I14*'Денежный поток'!$N$6)</f>
         <v>172584.72</v>
       </c>
+      <c r="J11" s="56">
+        <f>'Производительность'!J5*(1-'Ввод данных'!J14*'Денежный поток'!$N$6)</f>
+        <v>201722.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="55" t="inlineStr">
@@ -13085,6 +19004,10 @@
         <f>I6+I7+I8+I9+I10</f>
         <v>224723.54787182205</v>
       </c>
+      <c r="J12" s="65">
+        <f>J6+J7+J8+J9+J10</f>
+        <v>405942.0914580916</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="37" t="inlineStr">
@@ -13121,6 +19044,10 @@
         <f>I11+I12</f>
         <v>397308.26787182206</v>
       </c>
+      <c r="J13" s="60">
+        <f>J11+J12</f>
+        <v>607664.4914580917</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
@@ -13156,6 +19083,10 @@
       <c r="I14" s="56">
         <f>AVERAGE('Денежный поток'!E106:N106)</f>
         <v>2168.2663158398864</v>
+      </c>
+      <c r="J14" s="56">
+        <f>AVERAGE('Денежный поток'!E125:N125)</f>
+        <v>3483.686571582347</v>
       </c>
     </row>
     <row r="15">
@@ -13207,6 +19138,10 @@
         <f>I11/'Параметры'!C37/I14</f>
         <v>14.087182092357084</v>
       </c>
+      <c r="J16" s="57">
+        <f>J11/'Параметры'!C37/J14</f>
+        <v>10.248244100818015</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="22" t="inlineStr">
@@ -13243,6 +19178,10 @@
         <f>I6/'Параметры'!C37/I14</f>
         <v>12.497378814991473</v>
       </c>
+      <c r="J17" s="57">
+        <f>J6/'Параметры'!C37/J14</f>
+        <v>7.950729073540087</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="22" t="inlineStr">
@@ -13279,6 +19218,10 @@
         <f>I7/'Параметры'!C37/I14</f>
         <v>9.814749587132479</v>
       </c>
+      <c r="J18" s="57">
+        <f>J7/'Параметры'!C37/J14</f>
+        <v>18.231571777150464</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="22" t="inlineStr">
@@ -13315,6 +19258,10 @@
         <f>I8/'Параметры'!C37/I14</f>
         <v>0.8786240699818348</v>
       </c>
+      <c r="J19" s="57">
+        <f>J8/'Параметры'!C37/J14</f>
+        <v>0.8794514336455357</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
@@ -13351,6 +19298,10 @@
         <f>I9/'Параметры'!C37/I14</f>
         <v>4.618897562000193</v>
       </c>
+      <c r="J20" s="57">
+        <f>J9/'Параметры'!C37/J14</f>
+        <v>2.8748280863427436</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="22" t="inlineStr">
@@ -13387,6 +19338,10 @@
         <f>I10/'Параметры'!C37/I14</f>
         <v>-9.466649916187768</v>
       </c>
+      <c r="J21" s="57">
+        <f>J10/'Параметры'!C37/J14</f>
+        <v>-9.31322052537105</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="55" t="inlineStr">
@@ -13423,6 +19378,10 @@
         <f>I12/'Параметры'!C37/I14</f>
         <v>18.343000117918216</v>
       </c>
+      <c r="J22" s="67">
+        <f>J12/'Параметры'!C37/J14</f>
+        <v>20.623359845307785</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="37" t="inlineStr">
@@ -13458,6 +19417,10 @@
       <c r="I23" s="68">
         <f>I13/'Параметры'!C37/I14</f>
         <v>32.4301822102753</v>
+      </c>
+      <c r="J23" s="68">
+        <f>J13/'Параметры'!C37/J14</f>
+        <v>30.8716039461258</v>
       </c>
     </row>
     <row r="24">
@@ -13509,6 +19472,10 @@
         <f>I23/'Параметры'!C27</f>
         <v>11.636233301139326</v>
       </c>
+      <c r="J25" s="67">
+        <f>J23/'Параметры'!C27</f>
+        <v>11.07700177471324</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="22" t="inlineStr">
@@ -13545,6 +19512,10 @@
         <f>AVERAGE('Денежный поток'!E111:N111)/I14</f>
         <v>29.68450517817219</v>
       </c>
+      <c r="J26" s="57">
+        <f>AVERAGE('Денежный поток'!E130:N130)/J14</f>
+        <v>30.677880796959396</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="22" t="inlineStr">
@@ -13580,6 +19551,10 @@
       <c r="I27" s="59">
         <f>I16/I23</f>
         <v>0.4343849196102774</v>
+      </c>
+      <c r="J27" s="59">
+        <f>J16/J23</f>
+        <v>0.3319634483100483</v>
       </c>
     </row>
   </sheetData>
@@ -13594,7 +19569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13612,6 +19587,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13686,6 +19662,11 @@
         <v>TZCO TZ2000
 Дзикай</v>
       </c>
+      <c r="J4" s="15" t="str">
+        <f>'Ввод данных'!J7</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
@@ -13722,6 +19703,10 @@
         <f>'Производительность'!I5</f>
         <v>172584.72</v>
       </c>
+      <c r="J5" s="56">
+        <f>'Производительность'!J5</f>
+        <v>201722.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="22" t="inlineStr">
@@ -13758,6 +19743,10 @@
         <f>'Расчёт аннуитета'!I14</f>
         <v>2168.2663158398864</v>
       </c>
+      <c r="J6" s="56">
+        <f>'Расчёт аннуитета'!J14</f>
+        <v>3483.686571582347</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
@@ -13794,6 +19783,10 @@
         <f>'Производительность'!I13</f>
         <v>0.5387869555164468</v>
       </c>
+      <c r="J7" s="59">
+        <f>'Производительность'!J13</f>
+        <v>0.5768024638508371</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
@@ -13830,6 +19823,10 @@
         <f>'Расчёт аннуитета'!I13</f>
         <v>397308.26787182206</v>
       </c>
+      <c r="J8" s="56">
+        <f>'Расчёт аннуитета'!J13</f>
+        <v>607664.4914580917</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
@@ -13866,6 +19863,10 @@
         <f>'Расчёт аннуитета'!I26</f>
         <v>29.68450517817219</v>
       </c>
+      <c r="J9" s="57">
+        <f>'Расчёт аннуитета'!J26</f>
+        <v>30.677880796959396</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
@@ -13902,6 +19903,10 @@
         <f>'Расчёт аннуитета'!I16</f>
         <v>14.087182092357084</v>
       </c>
+      <c r="J10" s="57">
+        <f>'Расчёт аннуитета'!J16</f>
+        <v>10.248244100818015</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
@@ -13938,6 +19943,10 @@
         <f>'Расчёт аннуитета'!I22</f>
         <v>18.343000117918216</v>
       </c>
+      <c r="J11" s="57">
+        <f>'Расчёт аннуитета'!J22</f>
+        <v>20.623359845307785</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="55" t="inlineStr">
@@ -13974,6 +19983,10 @@
         <f>'Расчёт аннуитета'!I23</f>
         <v>32.4301822102753</v>
       </c>
+      <c r="J12" s="69">
+        <f>'Расчёт аннуитета'!J23</f>
+        <v>30.8716039461258</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
@@ -14009,6 +20022,10 @@
       <c r="I13" s="57">
         <f>'Расчёт аннуитета'!I25</f>
         <v>11.636233301139326</v>
+      </c>
+      <c r="J13" s="57">
+        <f>'Расчёт аннуитета'!J25</f>
+        <v>11.07700177471324</v>
       </c>
     </row>
     <row r="14">
@@ -14032,27 +20049,31 @@
         </is>
       </c>
       <c r="D15" s="18">
-        <f>RANK(D12,D12:I12,1)</f>
+        <f>RANK(D12,D12:J12,1)</f>
+        <v>6.0</v>
+      </c>
+      <c r="E15" s="18">
+        <f>RANK(E12,D12:J12,1)</f>
         <v>5.0</v>
       </c>
-      <c r="E15" s="18">
-        <f>RANK(E12,D12:I12,1)</f>
+      <c r="F15" s="18">
+        <f>RANK(F12,D12:J12,1)</f>
         <v>4.0</v>
       </c>
-      <c r="F15" s="18">
-        <f>RANK(F12,D12:I12,1)</f>
+      <c r="G15" s="18">
+        <f>RANK(G12,D12:J12,1)</f>
         <v>3.0</v>
       </c>
-      <c r="G15" s="18">
-        <f>RANK(G12,D12:I12,1)</f>
+      <c r="H15" s="18">
+        <f>RANK(H12,D12:J12,1)</f>
+        <v>7.0</v>
+      </c>
+      <c r="I15" s="18">
+        <f>RANK(I12,D12:J12,1)</f>
         <v>2.0</v>
       </c>
-      <c r="H15" s="18">
-        <f>RANK(H12,D12:I12,1)</f>
-        <v>6.0</v>
-      </c>
-      <c r="I15" s="18">
-        <f>RANK(I12,D12:I12,1)</f>
+      <c r="J15" s="18">
+        <f>RANK(J12,D12:J12,1)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -14063,27 +20084,31 @@
         </is>
       </c>
       <c r="D16" s="72">
-        <f>D12/MIN(D12:I12)-1</f>
-        <v>1.0935597171867815</v>
+        <f>D12/MIN(D12:J12)-1</f>
+        <v>1.1992547978700054</v>
       </c>
       <c r="E16" s="72">
-        <f>E12/MIN(D12:I12)-1</f>
-        <v>0.5017725078628701</v>
+        <f>E12/MIN(D12:J12)-1</f>
+        <v>0.5775907255536967</v>
       </c>
       <c r="F16" s="72">
-        <f>F12/MIN(D12:I12)-1</f>
-        <v>0.44364566239117087</v>
+        <f>F12/MIN(D12:J12)-1</f>
+        <v>0.516529298578754</v>
       </c>
       <c r="G16" s="72">
-        <f>G12/MIN(D12:I12)-1</f>
-        <v>0.43457744693735423</v>
+        <f>G12/MIN(D12:J12)-1</f>
+        <v>0.507003266824702</v>
       </c>
       <c r="H16" s="72">
-        <f>H12/MIN(D12:I12)-1</f>
-        <v>3.532304630518688</v>
+        <f>H12/MIN(D12:J12)-1</f>
+        <v>3.7611217498351284</v>
       </c>
       <c r="I16" s="72">
-        <f>I12/MIN(D12:I12)-1</f>
+        <f>I12/MIN(D12:J12)-1</f>
+        <v>0.0504858207843486</v>
+      </c>
+      <c r="J16" s="72">
+        <f>J12/MIN(D12:J12)-1</f>
         <v>0.0</v>
       </c>
     </row>
@@ -14094,9 +20119,9 @@
         </is>
       </c>
       <c r="C18" s="74" t="str">
-        <f>INDEX(D4:I4,MATCH(MIN(D12:I12),D12:I12,0))&amp;"  ("&amp;TEXT(MIN(D12:I12),"0.00")&amp;" руб/м³)"</f>
-        <v>TZCO TZ2000
-Дзикай  (32.43 руб/м³)</v>
+        <f>INDEX(D4:J4,MATCH(MIN(D12:J12),D12:J12,0))&amp;"  ("&amp;TEXT(MIN(D12:J12),"0.00")&amp;" руб/м³)"</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)  (30.87 руб/м³)</v>
       </c>
       <c r="D18" s="75" t="n"/>
       <c r="E18" s="75" t="n"/>
@@ -14154,6 +20179,11 @@
         <v>TZCO TZ2000
 Дзикай</v>
       </c>
+      <c r="J21" s="15" t="str">
+        <f>'Ввод данных'!J7</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
@@ -14185,6 +20215,10 @@
         <f>'Расчёт аннуитета'!I16</f>
         <v>14.087182092357084</v>
       </c>
+      <c r="J22" s="57">
+        <f>'Расчёт аннуитета'!J16</f>
+        <v>10.248244100818015</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="22" t="inlineStr">
@@ -14216,6 +20250,10 @@
         <f>'Расчёт аннуитета'!I17</f>
         <v>12.497378814991473</v>
       </c>
+      <c r="J23" s="57">
+        <f>'Расчёт аннуитета'!J17</f>
+        <v>7.950729073540087</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="22" t="inlineStr">
@@ -14247,6 +20285,10 @@
         <f>'Расчёт аннуитета'!I18</f>
         <v>9.814749587132479</v>
       </c>
+      <c r="J24" s="57">
+        <f>'Расчёт аннуитета'!J18</f>
+        <v>18.231571777150464</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="22" t="inlineStr">
@@ -14278,6 +20320,10 @@
         <f>'Расчёт аннуитета'!I19</f>
         <v>0.8786240699818348</v>
       </c>
+      <c r="J25" s="57">
+        <f>'Расчёт аннуитета'!J19</f>
+        <v>0.8794514336455357</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="22" t="inlineStr">
@@ -14309,6 +20355,10 @@
         <f>'Расчёт аннуитета'!I20</f>
         <v>4.618897562000193</v>
       </c>
+      <c r="J26" s="57">
+        <f>'Расчёт аннуитета'!J20</f>
+        <v>2.8748280863427436</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="22" t="inlineStr">
@@ -14340,21 +20390,25 @@
         <f>'Расчёт аннуитета'!I21</f>
         <v>-9.466649916187768</v>
       </c>
+      <c r="J27" s="57">
+        <f>'Расчёт аннуитета'!J21</f>
+        <v>-9.31322052537105</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:K1"/>
-    <mergeCell ref="C18:I18"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="B2:K2"/>
+    <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14372,6 +20426,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14446,6 +20501,11 @@
         <v>TZCO TZ2000
 Дзикай</v>
       </c>
+      <c r="J4" s="15" t="str">
+        <f>'Ввод данных'!J7</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="inlineStr">
@@ -14496,6 +20556,10 @@
         <f>'Производительность'!I5</f>
         <v>172584.72</v>
       </c>
+      <c r="J6" s="56">
+        <f>'Производительность'!J5</f>
+        <v>201722.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
@@ -14532,6 +20596,10 @@
         <f>'Расчёт аннуитета'!I14</f>
         <v>2168.2663158398864</v>
       </c>
+      <c r="J7" s="56">
+        <f>'Расчёт аннуитета'!J14</f>
+        <v>3483.686571582347</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
@@ -14568,6 +20636,10 @@
         <f>AVERAGE('Данные по годам'!E32:N32)</f>
         <v>0.7384420662100457</v>
       </c>
+      <c r="J8" s="59">
+        <f>AVERAGE('Данные по годам'!E37:N37)</f>
+        <v>0.8618150684931507</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="37" t="inlineStr">
@@ -14604,6 +20676,10 @@
         <f>'Расчёт аннуитета'!I23</f>
         <v>32.4301822102753</v>
       </c>
+      <c r="J9" s="68">
+        <f>'Расчёт аннуитета'!J23</f>
+        <v>30.8716039461258</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
@@ -14640,6 +20716,10 @@
         <f>'Расчёт аннуитета'!I25</f>
         <v>11.636233301139326</v>
       </c>
+      <c r="J10" s="57">
+        <f>'Расчёт аннуитета'!J25</f>
+        <v>11.07700177471324</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
@@ -14676,6 +20756,10 @@
         <f>'Расчёт аннуитета'!I13</f>
         <v>397308.26787182206</v>
       </c>
+      <c r="J11" s="56">
+        <f>'Расчёт аннуитета'!J13</f>
+        <v>607664.4914580917</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
@@ -14712,6 +20796,10 @@
         <f>'Расчёт аннуитета'!I16/'Расчёт аннуитета'!I23</f>
         <v>0.4343849196102774</v>
       </c>
+      <c r="J12" s="59">
+        <f>'Расчёт аннуитета'!J16/'Расчёт аннуитета'!J23</f>
+        <v>0.3319634483100483</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
@@ -14748,6 +20836,10 @@
         <f>'Расчёт аннуитета'!I17/'Расчёт аннуитета'!I23</f>
         <v>0.3853625839645069</v>
       </c>
+      <c r="J13" s="59">
+        <f>'Расчёт аннуитета'!J17/'Расчёт аннуитета'!J23</f>
+        <v>0.2575418202246617</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
@@ -14784,6 +20876,10 @@
         <f>'Расчёт аннуитета'!I18/'Расчёт аннуитета'!I23</f>
         <v>0.30264244349582275</v>
       </c>
+      <c r="J14" s="59">
+        <f>'Расчёт аннуитета'!J18/'Расчёт аннуитета'!J23</f>
+        <v>0.590561209873205</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="37" t="inlineStr">
@@ -14793,27 +20889,31 @@
       </c>
       <c r="C15" s="24" t="inlineStr"/>
       <c r="D15" s="60">
-        <f>RANK(D9,D9:I9,1)</f>
+        <f>RANK(D9,D9:J9,1)</f>
+        <v>6.0</v>
+      </c>
+      <c r="E15" s="60">
+        <f>RANK(E9,D9:J9,1)</f>
         <v>5.0</v>
       </c>
-      <c r="E15" s="60">
-        <f>RANK(E9,D9:I9,1)</f>
+      <c r="F15" s="60">
+        <f>RANK(F9,D9:J9,1)</f>
         <v>4.0</v>
       </c>
-      <c r="F15" s="60">
-        <f>RANK(F9,D9:I9,1)</f>
+      <c r="G15" s="60">
+        <f>RANK(G9,D9:J9,1)</f>
         <v>3.0</v>
       </c>
-      <c r="G15" s="60">
-        <f>RANK(G9,D9:I9,1)</f>
+      <c r="H15" s="60">
+        <f>RANK(H9,D9:J9,1)</f>
+        <v>7.0</v>
+      </c>
+      <c r="I15" s="60">
+        <f>RANK(I9,D9:J9,1)</f>
         <v>2.0</v>
       </c>
-      <c r="H15" s="60">
-        <f>RANK(H9,D9:I9,1)</f>
-        <v>6.0</v>
-      </c>
-      <c r="I15" s="60">
-        <f>RANK(I9,D9:I9,1)</f>
+      <c r="J15" s="60">
+        <f>RANK(J9,D9:J9,1)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -14843,28 +20943,32 @@
         </is>
       </c>
       <c r="D17" s="57">
-        <f>'Расчёт аннуитета'!D16-MIN(D16:I16)</f>
+        <f>'Расчёт аннуитета'!D16-MIN(D16:J16)</f>
         <v>25.44574682280948</v>
       </c>
       <c r="E17" s="57">
-        <f>'Расчёт аннуитета'!E16-MIN(D16:I16)</f>
+        <f>'Расчёт аннуитета'!E16-MIN(D16:J16)</f>
         <v>23.68323572771956</v>
       </c>
       <c r="F17" s="57">
-        <f>'Расчёт аннуитета'!F16-MIN(D16:I16)</f>
+        <f>'Расчёт аннуитета'!F16-MIN(D16:J16)</f>
         <v>22.57046943816774</v>
       </c>
       <c r="G17" s="57">
-        <f>'Расчёт аннуитета'!G16-MIN(D16:I16)</f>
+        <f>'Расчёт аннуитета'!G16-MIN(D16:J16)</f>
         <v>22.001548737510106</v>
       </c>
       <c r="H17" s="57">
-        <f>'Расчёт аннуитета'!H16-MIN(D16:I16)</f>
+        <f>'Расчёт аннуитета'!H16-MIN(D16:J16)</f>
         <v>18.772712397897372</v>
       </c>
       <c r="I17" s="57">
-        <f>'Расчёт аннуитета'!I16-MIN(D16:I16)</f>
+        <f>'Расчёт аннуитета'!I16-MIN(D16:J16)</f>
         <v>14.087182092357084</v>
+      </c>
+      <c r="J17" s="57">
+        <f>'Расчёт аннуитета'!J16-MIN(D16:J16)</f>
+        <v>10.248244100818015</v>
       </c>
     </row>
     <row r="18">
@@ -14879,28 +20983,32 @@
         </is>
       </c>
       <c r="D18" s="57">
-        <f>'Расчёт аннуитета'!D17-MIN(D17:I17)</f>
-        <v>-2.7247825636492493</v>
+        <f>'Расчёт аннуитета'!D17-MIN(D17:J17)</f>
+        <v>1.1141554278898198</v>
       </c>
       <c r="E18" s="57">
-        <f>'Расчёт аннуитета'!E17-MIN(D17:I17)</f>
-        <v>-3.141970177652503</v>
+        <f>'Расчёт аннуитета'!E17-MIN(D17:J17)</f>
+        <v>0.696967813886566</v>
       </c>
       <c r="F18" s="57">
-        <f>'Расчёт аннуитета'!F17-MIN(D17:I17)</f>
-        <v>-2.5684777783171366</v>
+        <f>'Расчёт аннуитета'!F17-MIN(D17:J17)</f>
+        <v>1.2704602132219325</v>
       </c>
       <c r="G18" s="57">
-        <f>'Расчёт аннуитета'!G17-MIN(D17:I17)</f>
-        <v>-2.337414331476703</v>
+        <f>'Расчёт аннуитета'!G17-MIN(D17:J17)</f>
+        <v>1.5015236600623663</v>
       </c>
       <c r="H18" s="57">
-        <f>'Расчёт аннуитета'!H17-MIN(D17:I17)</f>
-        <v>-1.0659270770398468</v>
+        <f>'Расчёт аннуитета'!H17-MIN(D17:J17)</f>
+        <v>2.7730109144992223</v>
       </c>
       <c r="I18" s="57">
-        <f>'Расчёт аннуитета'!I17-MIN(D17:I17)</f>
-        <v>-1.5898032773656112</v>
+        <f>'Расчёт аннуитета'!I17-MIN(D17:J17)</f>
+        <v>2.249134714173458</v>
+      </c>
+      <c r="J18" s="57">
+        <f>'Расчёт аннуитета'!J17-MIN(D17:J17)</f>
+        <v>-2.297515027277928</v>
       </c>
     </row>
     <row r="19">
@@ -14915,28 +21023,32 @@
         </is>
       </c>
       <c r="D19" s="57">
-        <f>'Расчёт аннуитета'!D18-MIN(D18:I18)</f>
-        <v>48.57164424746767</v>
+        <f>'Расчёт аннуитета'!D18-MIN(D18:J18)</f>
+        <v>47.72718909709309</v>
       </c>
       <c r="E19" s="57">
-        <f>'Расчёт аннуитета'!E18-MIN(D18:I18)</f>
-        <v>25.138796252655954</v>
+        <f>'Расчёт аннуитета'!E18-MIN(D18:J18)</f>
+        <v>24.29434110228138</v>
       </c>
       <c r="F19" s="57">
-        <f>'Расчёт аннуитета'!F18-MIN(D18:I18)</f>
-        <v>22.78356577829662</v>
+        <f>'Расчёт аннуитета'!F18-MIN(D18:J18)</f>
+        <v>21.939110627922044</v>
       </c>
       <c r="G19" s="57">
-        <f>'Расчёт аннуитета'!G18-MIN(D18:I18)</f>
-        <v>22.78356577829662</v>
+        <f>'Расчёт аннуитета'!G18-MIN(D18:J18)</f>
+        <v>21.939110627922044</v>
       </c>
       <c r="H19" s="57">
-        <f>'Расчёт аннуитета'!H18-MIN(D18:I18)</f>
-        <v>158.99530579435222</v>
+        <f>'Расчёт аннуитета'!H18-MIN(D18:J18)</f>
+        <v>158.15085064397766</v>
       </c>
       <c r="I19" s="57">
-        <f>'Расчёт аннуитета'!I18-MIN(D18:I18)</f>
-        <v>12.956719764784982</v>
+        <f>'Расчёт аннуитета'!I18-MIN(D18:J18)</f>
+        <v>12.112264614410407</v>
+      </c>
+      <c r="J19" s="57">
+        <f>'Расчёт аннуитета'!J18-MIN(D18:J18)</f>
+        <v>20.529086804428392</v>
       </c>
     </row>
     <row r="20">
@@ -14951,27 +21063,31 @@
         </is>
       </c>
       <c r="D20" s="57">
-        <f>'Расчёт аннуитета'!D20-MIN(D20:I20)</f>
+        <f>'Расчёт аннуитета'!D20-MIN(D20:J20)</f>
         <v/>
       </c>
       <c r="E20" s="57">
-        <f>'Расчёт аннуитета'!E20-MIN(D20:I20)</f>
+        <f>'Расчёт аннуитета'!E20-MIN(D20:J20)</f>
         <v/>
       </c>
       <c r="F20" s="57">
-        <f>'Расчёт аннуитета'!F20-MIN(D20:I20)</f>
+        <f>'Расчёт аннуитета'!F20-MIN(D20:J20)</f>
         <v/>
       </c>
       <c r="G20" s="57">
-        <f>'Расчёт аннуитета'!G20-MIN(D20:I20)</f>
+        <f>'Расчёт аннуитета'!G20-MIN(D20:J20)</f>
         <v/>
       </c>
       <c r="H20" s="57">
-        <f>'Расчёт аннуитета'!H20-MIN(D20:I20)</f>
+        <f>'Расчёт аннуитета'!H20-MIN(D20:J20)</f>
         <v/>
       </c>
       <c r="I20" s="57">
-        <f>'Расчёт аннуитета'!I20-MIN(D20:I20)</f>
+        <f>'Расчёт аннуитета'!I20-MIN(D20:J20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="57">
+        <f>'Расчёт аннуитета'!J20-MIN(D20:J20)</f>
         <v/>
       </c>
     </row>
@@ -14987,27 +21103,31 @@
         </is>
       </c>
       <c r="D21" s="57">
-        <f>'Расчёт аннуитета'!D21-MIN(D21:I21)</f>
+        <f>'Расчёт аннуитета'!D21-MIN(D21:J21)</f>
         <v/>
       </c>
       <c r="E21" s="57">
-        <f>'Расчёт аннуитета'!E21-MIN(D21:I21)</f>
+        <f>'Расчёт аннуитета'!E21-MIN(D21:J21)</f>
         <v/>
       </c>
       <c r="F21" s="57">
-        <f>'Расчёт аннуитета'!F21-MIN(D21:I21)</f>
+        <f>'Расчёт аннуитета'!F21-MIN(D21:J21)</f>
         <v/>
       </c>
       <c r="G21" s="57">
-        <f>'Расчёт аннуитета'!G21-MIN(D21:I21)</f>
+        <f>'Расчёт аннуитета'!G21-MIN(D21:J21)</f>
         <v/>
       </c>
       <c r="H21" s="57">
-        <f>'Расчёт аннуитета'!H21-MIN(D21:I21)</f>
+        <f>'Расчёт аннуитета'!H21-MIN(D21:J21)</f>
         <v/>
       </c>
       <c r="I21" s="57">
-        <f>'Расчёт аннуитета'!I21-MIN(D21:I21)</f>
+        <f>'Расчёт аннуитета'!I21-MIN(D21:J21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="57">
+        <f>'Расчёт аннуитета'!J21-MIN(D21:J21)</f>
         <v/>
       </c>
     </row>
@@ -15023,27 +21143,31 @@
         </is>
       </c>
       <c r="D22" s="68">
-        <f>D9-MIN(D9:I9)</f>
-        <v>35.46434088618445</v>
+        <f>D9-MIN(D9:J9)</f>
+        <v>37.02291915033395</v>
       </c>
       <c r="E22" s="68">
-        <f>E9-MIN(D9:I9)</f>
-        <v>16.27257385809967</v>
+        <f>E9-MIN(D9:J9)</f>
+        <v>17.83115212224917</v>
       </c>
       <c r="F22" s="68">
-        <f>F9-MIN(D9:I9)</f>
-        <v>14.387509668143949</v>
+        <f>F9-MIN(D9:J9)</f>
+        <v>15.946087932293448</v>
       </c>
       <c r="G22" s="68">
-        <f>G9-MIN(D9:I9)</f>
-        <v>14.093425788654642</v>
+        <f>G9-MIN(D9:J9)</f>
+        <v>15.652004052804141</v>
       </c>
       <c r="H22" s="68">
-        <f>H9-MIN(D9:I9)</f>
-        <v>114.55328278992022</v>
+        <f>H9-MIN(D9:J9)</f>
+        <v>116.1118610540697</v>
       </c>
       <c r="I22" s="68">
-        <f>I9-MIN(D9:I9)</f>
+        <f>I9-MIN(D9:J9)</f>
+        <v>1.5585782641494994</v>
+      </c>
+      <c r="J22" s="68">
+        <f>J9-MIN(D9:J9)</f>
         <v>0.0</v>
       </c>
     </row>
@@ -15096,6 +21220,10 @@
         <f>('Расчёт аннуитета'!I16+'Расчёт аннуитета'!I18+'Расчёт аннуитета'!I20+'Расчёт аннуитета'!I21)/1.1+('Расчёт аннуитета'!I17+'Расчёт аннуитета'!I19)-0.2*'Расчёт аннуитета'!I17</f>
         <v>28.198508326795</v>
       </c>
+      <c r="J24" s="57">
+        <f>('Расчёт аннуитета'!J16+'Расчёт аннуитета'!J18+'Расчёт аннуитета'!J20+'Расчёт аннуитета'!J21)/1.1+('Расчёт аннуитета'!J17+'Расчёт аннуитета'!J19)-0.2*'Расчёт аннуитета'!J17</f>
+        <v>27.277692364241396</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="37" t="inlineStr">
@@ -15132,6 +21260,10 @@
         <f>'Расчёт аннуитета'!I23</f>
         <v>32.4301822102753</v>
       </c>
+      <c r="J25" s="68">
+        <f>'Расчёт аннуитета'!J23</f>
+        <v>30.8716039461258</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="22" t="inlineStr">
@@ -15168,6 +21300,10 @@
         <f>('Расчёт аннуитета'!I16+'Расчёт аннуитета'!I18+'Расчёт аннуитета'!I20+'Расчёт аннуитета'!I21)/0.9+('Расчёт аннуитета'!I17+'Расчёт аннуитета'!I19)+0.2*'Расчёт аннуитета'!I17</f>
         <v>37.046789009418255</v>
       </c>
+      <c r="J26" s="57">
+        <f>('Расчёт аннуитета'!J16+'Расчёт аннуитета'!J18+'Расчёт аннуитета'!J20+'Расчёт аннуитета'!J21)/0.9+('Расчёт аннуитета'!J17+'Расчёт аннуитета'!J19)+0.2*'Расчёт аннуитета'!J17</f>
+        <v>34.91079680960494</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="22" t="inlineStr">
@@ -15203,6 +21339,10 @@
       <c r="I27" s="57">
         <f>I26-I24</f>
         <v>8.848280682623255</v>
+      </c>
+      <c r="J27" s="57">
+        <f>J26-J24</f>
+        <v>7.633104445363543</v>
       </c>
     </row>
     <row r="28">
@@ -15254,6 +21394,10 @@
         <f>'Расчёт аннуитета'!I17/'Параметры'!C10</f>
         <v>0.22792957897121052</v>
       </c>
+      <c r="J29" s="57">
+        <f>'Расчёт аннуитета'!J17/'Параметры'!C10</f>
+        <v>0.14500691361554052</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="22" t="inlineStr">
@@ -15290,6 +21434,10 @@
         <f>'Расчёт аннуитета'!I17</f>
         <v>12.497378814991473</v>
       </c>
+      <c r="J30" s="57">
+        <f>'Расчёт аннуитета'!J17</f>
+        <v>7.950729073540087</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="22" t="inlineStr">
@@ -15326,6 +21474,10 @@
         <f>-('Расчёт аннуитета'!I16+'Расчёт аннуитета'!I18+'Расчёт аннуитета'!I20+'Расчёт аннуитета'!I21)*0.01/AVERAGE('Данные по годам'!E32:N32)</f>
         <v>-0.25803214899572274</v>
       </c>
+      <c r="J31" s="57">
+        <f>-('Расчёт аннуитета'!J16+'Расчёт аннуитета'!J18+'Расчёт аннуитета'!J20+'Расчёт аннуитета'!J21)*0.01/AVERAGE('Данные по годам'!E37:N37)</f>
+        <v>-0.2557558372410304</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="73" t="inlineStr">
@@ -15334,9 +21486,9 @@
         </is>
       </c>
       <c r="C33" s="77" t="str">
-        <f>"Лучший по удельному TCO: "&amp;INDEX(D4:I4,MATCH(MIN(D9:I9),D9:I9,0))&amp;" ("&amp;TEXT(MIN(D9:I9),"0.00")&amp;" руб/м³, "&amp;TEXT(MIN(D10:I10),"0.00")&amp;" руб/т). "&amp;"Отрыв от худшего: "&amp;TEXT(MAX(D9:I9)-MIN(D9:I9),"0.00")&amp;" руб/м³."</f>
-        <v>Лучший по удельному TCO: TZCO TZ2000
-Дзикай (32.43 руб/м³, 11.64 руб/т). Отрыв от худшего: 114.55 руб/м³.</v>
+        <f>"Лучший по удельному TCO: "&amp;INDEX(D4:J4,MATCH(MIN(D9:J9),D9:J9,0))&amp;" ("&amp;TEXT(MIN(D9:J9),"0.00")&amp;" руб/м³, "&amp;TEXT(MIN(D10:J10),"0.00")&amp;" руб/т). "&amp;"Отрыв от худшего: "&amp;TEXT(MAX(D9:J9)-MIN(D9:J9),"0.00")&amp;" руб/м³."</f>
+        <v>Лучший по удельному TCO: XCMG ESTAR ESE2000
+(поставщик не указан) (30.87 руб/м³, 11.08 руб/т). Отрыв от худшего: 116.11 руб/м³.</v>
       </c>
       <c r="D33" s="78" t="n"/>
       <c r="E33" s="78" t="n"/>
@@ -15391,6 +21543,7 @@
   <mergeCells count="12">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B40:K40"/>
+    <mergeCell ref="C33:J33"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B28:I28"/>
     <mergeCell ref="B5:I5"/>
@@ -15398,7 +21551,6 @@
     <mergeCell ref="B38:K38"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="C33:I33"/>
     <mergeCell ref="B36:K36"/>
     <mergeCell ref="B37:K37"/>
   </mergeCells>
@@ -15407,7 +21559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15461,14 +21613,14 @@
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Анализируемый экскаватор (1–6):</t>
+          <t>Анализируемый экскаватор (1–7):</t>
         </is>
       </c>
       <c r="C4" s="36" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="79" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,$C$4)</f>
+        <f>INDEX('Ввод данных'!D7:J7,$C$4)</f>
         <v>Komatsu PC2000-8
 Mining Solutions</v>
       </c>
@@ -15498,7 +21650,7 @@
         </is>
       </c>
       <c r="D7" s="57">
-        <f>INDEX('Расчёт аннуитета'!D23:I23,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D23:J23,$C$4)</f>
         <v>67.89452309645975</v>
       </c>
     </row>
@@ -15514,7 +21666,7 @@
         </is>
       </c>
       <c r="D8" s="57">
-        <f>INDEX('Расчёт аннуитета'!D16:I16,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D16:J16,$C$4)</f>
         <v>25.44574682280948</v>
       </c>
     </row>
@@ -15530,7 +21682,7 @@
         </is>
       </c>
       <c r="D9" s="57">
-        <f>INDEX('Расчёт аннуитета'!D17:I17,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D17:J17,$C$4)</f>
         <v>11.362399528707835</v>
       </c>
     </row>
@@ -15546,7 +21698,7 @@
         </is>
       </c>
       <c r="D10" s="57">
-        <f>INDEX('Расчёт аннуитета'!D18:I18,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D18:J18,$C$4)</f>
         <v>45.429674069815164</v>
       </c>
     </row>
@@ -15562,7 +21714,7 @@
         </is>
       </c>
       <c r="D11" s="57">
-        <f>INDEX('Расчёт аннуитета'!D20:I20,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D20:J20,$C$4)</f>
         <v>4.97755743541268</v>
       </c>
     </row>
@@ -15578,7 +21730,7 @@
         </is>
       </c>
       <c r="D12" s="56">
-        <f>INDEX('Расчёт аннуитета'!D14:I14,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D14:J14,$C$4)</f>
         <v>2012.031027256176</v>
       </c>
     </row>
@@ -15594,7 +21746,7 @@
         </is>
       </c>
       <c r="D13" s="56">
-        <f>INDEX('Производительность'!D5:I5,$C$4)</f>
+        <f>INDEX('Производительность'!D5:J5,$C$4)</f>
         <v>289278.04</v>
       </c>
     </row>
@@ -15610,7 +21762,7 @@
         </is>
       </c>
       <c r="D14" s="57">
-        <f>INDEX('Расчёт аннуитета'!D16:I16,$C$4)+INDEX('Расчёт аннуитета'!D18:I18,$C$4)+INDEX('Расчёт аннуитета'!D20:I20,$C$4)+INDEX('Расчёт аннуитета'!D21:I21,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D16:J16,$C$4)+INDEX('Расчёт аннуитета'!D18:J18,$C$4)+INDEX('Расчёт аннуитета'!D20:J20,$C$4)+INDEX('Расчёт аннуитета'!D21:J21,$C$4)</f>
         <v>55.64808025172029</v>
       </c>
     </row>
@@ -15626,7 +21778,7 @@
         </is>
       </c>
       <c r="D15" s="57">
-        <f>INDEX('Расчёт аннуитета'!D17:I17,$C$4)+INDEX('Расчёт аннуитета'!D19:I19,$C$4)</f>
+        <f>INDEX('Расчёт аннуитета'!D17:J17,$C$4)+INDEX('Расчёт аннуитета'!D19:J19,$C$4)</f>
         <v>12.246442844739455</v>
       </c>
     </row>
@@ -15922,23 +22074,23 @@
         </is>
       </c>
       <c r="C31" s="67">
-        <f>$D$13*(1-INDEX('Ввод данных'!D14:I14,$C$4)/(1+C30)^'Параметры'!C8)/((1-(1+C30)^-'Параметры'!C8)/C30)/$D$12+$D$7-$D$8</f>
+        <f>$D$13*(1-INDEX('Ввод данных'!D14:J14,$C$4)/(1+C30)^'Параметры'!C8)/((1-(1+C30)^-'Параметры'!C8)/C30)/$D$12+$D$7-$D$8</f>
         <v>63.87536354217907</v>
       </c>
       <c r="D31" s="67">
-        <f>$D$13*(1-INDEX('Ввод данных'!D14:I14,$C$4)/(1+D30)^'Параметры'!C8)/((1-(1+D30)^-'Параметры'!C8)/D30)/$D$12+$D$7-$D$8</f>
+        <f>$D$13*(1-INDEX('Ввод данных'!D14:J14,$C$4)/(1+D30)^'Параметры'!C8)/((1-(1+D30)^-'Параметры'!C8)/D30)/$D$12+$D$7-$D$8</f>
         <v>65.84735622241008</v>
       </c>
       <c r="E31" s="69">
-        <f>$D$13*(1-INDEX('Ввод данных'!D14:I14,$C$4)/(1+E30)^'Параметры'!C8)/((1-(1+E30)^-'Параметры'!C8)/E30)/$D$12+$D$7-$D$8</f>
+        <f>$D$13*(1-INDEX('Ввод данных'!D14:J14,$C$4)/(1+E30)^'Параметры'!C8)/((1-(1+E30)^-'Параметры'!C8)/E30)/$D$12+$D$7-$D$8</f>
         <v>67.89452309645975</v>
       </c>
       <c r="F31" s="67">
-        <f>$D$13*(1-INDEX('Ввод данных'!D14:I14,$C$4)/(1+F30)^'Параметры'!C8)/((1-(1+F30)^-'Параметры'!C8)/F30)/$D$12+$D$7-$D$8</f>
+        <f>$D$13*(1-INDEX('Ввод данных'!D14:J14,$C$4)/(1+F30)^'Параметры'!C8)/((1-(1+F30)^-'Параметры'!C8)/F30)/$D$12+$D$7-$D$8</f>
         <v>70.01222663072055</v>
       </c>
       <c r="G31" s="67">
-        <f>$D$13*(1-INDEX('Ввод данных'!D14:I14,$C$4)/(1+G30)^'Параметры'!C8)/((1-(1+G30)^-'Параметры'!C8)/G30)/$D$12+$D$7-$D$8</f>
+        <f>$D$13*(1-INDEX('Ввод данных'!D14:J14,$C$4)/(1+G30)^'Параметры'!C8)/((1-(1+G30)^-'Параметры'!C8)/G30)/$D$12+$D$7-$D$8</f>
         <v>72.19580252353752</v>
       </c>
     </row>
@@ -15963,7 +22115,7 @@
   <dataValidations count="1">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
       <formula1>1</formula1>
-      <formula2>6</formula2>
+      <formula2>7</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15971,7 +22123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16307,7 +22459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:N15"/>
+  <dimension ref="B1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16399,21 +22551,21 @@
     </row>
     <row r="6">
       <c r="B6" s="12" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(MIN('Расчёт аннуитета'!D23:I23),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>TZCO TZ2000
-Дзикай</v>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(MIN('Расчёт аннуитета'!D23:J23),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
       </c>
       <c r="C6" s="13">
-        <f>MIN('Расчёт аннуитета'!D23:I23)</f>
-        <v>32.4301822102753</v>
+        <f>MIN('Расчёт аннуитета'!D23:J23)</f>
+        <v>30.8716039461258</v>
       </c>
       <c r="D6" s="14">
-        <f>MIN('Расчёт аннуитета'!D13:I13)</f>
+        <f>MIN('Расчёт аннуитета'!D13:J13)</f>
         <v>397308.26787182206</v>
       </c>
       <c r="E6" s="13">
-        <f>MAX('Расчёт аннуитета'!D23:I23)-MIN('Расчёт аннуитета'!D23:I23)</f>
-        <v>114.55328278992022</v>
+        <f>MAX('Расчёт аннуитета'!D23:J23)-MIN('Расчёт аннуитета'!D23:J23)</f>
+        <v>116.1118610540697</v>
       </c>
     </row>
     <row r="8">
@@ -16462,17 +22614,17 @@
         <v>1</v>
       </c>
       <c r="C10" s="19" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(SMALL('Расчёт аннуитета'!D23:I23,1),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>TZCO TZ2000
-Дзикай</v>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,1),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>XCMG ESTAR ESE2000
+(поставщик не указан)</v>
       </c>
       <c r="G10" s="20">
-        <f>SMALL('Расчёт аннуитета'!D23:I23,1)</f>
-        <v>32.4301822102753</v>
+        <f>SMALL('Расчёт аннуитета'!D23:J23,1)</f>
+        <v>30.8716039461258</v>
       </c>
       <c r="I10" s="21">
-        <f>INDEX('Расчёт аннуитета'!$D$25:$I$25,MATCH(SMALL('Расчёт аннуитета'!D23:I23,1),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>11.636233301139326</v>
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,1),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>11.07700177471324</v>
       </c>
     </row>
     <row r="11">
@@ -16480,17 +22632,17 @@
         <v>2</v>
       </c>
       <c r="C11" s="22" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(SMALL('Расчёт аннуитета'!D23:I23,2),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>Sany SY2000
-АСТ</v>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,2),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>TZCO TZ2000
+Дзикай</v>
       </c>
       <c r="G11" s="21">
-        <f>SMALL('Расчёт аннуитета'!D23:I23,2)</f>
-        <v>46.52360799892994</v>
+        <f>SMALL('Расчёт аннуитета'!D23:J23,2)</f>
+        <v>32.4301822102753</v>
       </c>
       <c r="I11" s="21">
-        <f>INDEX('Расчёт аннуитета'!$D$25:$I$25,MATCH(SMALL('Расчёт аннуитета'!D23:I23,2),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>16.693077861115874</v>
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,2),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>11.636233301139326</v>
       </c>
     </row>
     <row r="12">
@@ -16498,17 +22650,17 @@
         <v>3</v>
       </c>
       <c r="C12" s="22" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(SMALL('Расчёт аннуитета'!D23:I23,3),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>Zoomlion ZE2000G
-Орикс</v>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,3),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>Sany SY2000
+АСТ</v>
       </c>
       <c r="G12" s="21">
-        <f>SMALL('Расчёт аннуитета'!D23:I23,3)</f>
-        <v>46.81769187841925</v>
+        <f>SMALL('Расчёт аннуитета'!D23:J23,3)</f>
+        <v>46.52360799892994</v>
       </c>
       <c r="I12" s="21">
-        <f>INDEX('Расчёт аннуитета'!$D$25:$I$25,MATCH(SMALL('Расчёт аннуитета'!D23:I23,3),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>16.798597731761483</v>
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,3),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>16.693077861115874</v>
       </c>
     </row>
     <row r="13">
@@ -16516,17 +22668,17 @@
         <v>4</v>
       </c>
       <c r="C13" s="22" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(SMALL('Расчёт аннуитета'!D23:I23,4),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>Komatsu PC2000-11R
-ИСТК</v>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,4),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>Zoomlion ZE2000G
+Орикс</v>
       </c>
       <c r="G13" s="21">
-        <f>SMALL('Расчёт аннуитета'!D23:I23,4)</f>
-        <v>48.70275606837497</v>
+        <f>SMALL('Расчёт аннуитета'!D23:J23,4)</f>
+        <v>46.81769187841925</v>
       </c>
       <c r="I13" s="21">
-        <f>INDEX('Расчёт аннуитета'!$D$25:$I$25,MATCH(SMALL('Расчёт аннуитета'!D23:I23,4),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>17.474975266729448</v>
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,4),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>16.798597731761483</v>
       </c>
     </row>
     <row r="14">
@@ -16534,17 +22686,17 @@
         <v>5</v>
       </c>
       <c r="C14" s="22" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(SMALL('Расчёт аннуитета'!D23:I23,5),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>Komatsu PC2000-8
-Mining Solutions</v>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,5),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>Komatsu PC2000-11R
+ИСТК</v>
       </c>
       <c r="G14" s="21">
-        <f>SMALL('Расчёт аннуитета'!D23:I23,5)</f>
-        <v>67.89452309645975</v>
+        <f>SMALL('Расчёт аннуитета'!D23:J23,5)</f>
+        <v>48.70275606837497</v>
       </c>
       <c r="I14" s="21">
-        <f>INDEX('Расчёт аннуитета'!$D$25:$I$25,MATCH(SMALL('Расчёт аннуитета'!D23:I23,5),'Расчёт аннуитета'!D23:I23,0))</f>
-        <v>24.361149299052656</v>
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,5),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>17.474975266729448</v>
       </c>
     </row>
     <row r="15">
@@ -16552,20 +22704,38 @@
         <v>6</v>
       </c>
       <c r="C15" s="22" t="str">
-        <f>INDEX('Ввод данных'!D7:I7,MATCH(SMALL('Расчёт аннуитета'!D23:I23,6),'Расчёт аннуитета'!D23:I23,0))</f>
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,6),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>Komatsu PC2000-8
+Mining Solutions</v>
+      </c>
+      <c r="G15" s="21">
+        <f>SMALL('Расчёт аннуитета'!D23:J23,6)</f>
+        <v>67.89452309645975</v>
+      </c>
+      <c r="I15" s="21">
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,6),'Расчёт аннуитета'!D23:J23,0))</f>
+        <v>24.361149299052656</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="22" t="str">
+        <f>INDEX('Ввод данных'!D7:J7,MATCH(SMALL('Расчёт аннуитета'!D23:J23,7),'Расчёт аннуитета'!D23:J23,0))</f>
         <v>Shantui SE2000LCW</v>
       </c>
-      <c r="G15" s="21">
-        <f>SMALL('Расчёт аннуитета'!D23:I23,6)</f>
+      <c r="G16" s="21">
+        <f>SMALL('Расчёт аннуитета'!D23:J23,7)</f>
         <v>146.9834650001955</v>
       </c>
-      <c r="I15" s="21">
-        <f>INDEX('Расчёт аннуитета'!$D$25:$I$25,MATCH(SMALL('Расчёт аннуитета'!D23:I23,6),'Расчёт аннуитета'!D23:I23,0))</f>
+      <c r="I16" s="21">
+        <f>INDEX('Расчёт аннуитета'!$D$25:$J$25,MATCH(SMALL('Расчёт аннуитета'!D23:J23,7),'Расчёт аннуитета'!D23:J23,0))</f>
         <v>52.73895407254952</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="24">
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="B8:J8"/>
@@ -16579,12 +22749,14 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="E5"/>
     <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B1:N1"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="G9:H9"/>
@@ -17249,6 +23421,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -17325,6 +23498,11 @@
           <t>Экскаватор 6</t>
         </is>
       </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Экскаватор 7</t>
+        </is>
+      </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
           <t>Пояснение</t>
@@ -17393,6 +23571,12 @@
 Дзикай</t>
         </is>
       </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>XCMG ESTAR ESE2000
+(поставщик не указан)</t>
+        </is>
+      </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
           <t>Название варианта</t>
@@ -17440,6 +23624,11 @@
           <t>Дзикай</t>
         </is>
       </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K8" s="25" t="inlineStr"/>
     </row>
     <row r="9">
@@ -17481,6 +23670,11 @@
       <c r="I9" s="30" t="inlineStr">
         <is>
           <t>Weichai 12M33</t>
+        </is>
+      </c>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>1102 л.с.</t>
         </is>
       </c>
       <c r="K9" s="25" t="inlineStr"/>
@@ -17530,6 +23724,9 @@
       <c r="I11" s="31" t="n">
         <v>15400</v>
       </c>
+      <c r="J11" s="31" t="n">
+        <v>18000</v>
+      </c>
       <c r="K11" s="25" t="inlineStr">
         <is>
           <t>В валюте контракта</t>
@@ -17577,6 +23774,11 @@
           <t>CNY</t>
         </is>
       </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
       <c r="K12" s="25" t="inlineStr">
         <is>
           <t>CNY / USD / EUR / RUB</t>
@@ -17612,6 +23814,9 @@
       <c r="I13" s="31" t="n">
         <v>0</v>
       </c>
+      <c r="J13" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="K13" s="25" t="inlineStr">
         <is>
           <t>Дополнительно к цене</t>
@@ -17645,6 +23850,9 @@
         <v>0</v>
       </c>
       <c r="I14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="25" t="inlineStr">
@@ -17698,6 +23906,9 @@
       <c r="I16" s="33" t="n">
         <v>12</v>
       </c>
+      <c r="J16" s="33" t="n">
+        <v>12</v>
+      </c>
       <c r="K16" s="25" t="inlineStr">
         <is>
           <t>Участвует в расчёте производительности</t>
@@ -17733,6 +23944,9 @@
       <c r="I17" s="33" t="n">
         <v>37.3</v>
       </c>
+      <c r="J17" s="33" t="n">
+        <v>26</v>
+      </c>
       <c r="K17" s="25" t="inlineStr">
         <is>
           <t>Черпание–поворот–разгрузка–поворот</t>
@@ -17766,6 +23980,9 @@
         <v>266.1</v>
       </c>
       <c r="I18" s="33" t="n">
+        <v>266.1</v>
+      </c>
+      <c r="J18" s="33" t="n">
         <v>266.1</v>
       </c>
       <c r="K18" s="25" t="inlineStr">
@@ -17817,6 +24034,9 @@
         <v>10015</v>
       </c>
       <c r="I20" s="31" t="n">
+        <v>10015</v>
+      </c>
+      <c r="J20" s="31" t="n">
         <v>10015</v>
       </c>
       <c r="K20" s="25" t="inlineStr">
@@ -17843,7 +24063,7 @@
     <mergeCell ref="B19:K19"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D12:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D12:J12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"CNY,USD,EUR,RUB"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19023,43 +25243,43 @@
         </is>
       </c>
       <c r="E35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(E70:E70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(E74:E103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(E70:E70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(E74:E103&gt;0)*1),0))*$E$29/1000</f>
         <v>1.2</v>
       </c>
       <c r="F35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(F70:F70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(F74:F103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(F70:F70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(F74:F103&gt;0)*1),0))*$E$29/1000</f>
         <v>24.0</v>
       </c>
       <c r="G35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(G70:G70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(G74:G103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(G70:G70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(G74:G103&gt;0)*1),0))*$E$29/1000</f>
         <v>21.6</v>
       </c>
       <c r="H35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(H70:H70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(H74:H103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(H70:H70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(H74:H103&gt;0)*1),0))*$E$29/1000</f>
         <v>22.8</v>
       </c>
       <c r="I35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(I70:I70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(I74:I103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(I70:I70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(I74:I103&gt;0)*1),0))*$E$29/1000</f>
         <v>3.6</v>
       </c>
       <c r="J35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(J70:J70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(J74:J103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(J70:J70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(J74:J103&gt;0)*1),0))*$E$29/1000</f>
         <v>36.0</v>
       </c>
       <c r="K35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(K70:K70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(K74:K103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(K70:K70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(K74:K103&gt;0)*1),0))*$E$29/1000</f>
         <v>9.6</v>
       </c>
       <c r="L35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(L70:L70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(L74:L103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(L70:L70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(L74:L103&gt;0)*1),0))*$E$29/1000</f>
         <v>34.8</v>
       </c>
       <c r="M35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(M70:M70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(M74:M103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(M70:M70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(M74:M103&gt;0)*1),0))*$E$29/1000</f>
         <v>10.8</v>
       </c>
       <c r="N35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(N70:N70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(N74:N103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(N70:N70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(N74:N103&gt;0)*1),0))*$E$29/1000</f>
         <v>16.8</v>
       </c>
     </row>
@@ -22793,43 +29013,43 @@
         </is>
       </c>
       <c r="E35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(E70:E70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(E74:E89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(E70:E70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(E74:E89&gt;0)*1),0))*$E$29/1000</f>
         <v>0.0</v>
       </c>
       <c r="F35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(F70:F70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(F74:F89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(F70:F70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(F74:F89&gt;0)*1),0))*$E$29/1000</f>
         <v>3.6</v>
       </c>
       <c r="G35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(G70:G70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(G74:G89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(G70:G70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(G74:G89&gt;0)*1),0))*$E$29/1000</f>
         <v>7.2</v>
       </c>
       <c r="H35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(H70:H70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(H74:H89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(H70:H70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(H74:H89&gt;0)*1),0))*$E$29/1000</f>
         <v>10.8</v>
       </c>
       <c r="I35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(I70:I70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(I74:I89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(I70:I70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(I74:I89&gt;0)*1),0))*$E$29/1000</f>
         <v>1.2</v>
       </c>
       <c r="J35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(J70:J70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(J74:J89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(J70:J70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(J74:J89&gt;0)*1),0))*$E$29/1000</f>
         <v>10.8</v>
       </c>
       <c r="K35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(K70:K70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(K74:K89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(K70:K70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(K74:K89&gt;0)*1),0))*$E$29/1000</f>
         <v>3.6</v>
       </c>
       <c r="L35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(L70:L70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(L74:L89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(L70:L70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(L74:L89&gt;0)*1),0))*$E$29/1000</f>
         <v>7.2</v>
       </c>
       <c r="M35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(M70:M70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(M74:M89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(M70:M70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(M74:M89&gt;0)*1),0))*$E$29/1000</f>
         <v>12.0</v>
       </c>
       <c r="N35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(N70:N70&gt;0)*1)+SUMPRODUCT($P$74:$P$89,(N74:N89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(N70:N70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$89,(N74:N89&gt;0)*1),0))*$E$29/1000</f>
         <v>0.0</v>
       </c>
     </row>
@@ -25723,43 +31943,43 @@
         </is>
       </c>
       <c r="E35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(E75:E89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(E75:E89&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="F35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(F75:F89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(F75:F89&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
       <c r="G35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(G75:G89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(G75:G89&gt;0)*1),0))*$E$29/1000</f>
         <v>18.0</v>
       </c>
       <c r="H35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(H75:H89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(H75:H89&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
       <c r="I35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(I75:I89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(I75:I89&gt;0)*1),0))*$E$29/1000</f>
         <v>16.8</v>
       </c>
       <c r="J35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(J75:J89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(J75:J89&gt;0)*1),0))*$E$29/1000</f>
         <v>6.0</v>
       </c>
       <c r="K35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(K75:K89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(K75:K89&gt;0)*1),0))*$E$29/1000</f>
         <v>14.4</v>
       </c>
       <c r="L35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(L75:L89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(L75:L89&gt;0)*1),0))*$E$29/1000</f>
         <v>7.2</v>
       </c>
       <c r="M35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(M75:M89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(M75:M89&gt;0)*1),0))*$E$29/1000</f>
         <v>18.0</v>
       </c>
       <c r="N35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(N75:N89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(N75:N89&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
     </row>
@@ -28709,43 +34929,43 @@
         </is>
       </c>
       <c r="E35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(E75:E89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(E70:E71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(E75:E89&gt;0)*1),0))*$E$29/1000</f>
         <v>2.4</v>
       </c>
       <c r="F35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(F75:F89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(F70:F71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(F75:F89&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
       <c r="G35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(G75:G89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(G70:G71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(G75:G89&gt;0)*1),0))*$E$29/1000</f>
         <v>18.0</v>
       </c>
       <c r="H35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(H75:H89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(H70:H71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(H75:H89&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
       <c r="I35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(I75:I89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(I70:I71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(I75:I89&gt;0)*1),0))*$E$29/1000</f>
         <v>16.8</v>
       </c>
       <c r="J35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(J75:J89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(J70:J71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(J75:J89&gt;0)*1),0))*$E$29/1000</f>
         <v>6.0</v>
       </c>
       <c r="K35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(K75:K89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(K70:K71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(K75:K89&gt;0)*1),0))*$E$29/1000</f>
         <v>14.4</v>
       </c>
       <c r="L35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(L75:L89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(L70:L71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(L75:L89&gt;0)*1),0))*$E$29/1000</f>
         <v>7.2</v>
       </c>
       <c r="M35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(M75:M89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(M70:M71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(M75:M89&gt;0)*1),0))*$E$29/1000</f>
         <v>18.0</v>
       </c>
       <c r="N35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1)+SUMPRODUCT($P$75:$P$89,(N75:N89&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$71,(N70:N71&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$75:$P$89,(N75:N89&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
     </row>
@@ -31694,43 +37914,43 @@
         </is>
       </c>
       <c r="E35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(E70:E70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(E74:E103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(E70:E70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(E74:E103&gt;0)*1),0))*$E$29/1000</f>
         <v>1.2</v>
       </c>
       <c r="F35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(F70:F70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(F74:F103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(F70:F70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(F74:F103&gt;0)*1),0))*$E$29/1000</f>
         <v>14.4</v>
       </c>
       <c r="G35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(G70:G70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(G74:G103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(G70:G70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(G74:G103&gt;0)*1),0))*$E$29/1000</f>
         <v>19.2</v>
       </c>
       <c r="H35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(H70:H70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(H74:H103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(H70:H70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(H74:H103&gt;0)*1),0))*$E$29/1000</f>
         <v>15.6</v>
       </c>
       <c r="I35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(I70:I70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(I74:I103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(I70:I70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(I74:I103&gt;0)*1),0))*$E$29/1000</f>
         <v>4.8</v>
       </c>
       <c r="J35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(J70:J70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(J74:J103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(J70:J70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(J74:J103&gt;0)*1),0))*$E$29/1000</f>
         <v>32.4</v>
       </c>
       <c r="K35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(K70:K70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(K74:K103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(K70:K70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(K74:K103&gt;0)*1),0))*$E$29/1000</f>
         <v>15.6</v>
       </c>
       <c r="L35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(L70:L70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(L74:L103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(L70:L70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(L74:L103&gt;0)*1),0))*$E$29/1000</f>
         <v>19.2</v>
       </c>
       <c r="M35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(M70:M70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(M74:M103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(M70:M70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(M74:M103&gt;0)*1),0))*$E$29/1000</f>
         <v>18.0</v>
       </c>
       <c r="N35" s="38">
-        <f>(SUMPRODUCT($P$70:$P$70,(N70:N70&gt;0)*1)+SUMPRODUCT($P$74:$P$103,(N74:N103&gt;0)*1))*$E$29/1000</f>
+        <f>(IFERROR(SUMPRODUCT($P$70:$P$70,(N70:N70&gt;0)*1),0)+IFERROR(SUMPRODUCT($P$74:$P$103,(N74:N103&gt;0)*1),0))*$E$29/1000</f>
         <v>1.2</v>
       </c>
     </row>
